--- a/ACCY122/Session/S04/ACCY122 L4 Workbook.xlsx
+++ b/ACCY122/Session/S04/ACCY122 L4 Workbook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onlym\Desktop\Manek\Notes\SIM\UOW\2026 UOW\Learning Material\In Session Explanation\L4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Session/S04/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CA7FE1-7C79-4C7A-80B2-FF7C2E86C6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80AF51A3-F80C-EA4E-A5D7-308ACCDC4FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" activeTab="2" xr2:uid="{49300C88-9C68-40D1-BFDB-69B44FEEA068}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18760" xr2:uid="{49300C88-9C68-40D1-BFDB-69B44FEEA068}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="233">
   <si>
     <t>Balanced Day Adjustments</t>
   </si>
@@ -768,13 +768,16 @@
   </si>
   <si>
     <t>Int Payable</t>
+  </si>
+  <si>
+    <t>for journals always start with with dr side 1st </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -837,6 +840,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1177,7 +1186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1319,9 +1328,6 @@
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1329,7 +1335,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1338,7 +1343,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1351,9 +1356,10 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1399,8 +1405,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1065254" y="634714"/>
-          <a:ext cx="5737589" cy="5657269"/>
+          <a:off x="1094349" y="666380"/>
+          <a:ext cx="5999442" cy="5984498"/>
           <a:chOff x="0" y="78429"/>
           <a:chExt cx="6059328" cy="3928254"/>
         </a:xfrm>
@@ -2483,9 +2489,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3154719-4B7A-4BD1-A273-F4DC249F84D4}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <dimension ref="C38"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C38" s="84" t="s">
+        <v>232</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2494,27 +2506,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F923618A-53E6-4AA0-84BA-AB41705F9398}">
   <dimension ref="B1:O20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="18.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.46484375" customWidth="1"/>
-    <col min="7" max="7" width="10.46484375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.06640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.46484375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.2">
       <c r="G1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F3" t="s">
         <v>2</v>
       </c>
@@ -2531,7 +2543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2549,7 +2561,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="2" t="s">
@@ -2563,8 +2575,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="C6" s="71" t="s">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C6" s="83" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="1"/>
@@ -2591,8 +2603,8 @@
       </c>
       <c r="O6" s="7"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="C7" s="71"/>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C7" s="83"/>
       <c r="D7" s="1"/>
       <c r="E7" s="2" t="s">
         <v>11</v>
@@ -2604,8 +2616,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="C8" s="71"/>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C8" s="83"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
         <v>21</v>
@@ -2618,8 +2630,8 @@
       </c>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="C9" s="71"/>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C9" s="83"/>
       <c r="D9" s="1"/>
       <c r="E9" s="2" t="s">
         <v>11</v>
@@ -2627,8 +2639,8 @@
       <c r="M9" s="6"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="C10" s="71"/>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C10" s="83"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
         <v>23</v>
@@ -2656,7 +2668,7 @@
       </c>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" spans="2:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -2676,7 +2688,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="2" t="s">
@@ -2693,7 +2705,7 @@
       </c>
       <c r="O12" s="7"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>32</v>
       </c>
@@ -2710,7 +2722,7 @@
       <c r="M13" s="6"/>
       <c r="O13" s="7"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F14" t="s">
         <v>168</v>
       </c>
@@ -2728,7 +2740,7 @@
       </c>
       <c r="O14" s="7"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="M15" s="6" t="s">
         <v>36</v>
       </c>
@@ -2736,17 +2748,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
       <c r="M16" s="6" t="s">
         <v>37</v>
       </c>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="11:15" x14ac:dyDescent="0.45">
+    <row r="17" spans="11:15" x14ac:dyDescent="0.2">
       <c r="M17" s="6"/>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" spans="11:15" x14ac:dyDescent="0.45">
+    <row r="18" spans="11:15" x14ac:dyDescent="0.2">
       <c r="K18">
         <v>4</v>
       </c>
@@ -2761,7 +2773,7 @@
       </c>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" spans="11:15" x14ac:dyDescent="0.45">
+    <row r="19" spans="11:15" x14ac:dyDescent="0.2">
       <c r="M19" s="6" t="s">
         <v>40</v>
       </c>
@@ -2769,7 +2781,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="11:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="20" spans="11:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="M20" s="11" t="s">
         <v>41</v>
       </c>
@@ -2790,13 +2802,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC50BE0-433C-401E-8C60-EBD47C86025A}">
   <dimension ref="A1:M35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="18.1328125" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" customWidth="1"/>
     <col min="11" max="11" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B1" s="3"/>
       <c r="C1" s="4" t="s">
         <v>15</v>
@@ -2807,28 +2819,28 @@
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>93</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" t="s">
         <v>181</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" t="s">
         <v>191</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="74">
+      <c r="B3" s="73">
         <v>46387</v>
       </c>
       <c r="C3" s="4"/>
@@ -2838,16 +2850,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="6"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
       <c r="E4" s="7"/>
-      <c r="G4" s="73" t="s">
+      <c r="G4" s="72" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -2856,242 +2866,218 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="6"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
-      <c r="B7" s="74">
+      <c r="B7" s="73">
         <v>46387</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="5"/>
-      <c r="G7" s="73">
+      <c r="G7" s="72">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B8" s="6"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
       <c r="E8" s="7"/>
-      <c r="G8" s="73" t="s">
+      <c r="G8" s="72" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11"/>
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
       <c r="E9" s="13"/>
-      <c r="G9" s="73">
+      <c r="G9" s="72">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="6"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
       <c r="E10" s="7"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>3</v>
       </c>
-      <c r="B11" s="74">
+      <c r="B11" s="73">
         <v>46387</v>
       </c>
-      <c r="C11" s="86"/>
+      <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="5"/>
-      <c r="G11" s="73">
+      <c r="G11" s="72">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="6"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="75"/>
       <c r="E12" s="7"/>
-      <c r="G12" s="73" t="s">
+      <c r="G12" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-    </row>
-    <row r="13" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+    </row>
+    <row r="13" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="11"/>
-      <c r="C13" s="87"/>
+      <c r="C13" s="12"/>
       <c r="D13" s="12"/>
       <c r="E13" s="13"/>
-      <c r="G13" s="73">
+      <c r="G13" s="72">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="6"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
       <c r="E14" s="7"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>4</v>
       </c>
-      <c r="B15" s="74">
+      <c r="B15" s="73">
         <v>46387</v>
       </c>
-      <c r="C15" s="86"/>
+      <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="5"/>
-      <c r="G15" s="73">
+      <c r="G15" s="72">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="6"/>
-      <c r="C16" s="85"/>
-      <c r="D16" s="75"/>
       <c r="E16" s="7"/>
-      <c r="G16" s="73" t="s">
+      <c r="G16" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="H16" s="72"/>
-      <c r="I16" s="72"/>
-    </row>
-    <row r="17" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+    </row>
+    <row r="17" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="11"/>
-      <c r="C17" s="87"/>
+      <c r="C17" s="12"/>
       <c r="D17" s="12"/>
       <c r="E17" s="13"/>
-      <c r="G17" s="73">
+      <c r="G17" s="72">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="6"/>
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
       <c r="E18" s="7"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>5</v>
       </c>
-      <c r="B19" s="74">
+      <c r="B19" s="73">
         <v>46387</v>
       </c>
-      <c r="C19" s="85"/>
-      <c r="D19" s="75"/>
       <c r="E19" s="7"/>
-      <c r="G19" s="73">
+      <c r="G19" s="72">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B20" s="6"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="75"/>
       <c r="E20" s="7"/>
-      <c r="G20" s="73" t="s">
+      <c r="G20" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="H20" s="72"/>
-      <c r="I20" s="72"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B21" s="6"/>
-      <c r="C21" s="85"/>
-      <c r="D21" s="75"/>
       <c r="E21" s="7"/>
-      <c r="G21" s="73">
+      <c r="G21" s="72">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B22" s="11"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
       <c r="E22" s="13"/>
     </row>
-    <row r="23" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>6</v>
       </c>
-      <c r="B24" s="74">
+      <c r="B24" s="73">
         <v>46387</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="5"/>
-      <c r="G24" s="73">
+      <c r="G24" s="72">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B25" s="6"/>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
       <c r="E25" s="7"/>
-      <c r="G25" s="73" t="s">
+      <c r="G25" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="H25" s="72"/>
-      <c r="I25" s="72"/>
-    </row>
-    <row r="26" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+    </row>
+    <row r="26" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="11"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
       <c r="E26" s="13"/>
-      <c r="G26" s="73">
+      <c r="G26" s="72">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="28" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>7</v>
       </c>
-      <c r="B28" s="74">
+      <c r="B28" s="73">
         <v>46387</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="5"/>
-      <c r="G28" s="73">
+      <c r="G28" s="72">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B29" s="6"/>
-      <c r="C29" s="75"/>
-      <c r="D29" s="75"/>
       <c r="E29" s="4"/>
-      <c r="G29" s="73" t="s">
+      <c r="G29" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72"/>
-    </row>
-    <row r="30" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+    </row>
+    <row r="30" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B30" s="11"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
       <c r="E30" s="13"/>
-      <c r="G30" s="73">
+      <c r="G30" s="72">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="G32">
         <v>1</v>
       </c>
@@ -3101,15 +3087,15 @@
       <c r="I32" t="s">
         <v>192</v>
       </c>
-      <c r="K32" s="76"/>
-      <c r="L32" s="77" t="s">
+      <c r="K32" s="74"/>
+      <c r="L32" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="M32" s="78" t="s">
+      <c r="M32" s="76" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="7:13" x14ac:dyDescent="0.45">
+    <row r="33" spans="7:13" x14ac:dyDescent="0.2">
       <c r="G33">
         <v>2</v>
       </c>
@@ -3119,37 +3105,37 @@
       <c r="I33" t="s">
         <v>194</v>
       </c>
-      <c r="K33" s="79" t="s">
+      <c r="K33" s="77" t="s">
         <v>202</v>
       </c>
-      <c r="L33" s="80" t="s">
+      <c r="L33" s="78" t="s">
         <v>204</v>
       </c>
-      <c r="M33" s="81" t="s">
+      <c r="M33" s="79" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="7:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="34" spans="7:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G34">
         <v>3</v>
       </c>
-      <c r="H34" s="72" t="s">
+      <c r="H34" s="71" t="s">
         <v>196</v>
       </c>
-      <c r="I34" s="72" t="s">
+      <c r="I34" s="71" t="s">
         <v>196</v>
       </c>
-      <c r="K34" s="82" t="s">
+      <c r="K34" s="80" t="s">
         <v>203</v>
       </c>
-      <c r="L34" s="83" t="s">
+      <c r="L34" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="M34" s="84" t="s">
+      <c r="M34" s="82" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="35" spans="7:13" x14ac:dyDescent="0.45">
+    <row r="35" spans="7:13" x14ac:dyDescent="0.2">
       <c r="G35">
         <v>4</v>
       </c>
@@ -3168,32 +3154,32 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{431369FE-F92F-4C37-9408-0538561CEBA7}">
   <dimension ref="A1:U32"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.53125" customWidth="1"/>
-    <col min="2" max="2" width="6.73046875" customWidth="1"/>
-    <col min="3" max="4" width="8.73046875" customWidth="1"/>
+    <col min="1" max="1" width="31.5" customWidth="1"/>
+    <col min="2" max="2" width="6.6640625" customWidth="1"/>
+    <col min="3" max="4" width="8.6640625" customWidth="1"/>
     <col min="5" max="5" width="4.33203125" customWidth="1"/>
-    <col min="6" max="7" width="8.73046875" customWidth="1"/>
-    <col min="8" max="8" width="2.73046875" customWidth="1"/>
-    <col min="9" max="9" width="9.19921875" customWidth="1"/>
-    <col min="10" max="10" width="9.73046875" customWidth="1"/>
-    <col min="11" max="11" width="2.59765625" customWidth="1"/>
-    <col min="12" max="12" width="10.06640625" customWidth="1"/>
-    <col min="13" max="13" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="8.6640625" customWidth="1"/>
+    <col min="8" max="8" width="2.6640625" customWidth="1"/>
+    <col min="9" max="9" width="9.1640625" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" customWidth="1"/>
+    <col min="11" max="11" width="2.6640625" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="2.33203125" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="11.53125" customWidth="1"/>
-    <col min="18" max="18" width="13.265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.53125" customWidth="1"/>
-    <col min="20" max="21" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5" customWidth="1"/>
+    <col min="18" max="18" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.5" customWidth="1"/>
+    <col min="20" max="21" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
       <c r="B1" s="14"/>
     </row>
-    <row r="2" spans="1:21" ht="14.55" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="22" t="s">
         <v>42</v>
       </c>
@@ -3229,7 +3215,7 @@
       </c>
       <c r="P2" s="40"/>
     </row>
-    <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>43</v>
       </c>
@@ -3251,7 +3237,7 @@
       <c r="O3" s="47"/>
       <c r="P3" s="45"/>
     </row>
-    <row r="4" spans="1:21" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>44</v>
       </c>
@@ -3294,7 +3280,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="5" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
         <v>47</v>
       </c>
@@ -3335,7 +3321,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="6" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
         <v>48</v>
       </c>
@@ -3379,7 +3365,7 @@
       </c>
       <c r="U6" s="63"/>
     </row>
-    <row r="7" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="7" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
         <v>49</v>
       </c>
@@ -3421,7 +3407,7 @@
         <v>126500</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="8" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
         <v>50</v>
       </c>
@@ -3456,7 +3442,7 @@
       <c r="T8" s="65"/>
       <c r="U8" s="66"/>
     </row>
-    <row r="9" spans="1:21" ht="31.9" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="9" spans="1:21" ht="35" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
         <v>51</v>
       </c>
@@ -3493,7 +3479,7 @@
       <c r="T9" s="32"/>
       <c r="U9" s="32"/>
     </row>
-    <row r="10" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="10" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="27" t="s">
         <v>177</v>
       </c>
@@ -3533,7 +3519,7 @@
       </c>
       <c r="U10" s="62"/>
     </row>
-    <row r="11" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="11" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
         <v>52</v>
       </c>
@@ -3570,7 +3556,7 @@
         <v>63510</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="12" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
         <v>53</v>
       </c>
@@ -3607,7 +3593,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="13" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
         <v>54</v>
       </c>
@@ -3644,7 +3630,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="14" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="27" t="s">
         <v>55</v>
       </c>
@@ -3685,7 +3671,7 @@
         <v>7520</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="15" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
         <v>56</v>
       </c>
@@ -3722,7 +3708,7 @@
         <v>4235</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="16" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="27" t="s">
         <v>57</v>
       </c>
@@ -3759,7 +3745,7 @@
         <v>3045</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="17" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
         <v>58</v>
       </c>
@@ -3796,7 +3782,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="18" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
         <v>59</v>
       </c>
@@ -3837,7 +3823,7 @@
         <v>4940</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="19" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
         <v>60</v>
       </c>
@@ -3878,7 +3864,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="20" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
         <v>61</v>
       </c>
@@ -3921,7 +3907,7 @@
         <v>7400</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="21" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="27"/>
       <c r="B21" s="28"/>
       <c r="C21" s="15"/>
@@ -3943,7 +3929,7 @@
       <c r="T21" s="32"/>
       <c r="U21" s="32"/>
     </row>
-    <row r="22" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="22" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="30" t="s">
         <v>69</v>
       </c>
@@ -3986,7 +3972,7 @@
       </c>
       <c r="U22" s="62"/>
     </row>
-    <row r="23" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="23" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="30" t="s">
         <v>70</v>
       </c>
@@ -4026,7 +4012,7 @@
         <v>29555</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="24" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="30" t="s">
         <v>71</v>
       </c>
@@ -4063,7 +4049,7 @@
       <c r="T24" s="65"/>
       <c r="U24" s="66"/>
     </row>
-    <row r="25" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="25" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="30" t="s">
         <v>72</v>
       </c>
@@ -4098,7 +4084,7 @@
       <c r="T25" s="32"/>
       <c r="U25" s="32"/>
     </row>
-    <row r="26" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="26" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A26" s="30" t="s">
         <v>73</v>
       </c>
@@ -4139,7 +4125,7 @@
       </c>
       <c r="U26" s="62"/>
     </row>
-    <row r="27" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="27" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A27" s="30" t="s">
         <v>74</v>
       </c>
@@ -4179,7 +4165,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="28" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="30" t="s">
         <v>75</v>
       </c>
@@ -4216,7 +4202,7 @@
       <c r="T28" s="12"/>
       <c r="U28" s="13"/>
     </row>
-    <row r="29" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="29" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>179</v>
       </c>
@@ -4241,7 +4227,7 @@
         <v>29555</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="30" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A30" s="32"/>
       <c r="B30" s="29"/>
       <c r="C30" s="15"/>
@@ -4259,7 +4245,7 @@
       <c r="O30" s="52"/>
       <c r="P30" s="53"/>
     </row>
-    <row r="31" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="31" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
         <v>68</v>
       </c>
@@ -4309,7 +4295,7 @@
         <v>118860</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="L32">
         <f>M31-L31</f>
         <v>0</v>
@@ -4324,18 +4310,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451FE678-24D7-4F17-8C17-332E4659A9B1}">
   <dimension ref="A1:P35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.59765625" customWidth="1"/>
-    <col min="3" max="4" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="3.53125" customWidth="1"/>
-    <col min="11" max="11" width="3.19921875" customWidth="1"/>
+    <col min="1" max="1" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="3" max="4" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="3.5" customWidth="1"/>
+    <col min="11" max="11" width="3.1640625" customWidth="1"/>
     <col min="14" max="14" width="3.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="27" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:16" ht="32" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>124</v>
       </c>
@@ -4371,7 +4357,7 @@
       </c>
       <c r="P1" s="21"/>
     </row>
-    <row r="2" spans="1:16" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="15"/>
       <c r="C2" s="15"/>
@@ -4391,7 +4377,7 @@
       <c r="O2" s="21"/>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="3" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
         <v>94</v>
       </c>
@@ -4431,7 +4417,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="4" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>77</v>
       </c>
@@ -4453,7 +4439,7 @@
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
     </row>
-    <row r="5" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="5" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>95</v>
       </c>
@@ -4475,7 +4461,7 @@
       <c r="O5" s="15"/>
       <c r="P5" s="15"/>
     </row>
-    <row r="6" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="6" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>96</v>
       </c>
@@ -4497,7 +4483,7 @@
       <c r="O6" s="15"/>
       <c r="P6" s="15"/>
     </row>
-    <row r="7" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="7" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>78</v>
       </c>
@@ -4525,7 +4511,7 @@
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
     </row>
-    <row r="8" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="8" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>97</v>
       </c>
@@ -4547,7 +4533,7 @@
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
     </row>
-    <row r="9" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="9" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
         <v>98</v>
       </c>
@@ -4569,7 +4555,7 @@
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
     </row>
-    <row r="10" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="10" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>189</v>
       </c>
@@ -4596,7 +4582,7 @@
       <c r="O10" s="15"/>
       <c r="P10" s="15"/>
     </row>
-    <row r="11" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="11" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
         <v>80</v>
       </c>
@@ -4618,7 +4604,7 @@
       <c r="O11" s="15"/>
       <c r="P11" s="15"/>
     </row>
-    <row r="12" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="12" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>190</v>
       </c>
@@ -4645,7 +4631,7 @@
       <c r="O12" s="15"/>
       <c r="P12" s="15"/>
     </row>
-    <row r="13" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="13" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
         <v>99</v>
       </c>
@@ -4667,7 +4653,7 @@
       <c r="O13" s="15"/>
       <c r="P13" s="15"/>
     </row>
-    <row r="14" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="14" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
         <v>100</v>
       </c>
@@ -4695,7 +4681,7 @@
       <c r="O14" s="15"/>
       <c r="P14" s="15"/>
     </row>
-    <row r="15" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="15" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
         <v>101</v>
       </c>
@@ -4717,7 +4703,7 @@
       <c r="O15" s="15"/>
       <c r="P15" s="15"/>
     </row>
-    <row r="16" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="16" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
         <v>102</v>
       </c>
@@ -4739,7 +4725,7 @@
       <c r="O16" s="15"/>
       <c r="P16" s="15"/>
     </row>
-    <row r="17" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="17" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
         <v>103</v>
       </c>
@@ -4761,7 +4747,7 @@
       <c r="O17" s="15"/>
       <c r="P17" s="15"/>
     </row>
-    <row r="18" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="18" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
         <v>104</v>
       </c>
@@ -4783,7 +4769,7 @@
       <c r="O18" s="15"/>
       <c r="P18" s="15"/>
     </row>
-    <row r="19" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="19" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
         <v>105</v>
       </c>
@@ -4811,7 +4797,7 @@
       <c r="O19" s="15"/>
       <c r="P19" s="15"/>
     </row>
-    <row r="20" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="20" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>70</v>
       </c>
@@ -4837,7 +4823,7 @@
       <c r="O20" s="15"/>
       <c r="P20" s="15"/>
     </row>
-    <row r="21" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="21" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
         <v>84</v>
       </c>
@@ -4863,7 +4849,7 @@
       <c r="O21" s="15"/>
       <c r="P21" s="15"/>
     </row>
-    <row r="22" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="22" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
         <v>88</v>
       </c>
@@ -4885,7 +4871,7 @@
       <c r="O22" s="15"/>
       <c r="P22" s="15"/>
     </row>
-    <row r="23" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="23" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
         <v>90</v>
       </c>
@@ -4911,7 +4897,7 @@
       <c r="O23" s="15"/>
       <c r="P23" s="15"/>
     </row>
-    <row r="24" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="24" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
         <v>106</v>
       </c>
@@ -4939,7 +4925,7 @@
       <c r="O24" s="15"/>
       <c r="P24" s="15"/>
     </row>
-    <row r="25" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+    <row r="25" spans="1:16" ht="20" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>125</v>
       </c>
@@ -4965,7 +4951,7 @@
       <c r="O25" s="15"/>
       <c r="P25" s="15"/>
     </row>
-    <row r="26" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+    <row r="26" spans="1:16" ht="20" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>126</v>
       </c>
@@ -4989,7 +4975,7 @@
       <c r="O26" s="15"/>
       <c r="P26" s="15"/>
     </row>
-    <row r="27" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+    <row r="27" spans="1:16" ht="20" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
         <v>127</v>
       </c>
@@ -5013,7 +4999,7 @@
       <c r="O27" s="15"/>
       <c r="P27" s="15"/>
     </row>
-    <row r="28" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+    <row r="28" spans="1:16" ht="20" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
         <v>79</v>
       </c>
@@ -5037,7 +5023,7 @@
       <c r="O28" s="15"/>
       <c r="P28" s="15"/>
     </row>
-    <row r="29" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+    <row r="29" spans="1:16" ht="20" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
         <v>75</v>
       </c>
@@ -5061,7 +5047,7 @@
       <c r="O29" s="15"/>
       <c r="P29" s="15"/>
     </row>
-    <row r="30" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+    <row r="30" spans="1:16" ht="20" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
         <v>128</v>
       </c>
@@ -5085,7 +5071,7 @@
       <c r="O30" s="15"/>
       <c r="P30" s="15"/>
     </row>
-    <row r="31" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+    <row r="31" spans="1:16" ht="20" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
         <v>72</v>
       </c>
@@ -5109,7 +5095,7 @@
       <c r="O31" s="15"/>
       <c r="P31" s="15"/>
     </row>
-    <row r="32" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+    <row r="32" spans="1:16" ht="19" x14ac:dyDescent="0.25">
       <c r="A32" s="18"/>
       <c r="B32" s="16"/>
       <c r="C32" s="15"/>
@@ -5127,7 +5113,7 @@
       <c r="O32" s="15"/>
       <c r="P32" s="15"/>
     </row>
-    <row r="33" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+    <row r="33" spans="1:16" ht="20" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
         <v>129</v>
       </c>
@@ -5147,7 +5133,7 @@
       <c r="O33" s="15"/>
       <c r="P33" s="15"/>
     </row>
-    <row r="34" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="34" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A34" s="17"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -5165,7 +5151,7 @@
       <c r="O34" s="15"/>
       <c r="P34" s="15"/>
     </row>
-    <row r="35" spans="1:16" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="35" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A35" s="14"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15">
@@ -5198,7 +5184,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB70836-D79F-4864-89CC-B27D7E0A03DC}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5207,13 +5193,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA4CDB96-6C4C-4200-8B12-486AAEF84CD0}">
   <dimension ref="A1:M35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="18.1328125" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" customWidth="1"/>
     <col min="11" max="11" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B1" s="3"/>
       <c r="C1" s="4" t="s">
         <v>15</v>
@@ -5224,28 +5210,28 @@
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>93</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" t="s">
         <v>181</v>
       </c>
-      <c r="D2" s="75" t="s">
+      <c r="D2" t="s">
         <v>191</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="74">
+      <c r="B3" s="73">
         <v>46387</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -5265,17 +5251,16 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="6"/>
-      <c r="C4" s="75" t="s">
+      <c r="C4" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="75"/>
       <c r="E4" s="7">
         <f>D3</f>
         <v>4940</v>
       </c>
-      <c r="G4" s="73" t="s">
+      <c r="G4" s="72" t="s">
         <v>197</v>
       </c>
       <c r="H4" t="s">
@@ -5285,7 +5270,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11"/>
       <c r="C5" s="12" t="s">
         <v>208</v>
@@ -5302,17 +5287,15 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="6"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
-      <c r="B7" s="74">
+      <c r="B7" s="73">
         <v>46387</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -5322,7 +5305,7 @@
         <v>1185</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="G7" s="73">
+      <c r="G7" s="72">
         <v>1</v>
       </c>
       <c r="H7" t="s">
@@ -5332,16 +5315,15 @@
         <v>210</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B8" s="6"/>
-      <c r="C8" s="75" t="s">
+      <c r="C8" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="75"/>
       <c r="E8" s="7">
         <v>1185</v>
       </c>
-      <c r="G8" s="73" t="s">
+      <c r="G8" s="72" t="s">
         <v>197</v>
       </c>
       <c r="H8" t="s">
@@ -5351,14 +5333,14 @@
         <v>201</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11"/>
       <c r="C9" s="12" t="s">
         <v>212</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="13"/>
-      <c r="G9" s="73">
+      <c r="G9" s="72">
         <v>4</v>
       </c>
       <c r="H9" t="s">
@@ -5368,27 +5350,25 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="6"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
       <c r="E10" s="7"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>3</v>
       </c>
-      <c r="B11" s="74">
+      <c r="B11" s="73">
         <v>46387</v>
       </c>
-      <c r="C11" s="86" t="s">
+      <c r="C11" s="4" t="s">
         <v>214</v>
       </c>
       <c r="D11" s="4">
         <v>7400</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="G11" s="73">
+      <c r="G11" s="72">
         <v>1</v>
       </c>
       <c r="H11" t="s">
@@ -5398,33 +5378,32 @@
         <v>214</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="6"/>
-      <c r="C12" s="85" t="s">
+      <c r="C12" t="s">
         <v>213</v>
       </c>
-      <c r="D12" s="75"/>
       <c r="E12" s="7">
         <v>7400</v>
       </c>
-      <c r="G12" s="73" t="s">
+      <c r="G12" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="H12" s="72" t="s">
+      <c r="H12" s="71" t="s">
         <v>201</v>
       </c>
-      <c r="I12" s="72" t="s">
+      <c r="I12" s="71" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="11"/>
-      <c r="C13" s="87" t="s">
+      <c r="C13" s="12" t="s">
         <v>217</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="13"/>
-      <c r="G13" s="73">
+      <c r="G13" s="72">
         <v>4</v>
       </c>
       <c r="H13" t="s">
@@ -5434,27 +5413,25 @@
         <v>216</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="6"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
       <c r="E14" s="7"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>4</v>
       </c>
-      <c r="B15" s="74">
+      <c r="B15" s="73">
         <v>46387</v>
       </c>
-      <c r="C15" s="86" t="s">
+      <c r="C15" s="4" t="s">
         <v>218</v>
       </c>
       <c r="D15" s="4">
         <v>260</v>
       </c>
       <c r="E15" s="5"/>
-      <c r="G15" s="73">
+      <c r="G15" s="72">
         <v>1</v>
       </c>
       <c r="H15" t="s">
@@ -5464,33 +5441,32 @@
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="6"/>
-      <c r="C16" s="85" t="s">
+      <c r="C16" t="s">
         <v>219</v>
       </c>
-      <c r="D16" s="75"/>
       <c r="E16" s="7">
         <v>260</v>
       </c>
-      <c r="G16" s="73" t="s">
+      <c r="G16" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="H16" s="72" t="s">
+      <c r="H16" s="71" t="s">
         <v>200</v>
       </c>
-      <c r="I16" s="72" t="s">
+      <c r="I16" s="71" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="11"/>
-      <c r="C17" s="87" t="s">
+      <c r="C17" s="12" t="s">
         <v>221</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="13"/>
-      <c r="G17" s="73">
+      <c r="G17" s="72">
         <v>4</v>
       </c>
       <c r="H17" t="s">
@@ -5500,27 +5476,25 @@
         <v>215</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="6"/>
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
       <c r="E18" s="7"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>5</v>
       </c>
-      <c r="B19" s="74">
+      <c r="B19" s="73">
         <v>46387</v>
       </c>
-      <c r="C19" s="85" t="s">
+      <c r="C19" t="s">
         <v>224</v>
       </c>
-      <c r="D19" s="75">
+      <c r="D19">
         <v>830</v>
       </c>
       <c r="E19" s="7"/>
-      <c r="G19" s="73">
+      <c r="G19" s="72">
         <v>1</v>
       </c>
       <c r="H19" t="s">
@@ -5530,33 +5504,31 @@
         <v>223</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B20" s="6"/>
-      <c r="C20" s="85" t="s">
+      <c r="C20" t="s">
         <v>225</v>
       </c>
-      <c r="D20" s="75"/>
       <c r="E20" s="7">
         <v>830</v>
       </c>
-      <c r="G20" s="73" t="s">
+      <c r="G20" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="H20" s="72" t="s">
+      <c r="H20" s="71" t="s">
         <v>200</v>
       </c>
-      <c r="I20" s="72" t="s">
+      <c r="I20" s="71" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B21" s="6"/>
-      <c r="C21" s="85" t="s">
+      <c r="C21" t="s">
         <v>226</v>
       </c>
-      <c r="D21" s="75"/>
       <c r="E21" s="7"/>
-      <c r="G21" s="73">
+      <c r="G21" s="72">
         <v>4</v>
       </c>
       <c r="H21" t="s">
@@ -5566,18 +5538,18 @@
         <v>215</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B22" s="11"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
       <c r="E22" s="13"/>
     </row>
-    <row r="23" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>6</v>
       </c>
-      <c r="B24" s="74">
+      <c r="B24" s="73">
         <v>46387</v>
       </c>
       <c r="C24" s="4" t="s">
@@ -5587,7 +5559,7 @@
         <v>425</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="G24" s="73">
+      <c r="G24" s="72">
         <v>1</v>
       </c>
       <c r="H24" t="s">
@@ -5597,33 +5569,32 @@
         <v>228</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B25" s="6"/>
-      <c r="C25" s="75" t="s">
+      <c r="C25" t="s">
         <v>228</v>
       </c>
-      <c r="D25" s="75"/>
       <c r="E25" s="7">
         <v>425</v>
       </c>
-      <c r="G25" s="73" t="s">
+      <c r="G25" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="H25" s="72" t="s">
+      <c r="H25" s="71" t="s">
         <v>200</v>
       </c>
-      <c r="I25" s="72" t="s">
+      <c r="I25" s="71" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="11"/>
       <c r="C26" s="12" t="s">
         <v>229</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="13"/>
-      <c r="G26" s="73">
+      <c r="G26" s="72">
         <v>4</v>
       </c>
       <c r="H26" t="s">
@@ -5633,12 +5604,12 @@
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="28" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>7</v>
       </c>
-      <c r="B28" s="74">
+      <c r="B28" s="73">
         <v>46387</v>
       </c>
       <c r="C28" s="4" t="s">
@@ -5648,7 +5619,7 @@
         <v>250</v>
       </c>
       <c r="E28" s="5"/>
-      <c r="G28" s="73">
+      <c r="G28" s="72">
         <v>1</v>
       </c>
       <c r="H28" t="s">
@@ -5658,33 +5629,32 @@
         <v>231</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B29" s="6"/>
-      <c r="C29" s="75" t="s">
+      <c r="C29" t="s">
         <v>231</v>
       </c>
-      <c r="D29" s="75"/>
       <c r="E29" s="4">
         <v>250</v>
       </c>
-      <c r="G29" s="73" t="s">
+      <c r="G29" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="H29" s="72" t="s">
+      <c r="H29" s="71" t="s">
         <v>200</v>
       </c>
-      <c r="I29" s="72" t="s">
+      <c r="I29" s="71" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B30" s="11"/>
       <c r="C30" s="12" t="s">
         <v>229</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="13"/>
-      <c r="G30" s="73">
+      <c r="G30" s="72">
         <v>4</v>
       </c>
       <c r="H30" t="s">
@@ -5694,8 +5664,8 @@
         <v>215</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="G32">
         <v>1</v>
       </c>
@@ -5705,15 +5675,15 @@
       <c r="I32" t="s">
         <v>192</v>
       </c>
-      <c r="K32" s="76"/>
-      <c r="L32" s="77" t="s">
+      <c r="K32" s="74"/>
+      <c r="L32" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="M32" s="78" t="s">
+      <c r="M32" s="76" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="7:13" x14ac:dyDescent="0.45">
+    <row r="33" spans="7:13" x14ac:dyDescent="0.2">
       <c r="G33">
         <v>2</v>
       </c>
@@ -5723,37 +5693,37 @@
       <c r="I33" t="s">
         <v>194</v>
       </c>
-      <c r="K33" s="79" t="s">
+      <c r="K33" s="77" t="s">
         <v>202</v>
       </c>
-      <c r="L33" s="80" t="s">
+      <c r="L33" s="78" t="s">
         <v>204</v>
       </c>
-      <c r="M33" s="81" t="s">
+      <c r="M33" s="79" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="7:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="34" spans="7:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G34">
         <v>3</v>
       </c>
-      <c r="H34" s="72" t="s">
+      <c r="H34" s="71" t="s">
         <v>196</v>
       </c>
-      <c r="I34" s="72" t="s">
+      <c r="I34" s="71" t="s">
         <v>196</v>
       </c>
-      <c r="K34" s="82" t="s">
+      <c r="K34" s="80" t="s">
         <v>203</v>
       </c>
-      <c r="L34" s="83" t="s">
+      <c r="L34" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="M34" s="84" t="s">
+      <c r="M34" s="82" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="35" spans="7:13" x14ac:dyDescent="0.45">
+    <row r="35" spans="7:13" x14ac:dyDescent="0.2">
       <c r="G35">
         <v>4</v>
       </c>
@@ -5772,14 +5742,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14BBB4DE-EA90-4F91-8180-6C1E6B7C8861}">
   <dimension ref="A2:L32"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.06640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.796875" customWidth="1"/>
-    <col min="10" max="10" width="9.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
         <v>76</v>
       </c>
@@ -5807,7 +5777,7 @@
       </c>
       <c r="L2" s="14"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="14"/>
       <c r="B3" s="14" t="s">
         <v>63</v>
@@ -5824,7 +5794,7 @@
       <c r="K3" s="14"/>
       <c r="L3" s="14"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="14"/>
       <c r="B4" s="14" t="s">
         <v>45</v>
@@ -5858,7 +5828,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>77</v>
       </c>
@@ -5880,7 +5850,7 @@
       </c>
       <c r="L5" s="14"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
         <v>78</v>
       </c>
@@ -5906,7 +5876,7 @@
       </c>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
         <v>79</v>
       </c>
@@ -5932,7 +5902,7 @@
       </c>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
         <v>80</v>
       </c>
@@ -5954,7 +5924,7 @@
       </c>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
         <v>81</v>
       </c>
@@ -5980,7 +5950,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
         <v>82</v>
       </c>
@@ -6002,7 +5972,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
         <v>52</v>
       </c>
@@ -6024,7 +5994,7 @@
         <v>15540</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
         <v>53</v>
       </c>
@@ -6046,7 +6016,7 @@
       </c>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
         <v>83</v>
       </c>
@@ -6068,7 +6038,7 @@
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
         <v>84</v>
       </c>
@@ -6094,7 +6064,7 @@
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
         <v>85</v>
       </c>
@@ -6116,7 +6086,7 @@
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
         <v>86</v>
       </c>
@@ -6138,7 +6108,7 @@
       <c r="K16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
         <v>87</v>
       </c>
@@ -6160,7 +6130,7 @@
       <c r="K17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
         <v>88</v>
       </c>
@@ -6186,7 +6156,7 @@
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
         <v>89</v>
       </c>
@@ -6212,7 +6182,7 @@
       <c r="K19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
         <v>90</v>
       </c>
@@ -6238,7 +6208,7 @@
       <c r="K20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="14"/>
       <c r="B21" s="14">
         <v>206640</v>
@@ -6256,7 +6226,7 @@
       <c r="K21" s="14"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="s">
         <v>69</v>
       </c>
@@ -6280,7 +6250,7 @@
       <c r="K22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="14" t="s">
         <v>70</v>
       </c>
@@ -6304,7 +6274,7 @@
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="14" t="s">
         <v>71</v>
       </c>
@@ -6328,7 +6298,7 @@
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="14" t="s">
         <v>72</v>
       </c>
@@ -6352,7 +6322,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="14" t="s">
         <v>73</v>
       </c>
@@ -6376,7 +6346,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="14" t="s">
         <v>74</v>
       </c>
@@ -6400,7 +6370,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="14" t="s">
         <v>75</v>
       </c>
@@ -6424,7 +6394,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="14" t="s">
         <v>92</v>
       </c>
@@ -6448,7 +6418,7 @@
         <v>89305</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="14" t="s">
         <v>91</v>
       </c>
@@ -6468,7 +6438,7 @@
         <v>29555</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="14"/>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -6482,7 +6452,7 @@
       <c r="K31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="14" t="s">
         <v>68</v>
       </c>
@@ -6530,22 +6500,22 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F243036-475E-442E-9214-8F3E938FBBFF}">
   <dimension ref="A2:K39"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.73046875" customWidth="1"/>
-    <col min="2" max="2" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" customWidth="1"/>
-    <col min="8" max="8" width="12.53125" customWidth="1"/>
-    <col min="9" max="9" width="11.19921875" customWidth="1"/>
-    <col min="10" max="10" width="10.46484375" customWidth="1"/>
-    <col min="11" max="11" width="10.796875" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.5" customWidth="1"/>
+    <col min="9" max="9" width="11.1640625" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A2" s="32"/>
       <c r="B2" s="32" t="s">
         <v>130</v>
@@ -6568,7 +6538,7 @@
       </c>
       <c r="K2" s="32"/>
     </row>
-    <row r="3" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
         <v>76</v>
       </c>
@@ -6603,7 +6573,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
         <v>77</v>
       </c>
@@ -6624,7 +6594,7 @@
       </c>
       <c r="K4" s="32"/>
     </row>
-    <row r="5" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="5" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
         <v>95</v>
       </c>
@@ -6645,7 +6615,7 @@
       </c>
       <c r="K5" s="32"/>
     </row>
-    <row r="6" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="6" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
         <v>96</v>
       </c>
@@ -6666,7 +6636,7 @@
       </c>
       <c r="K6" s="32"/>
     </row>
-    <row r="7" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="7" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
         <v>78</v>
       </c>
@@ -6689,7 +6659,7 @@
       </c>
       <c r="K7" s="32"/>
     </row>
-    <row r="8" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="8" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
         <v>97</v>
       </c>
@@ -6710,7 +6680,7 @@
       </c>
       <c r="K8" s="32"/>
     </row>
-    <row r="9" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="9" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
         <v>98</v>
       </c>
@@ -6731,7 +6701,7 @@
       </c>
       <c r="K9" s="32"/>
     </row>
-    <row r="10" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="10" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
         <v>136</v>
       </c>
@@ -6754,7 +6724,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="11" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
         <v>80</v>
       </c>
@@ -6775,7 +6745,7 @@
       </c>
       <c r="K11" s="32"/>
     </row>
-    <row r="12" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="12" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
         <v>140</v>
       </c>
@@ -6798,7 +6768,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="13" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="32" t="s">
         <v>99</v>
       </c>
@@ -6819,7 +6789,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="14" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="32" t="s">
         <v>101</v>
       </c>
@@ -6840,7 +6810,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="15" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="32" t="s">
         <v>100</v>
       </c>
@@ -6863,7 +6833,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="16" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="32" t="s">
         <v>102</v>
       </c>
@@ -6884,7 +6854,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="32" t="s">
         <v>103</v>
       </c>
@@ -6905,7 +6875,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="18" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="32" t="s">
         <v>104</v>
       </c>
@@ -6926,7 +6896,7 @@
       </c>
       <c r="K18" s="32"/>
     </row>
-    <row r="19" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="19" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="32" t="s">
         <v>105</v>
       </c>
@@ -6949,7 +6919,7 @@
       <c r="J19" s="32"/>
       <c r="K19" s="32"/>
     </row>
-    <row r="20" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="20" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="32" t="s">
         <v>70</v>
       </c>
@@ -6972,7 +6942,7 @@
       <c r="J20" s="32"/>
       <c r="K20" s="32"/>
     </row>
-    <row r="21" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="32"/>
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
@@ -6985,7 +6955,7 @@
       <c r="J21" s="32"/>
       <c r="K21" s="32"/>
     </row>
-    <row r="22" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="22" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="32" t="s">
         <v>84</v>
       </c>
@@ -7008,7 +6978,7 @@
       <c r="J22" s="32"/>
       <c r="K22" s="32"/>
     </row>
-    <row r="23" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="23" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="32" t="s">
         <v>88</v>
       </c>
@@ -7029,7 +6999,7 @@
       <c r="J23" s="32"/>
       <c r="K23" s="32"/>
     </row>
-    <row r="24" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="24" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A24" s="32" t="s">
         <v>90</v>
       </c>
@@ -7052,7 +7022,7 @@
       <c r="J24" s="32"/>
       <c r="K24" s="32"/>
     </row>
-    <row r="25" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="25" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A25" s="32" t="s">
         <v>106</v>
       </c>
@@ -7075,7 +7045,7 @@
       <c r="J25" s="32"/>
       <c r="K25" s="32"/>
     </row>
-    <row r="26" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="26" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A26" s="32"/>
       <c r="D26" s="32"/>
       <c r="E26" s="32"/>
@@ -7086,7 +7056,7 @@
       <c r="J26" s="32"/>
       <c r="K26" s="32"/>
     </row>
-    <row r="27" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="27" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A27" s="32" t="s">
         <v>125</v>
       </c>
@@ -7107,7 +7077,7 @@
       <c r="J27" s="32"/>
       <c r="K27" s="32"/>
     </row>
-    <row r="28" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="28" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A28" s="32" t="s">
         <v>126</v>
       </c>
@@ -7128,7 +7098,7 @@
       <c r="J28" s="32"/>
       <c r="K28" s="32"/>
     </row>
-    <row r="29" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="29" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A29" s="32" t="s">
         <v>127</v>
       </c>
@@ -7149,7 +7119,7 @@
       <c r="J29" s="32"/>
       <c r="K29" s="32"/>
     </row>
-    <row r="30" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="30" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A30" s="32" t="s">
         <v>79</v>
       </c>
@@ -7170,7 +7140,7 @@
       </c>
       <c r="K30" s="32"/>
     </row>
-    <row r="31" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="31" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A31" s="32"/>
       <c r="B31" s="32"/>
       <c r="C31" s="32"/>
@@ -7183,7 +7153,7 @@
       <c r="J31" s="32"/>
       <c r="K31" s="32"/>
     </row>
-    <row r="32" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="32" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A32" s="32" t="s">
         <v>75</v>
       </c>
@@ -7204,7 +7174,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="33" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A33" s="32" t="s">
         <v>128</v>
       </c>
@@ -7225,7 +7195,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="34" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A34" s="32" t="s">
         <v>72</v>
       </c>
@@ -7246,7 +7216,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="35" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A35" s="32"/>
       <c r="B35" s="32"/>
       <c r="C35" s="32"/>
@@ -7263,7 +7233,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="36" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A36" s="32"/>
       <c r="B36" s="32"/>
       <c r="C36" s="32"/>
@@ -7276,7 +7246,7 @@
       <c r="J36" s="32"/>
       <c r="K36" s="32"/>
     </row>
-    <row r="37" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="37" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A37" s="32" t="s">
         <v>129</v>
       </c>
@@ -7295,7 +7265,7 @@
         <v>51315</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="38" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A38" s="32"/>
       <c r="B38" s="32"/>
       <c r="C38" s="32"/>
@@ -7308,7 +7278,7 @@
       <c r="J38" s="32"/>
       <c r="K38" s="32"/>
     </row>
-    <row r="39" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="39" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A39" s="32" t="s">
         <v>167</v>
       </c>

--- a/ACCY122/Session/S04/ACCY122 L4 Workbook.xlsx
+++ b/ACCY122/Session/S04/ACCY122 L4 Workbook.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onlym\Desktop\Manek\Notes\SIM\UOW\2026 UOW\Learning Material\In Session Explanation\L4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ACCY122\Session\S04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CA7FE1-7C79-4C7A-80B2-FF7C2E86C6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF30FBF8-C934-4FFC-9F92-76FF30587EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" activeTab="2" xr2:uid="{49300C88-9C68-40D1-BFDB-69B44FEEA068}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{49300C88-9C68-40D1-BFDB-69B44FEEA068}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="ANSWER" sheetId="4" r:id="rId6"/>
     <sheet name="5.1A" sheetId="8" r:id="rId7"/>
     <sheet name="P5.1 Answer" sheetId="5" r:id="rId8"/>
-    <sheet name="Sheet2" sheetId="7" r:id="rId9"/>
+    <sheet name="P5.5" sheetId="7" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="215">
   <si>
     <t>Balanced Day Adjustments</t>
   </si>
@@ -395,57 +395,6 @@
     <t>Telecommunications Expense</t>
   </si>
   <si>
-    <t>9 260</t>
-  </si>
-  <si>
-    <t>1 140</t>
-  </si>
-  <si>
-    <t>60 000</t>
-  </si>
-  <si>
-    <t>152 000</t>
-  </si>
-  <si>
-    <t>23 400</t>
-  </si>
-  <si>
-    <t>52 780</t>
-  </si>
-  <si>
-    <t>1 660</t>
-  </si>
-  <si>
-    <t>87 940</t>
-  </si>
-  <si>
-    <t>2 090</t>
-  </si>
-  <si>
-    <t>6 420</t>
-  </si>
-  <si>
-    <t>7 960</t>
-  </si>
-  <si>
-    <t>1 560</t>
-  </si>
-  <si>
-    <t>2 000</t>
-  </si>
-  <si>
-    <t>88 600</t>
-  </si>
-  <si>
-    <t>71 490</t>
-  </si>
-  <si>
-    <t>156 860</t>
-  </si>
-  <si>
-    <t>$398 890</t>
-  </si>
-  <si>
     <t>Problem 5.4</t>
   </si>
   <si>
@@ -464,120 +413,9 @@
     <t>Profit for the year</t>
   </si>
   <si>
-    <t>Unadjusted trial balance</t>
-  </si>
-  <si>
-    <t>Adjusted trial balance</t>
-  </si>
-  <si>
-    <t>Income statement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debit </t>
-  </si>
-  <si>
-    <t>5 200</t>
-  </si>
-  <si>
-    <t>(1)     720</t>
-  </si>
-  <si>
-    <t>Acc. Depr. Building</t>
-  </si>
-  <si>
-    <t>64 000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3)  8 760 </t>
-  </si>
-  <si>
-    <t>72 760</t>
-  </si>
-  <si>
-    <t>Acc. Depr. Office Equip.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3)  2 140 </t>
-  </si>
-  <si>
-    <t>8 560</t>
-  </si>
-  <si>
-    <t>(2)  1 200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2)  1 200 </t>
-  </si>
-  <si>
-    <t>158 060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4)    585  </t>
-  </si>
-  <si>
-    <t>(7)    980</t>
-  </si>
-  <si>
-    <t>88 920</t>
-  </si>
-  <si>
-    <t>(5)   220</t>
-  </si>
-  <si>
-    <t>2 310</t>
-  </si>
-  <si>
-    <t>1 740</t>
-  </si>
-  <si>
-    <t>(6)    320</t>
-  </si>
-  <si>
     <t>2 060</t>
   </si>
   <si>
-    <t xml:space="preserve">(1)     720 </t>
-  </si>
-  <si>
-    <t>(3)  8 760</t>
-  </si>
-  <si>
-    <t>8 760</t>
-  </si>
-  <si>
-    <t>(3)  2 140</t>
-  </si>
-  <si>
-    <t>2 140</t>
-  </si>
-  <si>
-    <t>(4)585    195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5)   220 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6)    320 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7)    980 </t>
-  </si>
-  <si>
-    <t>14 925</t>
-  </si>
-  <si>
-    <t>411 310</t>
-  </si>
-  <si>
-    <t>304 565</t>
-  </si>
-  <si>
-    <t>253 250</t>
-  </si>
-  <si>
-    <t>Totals</t>
-  </si>
-  <si>
     <t>BS, IS</t>
   </si>
   <si>
@@ -768,13 +606,158 @@
   </si>
   <si>
     <t>Int Payable</t>
+  </si>
+  <si>
+    <t>Practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRACTICE </t>
+  </si>
+  <si>
+    <t>ref 6</t>
+  </si>
+  <si>
+    <t>Acc. Depn – Building</t>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Acc. Depr. – Equipment</t>
+  </si>
+  <si>
+    <t>P. Oodle, Capital</t>
+  </si>
+  <si>
+    <t>P. Oodle, Drawings</t>
+  </si>
+  <si>
+    <t>Fees Earned</t>
+  </si>
+  <si>
+    <t>Rent Revenue</t>
+  </si>
+  <si>
+    <t>Depr. Exp – Building</t>
+  </si>
+  <si>
+    <t>Depr. Exp. – Equipment</t>
+  </si>
+  <si>
+    <t>Rates Payable</t>
+  </si>
+  <si>
+    <t>Unearned Fees</t>
+  </si>
+  <si>
+    <t>Rates Expense</t>
+  </si>
+  <si>
+    <t>4)</t>
+  </si>
+  <si>
+    <t>6)</t>
+  </si>
+  <si>
+    <t>5)</t>
+  </si>
+  <si>
+    <t>2)</t>
+  </si>
+  <si>
+    <t>REF</t>
+  </si>
+  <si>
+    <t>3)</t>
+  </si>
+  <si>
+    <t>1)</t>
+  </si>
+  <si>
+    <t>ref 3 - the service has not yet been provided at the time of receiving the payment</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">it cannot be recorded as “Fees Earned” yet, it is recorded as a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>liability</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> called </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>unearned fees</t>
+    </r>
+  </si>
+  <si>
+    <t>ref 4 - there is nothing to adjust for the princiapl since it hasnt been paid only if it says it is paid but not recorded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Mortgage Payable  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cr Cash  </t>
+  </si>
+  <si>
+    <t>and if such scenario then additional</t>
+  </si>
+  <si>
+    <t>Income Statement</t>
+  </si>
+  <si>
+    <t>We still need to record the expense because it belongs to June.</t>
+  </si>
+  <si>
+    <t>Expense ($320 telecommunications) has been incurred in June</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr Teleco Expense     320  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Cr Telco Expenses Payable    320  </t>
+  </si>
+  <si>
+    <t>Used but not billed → Accrued expense</t>
+  </si>
+  <si>
+    <t>Paid but not used → Unearned (prepaid)</t>
+  </si>
+  <si>
+    <t>ref 5</t>
+  </si>
+  <si>
+    <t>there is nothing to adjust for the princiapl since it hasnt been paid only if it says it is paid but not recorded</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -838,8 +821,57 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -894,8 +926,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1173,11 +1223,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1319,9 +1423,6 @@
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1329,7 +1430,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1338,7 +1438,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1351,9 +1451,60 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1399,8 +1550,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1065254" y="634714"/>
-          <a:ext cx="5737589" cy="5657269"/>
+          <a:off x="1029211" y="656694"/>
+          <a:ext cx="5413202" cy="5884404"/>
           <a:chOff x="0" y="78429"/>
           <a:chExt cx="6059328" cy="3928254"/>
         </a:xfrm>
@@ -1960,22 +2111,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>109681</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>132772</xdr:rowOff>
+      <xdr:colOff>798480</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>19381</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>246097</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>132773</xdr:rowOff>
+      <xdr:colOff>611934</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>95196</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="6" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B85E5104-87CA-950D-541D-34B590E55AA9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09DA030C-AAED-BE23-2336-27E9395962FC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1998,8 +2149,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="109681" y="6055590"/>
-          <a:ext cx="5752523" cy="1293091"/>
+          <a:off x="798480" y="8106106"/>
+          <a:ext cx="7242954" cy="1790315"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2020,23 +2171,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>93630</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>76531</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>173784</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>152346</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1804179</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>18665</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09DA030C-AAED-BE23-2336-27E9395962FC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47E07067-D395-4EF8-8AB9-E2C88D324AFB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2045,7 +2196,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -2059,8 +2210,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6482707" y="7183646"/>
-          <a:ext cx="7736789" cy="1724374"/>
+          <a:off x="0" y="17983200"/>
+          <a:ext cx="7242954" cy="1790315"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2086,16 +2237,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>248150</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>574722</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>175069</xdr:rowOff>
+      <xdr:rowOff>202284</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>56754</xdr:colOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>192825</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>61977</xdr:rowOff>
+      <xdr:rowOff>89192</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2125,8 +2276,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7242221" y="1658248"/>
-          <a:ext cx="8034123" cy="2200122"/>
+          <a:off x="11827829" y="1794320"/>
+          <a:ext cx="7578282" cy="2336193"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2141,6 +2292,61 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>543966</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>85986</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5D3DD1C-C00D-A946-D70B-40F791ECAD0E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="8496300"/>
+          <a:ext cx="7459116" cy="1867161"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2484,7 +2690,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3154719-4B7A-4BD1-A273-F4DC249F84D4}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2494,27 +2700,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F923618A-53E6-4AA0-84BA-AB41705F9398}">
   <dimension ref="B1:O20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="18.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.46484375" customWidth="1"/>
-    <col min="7" max="7" width="10.46484375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.06640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.46484375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F3" t="s">
         <v>2</v>
       </c>
@@ -2531,7 +2737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2549,7 +2755,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="2" t="s">
@@ -2563,8 +2769,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="C6" s="71" t="s">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C6" s="109" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="1"/>
@@ -2591,8 +2797,8 @@
       </c>
       <c r="O6" s="7"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="C7" s="71"/>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C7" s="109"/>
       <c r="D7" s="1"/>
       <c r="E7" s="2" t="s">
         <v>11</v>
@@ -2604,8 +2810,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="C8" s="71"/>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C8" s="109"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
         <v>21</v>
@@ -2618,8 +2824,8 @@
       </c>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="C9" s="71"/>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C9" s="109"/>
       <c r="D9" s="1"/>
       <c r="E9" s="2" t="s">
         <v>11</v>
@@ -2627,8 +2833,8 @@
       <c r="M9" s="6"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="C10" s="71"/>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C10" s="109"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
         <v>23</v>
@@ -2656,7 +2862,7 @@
       </c>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" spans="2:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -2676,7 +2882,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="2" t="s">
@@ -2686,14 +2892,14 @@
         <v>11</v>
       </c>
       <c r="H12" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>31</v>
       </c>
       <c r="O12" s="7"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
         <v>32</v>
       </c>
@@ -2710,9 +2916,9 @@
       <c r="M13" s="6"/>
       <c r="O13" s="7"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="K14">
         <v>3</v>
@@ -2728,7 +2934,7 @@
       </c>
       <c r="O14" s="7"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="M15" s="6" t="s">
         <v>36</v>
       </c>
@@ -2736,17 +2942,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="M16" s="6" t="s">
         <v>37</v>
       </c>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="11:15" x14ac:dyDescent="0.45">
+    <row r="17" spans="11:15" x14ac:dyDescent="0.25">
       <c r="M17" s="6"/>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" spans="11:15" x14ac:dyDescent="0.45">
+    <row r="18" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K18">
         <v>4</v>
       </c>
@@ -2761,7 +2967,7 @@
       </c>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" spans="11:15" x14ac:dyDescent="0.45">
+    <row r="19" spans="11:15" x14ac:dyDescent="0.25">
       <c r="M19" s="6" t="s">
         <v>40</v>
       </c>
@@ -2769,7 +2975,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="11:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="20" spans="11:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M20" s="11" t="s">
         <v>41</v>
       </c>
@@ -2790,13 +2996,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC50BE0-433C-401E-8C60-EBD47C86025A}">
   <dimension ref="A1:M35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="18.1328125" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B1" s="3"/>
       <c r="C1" s="4" t="s">
         <v>15</v>
@@ -2804,31 +3010,31 @@
       <c r="D1" s="4"/>
       <c r="E1" s="5"/>
       <c r="H1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>93</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C2" s="75" t="s">
-        <v>181</v>
-      </c>
-      <c r="D2" s="75" t="s">
-        <v>191</v>
+        <v>126</v>
+      </c>
+      <c r="C2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" t="s">
+        <v>137</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="74">
+      <c r="B3" s="73">
         <v>46387</v>
       </c>
       <c r="C3" s="4"/>
@@ -2838,16 +3044,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="6"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
       <c r="E4" s="7"/>
-      <c r="G4" s="73" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G4" s="72" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -2856,308 +3060,284 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="6"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
-      <c r="B7" s="74">
+      <c r="B7" s="73">
         <v>46387</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="5"/>
-      <c r="G7" s="73">
+      <c r="G7" s="72">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="6"/>
-      <c r="C8" s="75"/>
-      <c r="D8" s="75"/>
       <c r="E8" s="7"/>
-      <c r="G8" s="73" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G8" s="72" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="11"/>
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
       <c r="E9" s="13"/>
-      <c r="G9" s="73">
+      <c r="G9" s="72">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
       <c r="E10" s="7"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>3</v>
       </c>
-      <c r="B11" s="74">
+      <c r="B11" s="73">
         <v>46387</v>
       </c>
-      <c r="C11" s="86"/>
+      <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="5"/>
-      <c r="G11" s="73">
+      <c r="G11" s="72">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="6"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="75"/>
       <c r="E12" s="7"/>
-      <c r="G12" s="73" t="s">
-        <v>197</v>
-      </c>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-    </row>
-    <row r="13" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G12" s="72" t="s">
+        <v>143</v>
+      </c>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="11"/>
-      <c r="C13" s="87"/>
+      <c r="C13" s="12"/>
       <c r="D13" s="12"/>
       <c r="E13" s="13"/>
-      <c r="G13" s="73">
+      <c r="G13" s="72">
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="6"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
       <c r="E14" s="7"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>4</v>
       </c>
-      <c r="B15" s="74">
+      <c r="B15" s="73">
         <v>46387</v>
       </c>
-      <c r="C15" s="86"/>
+      <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="5"/>
-      <c r="G15" s="73">
+      <c r="G15" s="72">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
-      <c r="C16" s="85"/>
-      <c r="D16" s="75"/>
       <c r="E16" s="7"/>
-      <c r="G16" s="73" t="s">
-        <v>197</v>
-      </c>
-      <c r="H16" s="72"/>
-      <c r="I16" s="72"/>
-    </row>
-    <row r="17" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G16" s="72" t="s">
+        <v>143</v>
+      </c>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="11"/>
-      <c r="C17" s="87"/>
+      <c r="C17" s="12"/>
       <c r="D17" s="12"/>
       <c r="E17" s="13"/>
-      <c r="G17" s="73">
+      <c r="G17" s="72">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="6"/>
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
       <c r="E18" s="7"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>5</v>
       </c>
-      <c r="B19" s="74">
+      <c r="B19" s="73">
         <v>46387</v>
       </c>
-      <c r="C19" s="85"/>
-      <c r="D19" s="75"/>
       <c r="E19" s="7"/>
-      <c r="G19" s="73">
+      <c r="G19" s="72">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B20" s="6"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="75"/>
       <c r="E20" s="7"/>
-      <c r="G20" s="73" t="s">
-        <v>197</v>
-      </c>
-      <c r="H20" s="72"/>
-      <c r="I20" s="72"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="G20" s="72" t="s">
+        <v>143</v>
+      </c>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B21" s="6"/>
-      <c r="C21" s="85"/>
-      <c r="D21" s="75"/>
       <c r="E21" s="7"/>
-      <c r="G21" s="73">
+      <c r="G21" s="72">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="11"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
       <c r="E22" s="13"/>
     </row>
-    <row r="23" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>6</v>
       </c>
-      <c r="B24" s="74">
+      <c r="B24" s="73">
         <v>46387</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="5"/>
-      <c r="G24" s="73">
+      <c r="G24" s="72">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B25" s="6"/>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
       <c r="E25" s="7"/>
-      <c r="G25" s="73" t="s">
-        <v>197</v>
-      </c>
-      <c r="H25" s="72"/>
-      <c r="I25" s="72"/>
-    </row>
-    <row r="26" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G25" s="72" t="s">
+        <v>143</v>
+      </c>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="11"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
       <c r="E26" s="13"/>
-      <c r="G26" s="73">
+      <c r="G26" s="72">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="28" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>7</v>
       </c>
-      <c r="B28" s="74">
+      <c r="B28" s="73">
         <v>46387</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="5"/>
-      <c r="G28" s="73">
+      <c r="G28" s="72">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B29" s="6"/>
-      <c r="C29" s="75"/>
-      <c r="D29" s="75"/>
       <c r="E29" s="4"/>
-      <c r="G29" s="73" t="s">
-        <v>197</v>
-      </c>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72"/>
-    </row>
-    <row r="30" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G29" s="72" t="s">
+        <v>143</v>
+      </c>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="11"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
       <c r="E30" s="13"/>
-      <c r="G30" s="73">
+      <c r="G30" s="72">
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>193</v>
+        <v>139</v>
       </c>
       <c r="I32" t="s">
-        <v>192</v>
-      </c>
-      <c r="K32" s="76"/>
-      <c r="L32" s="77" t="s">
+        <v>138</v>
+      </c>
+      <c r="K32" s="74"/>
+      <c r="L32" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="M32" s="78" t="s">
+      <c r="M32" s="76" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="7:13" x14ac:dyDescent="0.45">
+    <row r="33" spans="7:13" x14ac:dyDescent="0.25">
       <c r="G33">
         <v>2</v>
       </c>
       <c r="H33" t="s">
-        <v>194</v>
+        <v>140</v>
       </c>
       <c r="I33" t="s">
-        <v>194</v>
-      </c>
-      <c r="K33" s="79" t="s">
-        <v>202</v>
-      </c>
-      <c r="L33" s="80" t="s">
-        <v>204</v>
-      </c>
-      <c r="M33" s="81" t="s">
+        <v>140</v>
+      </c>
+      <c r="K33" s="77" t="s">
+        <v>148</v>
+      </c>
+      <c r="L33" s="78" t="s">
+        <v>150</v>
+      </c>
+      <c r="M33" s="79" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="7:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="34" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G34">
         <v>3</v>
       </c>
-      <c r="H34" s="72" t="s">
-        <v>196</v>
-      </c>
-      <c r="I34" s="72" t="s">
-        <v>196</v>
-      </c>
-      <c r="K34" s="82" t="s">
-        <v>203</v>
-      </c>
-      <c r="L34" s="83" t="s">
+      <c r="H34" s="71" t="s">
+        <v>142</v>
+      </c>
+      <c r="I34" s="71" t="s">
+        <v>142</v>
+      </c>
+      <c r="K34" s="80" t="s">
+        <v>149</v>
+      </c>
+      <c r="L34" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="M34" s="84" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="35" spans="7:13" x14ac:dyDescent="0.45">
+      <c r="M34" s="82" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="7:13" x14ac:dyDescent="0.25">
       <c r="G35">
         <v>4</v>
       </c>
       <c r="H35" t="s">
-        <v>195</v>
+        <v>141</v>
       </c>
       <c r="I35" t="s">
-        <v>195</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -3167,33 +3347,35 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{431369FE-F92F-4C37-9408-0538561CEBA7}">
-  <dimension ref="A1:U32"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:U74"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.53125" customWidth="1"/>
-    <col min="2" max="2" width="6.73046875" customWidth="1"/>
-    <col min="3" max="4" width="8.73046875" customWidth="1"/>
-    <col min="5" max="5" width="4.33203125" customWidth="1"/>
-    <col min="6" max="7" width="8.73046875" customWidth="1"/>
-    <col min="8" max="8" width="2.73046875" customWidth="1"/>
-    <col min="9" max="9" width="9.19921875" customWidth="1"/>
-    <col min="10" max="10" width="9.73046875" customWidth="1"/>
-    <col min="11" max="11" width="2.59765625" customWidth="1"/>
-    <col min="12" max="12" width="10.06640625" customWidth="1"/>
-    <col min="13" max="13" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="2.33203125" customWidth="1"/>
+    <col min="1" max="1" width="31.5703125" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="27.140625" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="19" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" customWidth="1"/>
+    <col min="14" max="14" width="2.28515625" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="11.53125" customWidth="1"/>
-    <col min="18" max="18" width="13.265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.53125" customWidth="1"/>
-    <col min="20" max="21" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" customWidth="1"/>
+    <col min="18" max="18" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.5703125" customWidth="1"/>
+    <col min="20" max="21" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
       <c r="B1" s="14"/>
     </row>
-    <row r="2" spans="1:21" ht="14.55" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:21" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>42</v>
       </c>
@@ -3206,7 +3388,7 @@
       </c>
       <c r="E2" s="35"/>
       <c r="F2" s="36" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="G2" s="37"/>
       <c r="H2" s="38"/>
@@ -3229,7 +3411,7 @@
       </c>
       <c r="P2" s="40"/>
     </row>
-    <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
         <v>43</v>
       </c>
@@ -3251,7 +3433,7 @@
       <c r="O3" s="47"/>
       <c r="P3" s="45"/>
     </row>
-    <row r="4" spans="1:21" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>44</v>
       </c>
@@ -3294,12 +3476,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="5" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A5" s="27" t="s">
         <v>47</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="C5" s="50">
         <v>6200</v>
@@ -3323,24 +3505,24 @@
       </c>
       <c r="P5" s="53"/>
       <c r="R5" s="60" t="s">
-        <v>180</v>
+        <v>126</v>
       </c>
       <c r="S5" s="61" t="s">
-        <v>181</v>
+        <v>127</v>
       </c>
       <c r="T5" s="61" t="s">
-        <v>182</v>
+        <v>128</v>
       </c>
       <c r="U5" s="62" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A6" s="27" t="s">
         <v>48</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="C6" s="50">
         <v>7260</v>
@@ -3368,7 +3550,7 @@
       </c>
       <c r="P6" s="53"/>
       <c r="R6" s="24" t="s">
-        <v>184</v>
+        <v>130</v>
       </c>
       <c r="S6" s="24" t="s">
         <v>18</v>
@@ -3379,12 +3561,12 @@
       </c>
       <c r="U6" s="63"/>
     </row>
-    <row r="7" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="7" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A7" s="27" t="s">
         <v>49</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="C7" s="50">
         <v>1725</v>
@@ -3421,12 +3603,12 @@
         <v>126500</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="8" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="27" t="s">
         <v>50</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="C8" s="50">
         <v>82800</v>
@@ -3456,12 +3638,12 @@
       <c r="T8" s="65"/>
       <c r="U8" s="66"/>
     </row>
-    <row r="9" spans="1:21" ht="31.9" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="9" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="27" t="s">
         <v>51</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>176</v>
+        <v>122</v>
       </c>
       <c r="C9" s="50"/>
       <c r="D9" s="50">
@@ -3493,12 +3675,12 @@
       <c r="T9" s="32"/>
       <c r="U9" s="32"/>
     </row>
-    <row r="10" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="10" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A10" s="27" t="s">
-        <v>177</v>
+        <v>123</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="C10" s="50"/>
       <c r="D10" s="50">
@@ -3522,7 +3704,7 @@
         <v>50000</v>
       </c>
       <c r="R10" s="60" t="s">
-        <v>184</v>
+        <v>130</v>
       </c>
       <c r="S10" s="61" t="s">
         <v>20</v>
@@ -3533,12 +3715,12 @@
       </c>
       <c r="U10" s="62"/>
     </row>
-    <row r="11" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="11" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A11" s="27" t="s">
         <v>52</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="C11" s="50"/>
       <c r="D11" s="50">
@@ -3570,12 +3752,12 @@
         <v>63510</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="12" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A12" s="27" t="s">
         <v>53</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="C12" s="50">
         <v>27000</v>
@@ -3607,12 +3789,12 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="13" spans="1:21" ht="30" x14ac:dyDescent="0.4">
       <c r="A13" s="27" t="s">
         <v>54</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>172</v>
+        <v>118</v>
       </c>
       <c r="C13" s="50"/>
       <c r="D13" s="50">
@@ -3644,12 +3826,12 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="14" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A14" s="27" t="s">
         <v>55</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="C14" s="50">
         <v>63250</v>
@@ -3685,12 +3867,12 @@
         <v>7520</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="15" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A15" s="27" t="s">
         <v>56</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="C15" s="50">
         <v>2250</v>
@@ -3722,12 +3904,12 @@
         <v>4235</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="16" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A16" s="27" t="s">
         <v>57</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="C16" s="50">
         <v>1260</v>
@@ -3759,12 +3941,12 @@
         <v>3045</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="17" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A17" s="27" t="s">
         <v>58</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="C17" s="50">
         <v>7520</v>
@@ -3789,19 +3971,19 @@
       <c r="P17" s="53"/>
       <c r="R17" s="24"/>
       <c r="S17" s="27" t="s">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="T17" s="28"/>
       <c r="U17" s="67">
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="18" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A18" s="27" t="s">
         <v>59</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="C18" s="50">
         <v>3405</v>
@@ -3837,12 +4019,12 @@
         <v>4940</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="19" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A19" s="27" t="s">
         <v>60</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="C19" s="50">
         <v>2620</v>
@@ -3878,12 +4060,12 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="20" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="27" t="s">
         <v>61</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="C20" s="50">
         <v>1350</v>
@@ -3921,7 +4103,7 @@
         <v>7400</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="21" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="27"/>
       <c r="B21" s="28"/>
       <c r="C21" s="15"/>
@@ -3943,12 +4125,12 @@
       <c r="T21" s="32"/>
       <c r="U21" s="32"/>
     </row>
-    <row r="22" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="22" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A22" s="30" t="s">
         <v>69</v>
       </c>
       <c r="B22" s="31" t="s">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
@@ -3974,7 +4156,7 @@
       <c r="O22" s="52"/>
       <c r="P22" s="53"/>
       <c r="R22" s="60" t="s">
-        <v>184</v>
+        <v>130</v>
       </c>
       <c r="S22" s="61" t="str">
         <f>S10</f>
@@ -3986,12 +4168,12 @@
       </c>
       <c r="U22" s="62"/>
     </row>
-    <row r="23" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="23" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A23" s="30" t="s">
         <v>70</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="15"/>
@@ -4018,7 +4200,7 @@
       <c r="P23" s="53"/>
       <c r="R23" s="24"/>
       <c r="S23" s="59" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
       <c r="T23" s="32"/>
       <c r="U23" s="63">
@@ -4026,12 +4208,12 @@
         <v>29555</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="24" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="30" t="s">
         <v>71</v>
       </c>
       <c r="B24" s="31" t="s">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="15"/>
@@ -4058,17 +4240,17 @@
       <c r="P24" s="53"/>
       <c r="R24" s="64"/>
       <c r="S24" s="65" t="s">
-        <v>186</v>
+        <v>132</v>
       </c>
       <c r="T24" s="65"/>
       <c r="U24" s="66"/>
     </row>
-    <row r="25" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="25" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="30" t="s">
         <v>72</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
@@ -4098,12 +4280,12 @@
       <c r="T25" s="32"/>
       <c r="U25" s="32"/>
     </row>
-    <row r="26" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="26" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A26" s="30" t="s">
         <v>73</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
@@ -4129,7 +4311,7 @@
         <v>830</v>
       </c>
       <c r="R26" s="60" t="s">
-        <v>184</v>
+        <v>130</v>
       </c>
       <c r="S26" s="61" t="s">
         <v>39</v>
@@ -4139,12 +4321,12 @@
       </c>
       <c r="U26" s="62"/>
     </row>
-    <row r="27" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="27" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A27" s="30" t="s">
         <v>74</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
@@ -4179,12 +4361,12 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="28" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="30" t="s">
         <v>75</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
@@ -4211,14 +4393,14 @@
       </c>
       <c r="R28" s="11"/>
       <c r="S28" s="65" t="s">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="T28" s="12"/>
       <c r="U28" s="13"/>
     </row>
-    <row r="29" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="29" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A29" s="15" t="s">
-        <v>179</v>
+        <v>125</v>
       </c>
       <c r="B29" s="29"/>
       <c r="C29" s="15"/>
@@ -4241,7 +4423,7 @@
         <v>29555</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="16.899999999999999" x14ac:dyDescent="0.65">
+    <row r="30" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A30" s="32"/>
       <c r="B30" s="29"/>
       <c r="C30" s="15"/>
@@ -4259,7 +4441,7 @@
       <c r="O30" s="52"/>
       <c r="P30" s="53"/>
     </row>
-    <row r="31" spans="1:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="31" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="15" t="s">
         <v>68</v>
       </c>
@@ -4309,43 +4491,970 @@
         <v>118860</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="L32">
         <f>M31-L31</f>
         <v>0</v>
       </c>
     </row>
+    <row r="44" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="85" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="23"/>
+      <c r="C45" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="E45" s="35"/>
+      <c r="F45" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="G45" s="37"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J45" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="K45" s="38"/>
+      <c r="L45" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="M45" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="N45" s="41"/>
+      <c r="O45" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="P45" s="40"/>
+    </row>
+    <row r="46" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A46" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="23"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="F46" s="42"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="44"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="19"/>
+      <c r="K46" s="44"/>
+      <c r="L46" s="24"/>
+      <c r="M46" s="45"/>
+      <c r="N46" s="46"/>
+      <c r="O46" s="47"/>
+      <c r="P46" s="45"/>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" s="26"/>
+      <c r="C47" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E47" s="35"/>
+      <c r="F47" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="G47" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="H47" s="35"/>
+      <c r="I47" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="J47" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="K47" s="46"/>
+      <c r="L47" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="M47" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="N47" s="35"/>
+      <c r="O47" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="P47" s="49" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A48" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="50">
+        <v>6200</v>
+      </c>
+      <c r="D48" s="50"/>
+      <c r="E48" s="51"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="53"/>
+      <c r="H48" s="29"/>
+      <c r="I48" s="15">
+        <f>C48+F48-G48</f>
+        <v>6200</v>
+      </c>
+      <c r="J48" s="15"/>
+      <c r="K48" s="29"/>
+      <c r="L48" s="52"/>
+      <c r="M48" s="53"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="52">
+        <v>6200</v>
+      </c>
+      <c r="P48" s="53"/>
+    </row>
+    <row r="49" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A49" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="50">
+        <v>7260</v>
+      </c>
+      <c r="D49" s="50"/>
+      <c r="E49" s="51">
+        <v>1</v>
+      </c>
+      <c r="F49" s="52"/>
+      <c r="G49" s="83">
+        <v>4940</v>
+      </c>
+      <c r="H49" s="29"/>
+      <c r="I49" s="15">
+        <f t="shared" ref="I49:I51" si="5">C49+F49-G49</f>
+        <v>2320</v>
+      </c>
+      <c r="J49" s="15"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="52"/>
+      <c r="M49" s="53"/>
+      <c r="N49" s="29"/>
+      <c r="O49" s="52">
+        <v>2320</v>
+      </c>
+      <c r="P49" s="53"/>
+    </row>
+    <row r="50" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A50" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50" s="50">
+        <v>1725</v>
+      </c>
+      <c r="D50" s="50"/>
+      <c r="E50" s="51">
+        <v>2</v>
+      </c>
+      <c r="F50" s="52"/>
+      <c r="G50" s="83">
+        <v>1185</v>
+      </c>
+      <c r="H50" s="29"/>
+      <c r="I50" s="15">
+        <f t="shared" si="5"/>
+        <v>540</v>
+      </c>
+      <c r="J50" s="15"/>
+      <c r="K50" s="29"/>
+      <c r="L50" s="52"/>
+      <c r="M50" s="53"/>
+      <c r="N50" s="29"/>
+      <c r="O50" s="52">
+        <v>540</v>
+      </c>
+      <c r="P50" s="53"/>
+    </row>
+    <row r="51" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A51" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="50">
+        <v>82800</v>
+      </c>
+      <c r="D51" s="50"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="15">
+        <f t="shared" si="5"/>
+        <v>82800</v>
+      </c>
+      <c r="J51" s="15"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="52"/>
+      <c r="M51" s="53"/>
+      <c r="N51" s="29"/>
+      <c r="O51" s="52">
+        <v>82800</v>
+      </c>
+      <c r="P51" s="53"/>
+    </row>
+    <row r="52" spans="1:16" ht="30" x14ac:dyDescent="0.4">
+      <c r="A52" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="C52" s="50"/>
+      <c r="D52" s="50">
+        <v>14600</v>
+      </c>
+      <c r="E52" s="51">
+        <v>3</v>
+      </c>
+      <c r="F52" s="52"/>
+      <c r="G52" s="83">
+        <v>7400</v>
+      </c>
+      <c r="H52" s="29"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15">
+        <f>D52-F52+G52</f>
+        <v>22000</v>
+      </c>
+      <c r="K52" s="29"/>
+      <c r="L52" s="52"/>
+      <c r="M52" s="53"/>
+      <c r="N52" s="29"/>
+      <c r="O52" s="52"/>
+      <c r="P52" s="53">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A53" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="B53" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C53" s="50"/>
+      <c r="D53" s="50">
+        <v>50000</v>
+      </c>
+      <c r="E53" s="51"/>
+      <c r="F53" s="52"/>
+      <c r="G53" s="53"/>
+      <c r="H53" s="29"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15">
+        <f t="shared" ref="J53:J54" si="6">D53-F53+G53</f>
+        <v>50000</v>
+      </c>
+      <c r="K53" s="29"/>
+      <c r="L53" s="52"/>
+      <c r="M53" s="53"/>
+      <c r="N53" s="29"/>
+      <c r="O53" s="52"/>
+      <c r="P53" s="53">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A54" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="50"/>
+      <c r="D54" s="50">
+        <v>15540</v>
+      </c>
+      <c r="E54" s="51"/>
+      <c r="F54" s="52"/>
+      <c r="G54" s="53"/>
+      <c r="H54" s="29"/>
+      <c r="I54" s="15"/>
+      <c r="J54" s="15">
+        <f t="shared" si="6"/>
+        <v>15540</v>
+      </c>
+      <c r="K54" s="29"/>
+      <c r="L54" s="52"/>
+      <c r="M54" s="53"/>
+      <c r="N54" s="29"/>
+      <c r="O54" s="52"/>
+      <c r="P54" s="53">
+        <v>15540</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A55" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C55" s="50">
+        <v>27000</v>
+      </c>
+      <c r="D55" s="50"/>
+      <c r="E55" s="51"/>
+      <c r="F55" s="52"/>
+      <c r="G55" s="53"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="15">
+        <f>C55+F55-G55</f>
+        <v>27000</v>
+      </c>
+      <c r="J55" s="15"/>
+      <c r="K55" s="29"/>
+      <c r="L55" s="52"/>
+      <c r="M55" s="53"/>
+      <c r="N55" s="29"/>
+      <c r="O55" s="52">
+        <v>27000</v>
+      </c>
+      <c r="P55" s="53"/>
+    </row>
+    <row r="56" spans="1:16" ht="30" x14ac:dyDescent="0.4">
+      <c r="A56" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="C56" s="50"/>
+      <c r="D56" s="50">
+        <v>126500</v>
+      </c>
+      <c r="E56" s="51"/>
+      <c r="F56" s="52"/>
+      <c r="G56" s="53"/>
+      <c r="H56" s="29"/>
+      <c r="I56" s="15"/>
+      <c r="J56" s="15">
+        <f>D56-F56+G56</f>
+        <v>126500</v>
+      </c>
+      <c r="K56" s="29"/>
+      <c r="L56" s="52"/>
+      <c r="M56" s="34">
+        <v>126500</v>
+      </c>
+      <c r="N56" s="29"/>
+      <c r="O56" s="52"/>
+      <c r="P56" s="53"/>
+    </row>
+    <row r="57" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A57" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C57" s="50">
+        <v>63250</v>
+      </c>
+      <c r="D57" s="50"/>
+      <c r="E57" s="51">
+        <v>4</v>
+      </c>
+      <c r="F57" s="84">
+        <v>260</v>
+      </c>
+      <c r="G57" s="53"/>
+      <c r="H57" s="29"/>
+      <c r="I57" s="15">
+        <f>C57+F57-G57</f>
+        <v>63510</v>
+      </c>
+      <c r="J57" s="15"/>
+      <c r="K57" s="29"/>
+      <c r="L57" s="57">
+        <v>63510</v>
+      </c>
+      <c r="M57" s="53"/>
+      <c r="N57" s="29"/>
+      <c r="O57" s="52"/>
+      <c r="P57" s="53"/>
+    </row>
+    <row r="58" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A58" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C58" s="50">
+        <v>2250</v>
+      </c>
+      <c r="D58" s="50"/>
+      <c r="E58" s="51"/>
+      <c r="F58" s="52"/>
+      <c r="G58" s="53"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="15">
+        <f t="shared" ref="I58:I63" si="7">C58+F58-G58</f>
+        <v>2250</v>
+      </c>
+      <c r="J58" s="15"/>
+      <c r="K58" s="29"/>
+      <c r="L58" s="57">
+        <v>2250</v>
+      </c>
+      <c r="M58" s="53"/>
+      <c r="N58" s="29"/>
+      <c r="O58" s="52"/>
+      <c r="P58" s="53"/>
+    </row>
+    <row r="59" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A59" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C59" s="50">
+        <v>1260</v>
+      </c>
+      <c r="D59" s="50"/>
+      <c r="E59" s="51"/>
+      <c r="F59" s="52"/>
+      <c r="G59" s="53"/>
+      <c r="H59" s="29"/>
+      <c r="I59" s="15">
+        <f t="shared" si="7"/>
+        <v>1260</v>
+      </c>
+      <c r="J59" s="15"/>
+      <c r="K59" s="29"/>
+      <c r="L59" s="57">
+        <v>1260</v>
+      </c>
+      <c r="M59" s="53"/>
+      <c r="N59" s="29"/>
+      <c r="O59" s="52"/>
+      <c r="P59" s="53"/>
+    </row>
+    <row r="60" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A60" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C60" s="50">
+        <v>7520</v>
+      </c>
+      <c r="D60" s="50"/>
+      <c r="E60" s="51"/>
+      <c r="F60" s="52"/>
+      <c r="G60" s="53"/>
+      <c r="H60" s="29"/>
+      <c r="I60" s="15">
+        <f t="shared" si="7"/>
+        <v>7520</v>
+      </c>
+      <c r="J60" s="15"/>
+      <c r="K60" s="29"/>
+      <c r="L60" s="57">
+        <v>7520</v>
+      </c>
+      <c r="M60" s="53"/>
+      <c r="N60" s="29"/>
+      <c r="O60" s="52"/>
+      <c r="P60" s="53"/>
+    </row>
+    <row r="61" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A61" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C61" s="50">
+        <v>3405</v>
+      </c>
+      <c r="D61" s="50"/>
+      <c r="E61" s="51">
+        <v>5</v>
+      </c>
+      <c r="F61" s="84">
+        <v>830</v>
+      </c>
+      <c r="G61" s="53"/>
+      <c r="H61" s="29"/>
+      <c r="I61" s="15">
+        <f t="shared" si="7"/>
+        <v>4235</v>
+      </c>
+      <c r="J61" s="15"/>
+      <c r="K61" s="29"/>
+      <c r="L61" s="57">
+        <v>4235</v>
+      </c>
+      <c r="M61" s="53"/>
+      <c r="N61" s="29"/>
+      <c r="O61" s="52"/>
+      <c r="P61" s="53"/>
+    </row>
+    <row r="62" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A62" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B62" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C62" s="50">
+        <v>2620</v>
+      </c>
+      <c r="D62" s="50"/>
+      <c r="E62" s="51">
+        <v>6</v>
+      </c>
+      <c r="F62" s="84">
+        <v>425</v>
+      </c>
+      <c r="G62" s="53"/>
+      <c r="H62" s="29"/>
+      <c r="I62" s="15">
+        <f t="shared" si="7"/>
+        <v>3045</v>
+      </c>
+      <c r="J62" s="15"/>
+      <c r="K62" s="29"/>
+      <c r="L62" s="57">
+        <v>3045</v>
+      </c>
+      <c r="M62" s="53"/>
+      <c r="N62" s="29"/>
+      <c r="O62" s="52"/>
+      <c r="P62" s="53"/>
+    </row>
+    <row r="63" spans="1:16" ht="30" x14ac:dyDescent="0.4">
+      <c r="A63" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C63" s="50">
+        <v>1350</v>
+      </c>
+      <c r="D63" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="E63" s="54">
+        <v>7</v>
+      </c>
+      <c r="F63" s="84">
+        <v>250</v>
+      </c>
+      <c r="G63" s="53"/>
+      <c r="H63" s="29"/>
+      <c r="I63" s="15">
+        <f t="shared" si="7"/>
+        <v>1600</v>
+      </c>
+      <c r="J63" s="15"/>
+      <c r="K63" s="29"/>
+      <c r="L63" s="57">
+        <v>1600</v>
+      </c>
+      <c r="M63" s="53"/>
+      <c r="N63" s="29"/>
+      <c r="O63" s="52"/>
+      <c r="P63" s="53"/>
+    </row>
+    <row r="64" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A64" s="27"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="15"/>
+      <c r="E64" s="29"/>
+      <c r="F64" s="52"/>
+      <c r="G64" s="53"/>
+      <c r="H64" s="29"/>
+      <c r="I64" s="15"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="29"/>
+      <c r="L64" s="57"/>
+      <c r="M64" s="53"/>
+      <c r="N64" s="29"/>
+      <c r="O64" s="52"/>
+      <c r="P64" s="53"/>
+    </row>
+    <row r="65" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A65" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="29">
+        <v>1</v>
+      </c>
+      <c r="F65" s="83">
+        <v>4940</v>
+      </c>
+      <c r="G65" s="53"/>
+      <c r="H65" s="29"/>
+      <c r="I65" s="15">
+        <f>C65+F65-G65</f>
+        <v>4940</v>
+      </c>
+      <c r="J65" s="15"/>
+      <c r="K65" s="29"/>
+      <c r="L65" s="57">
+        <v>4940</v>
+      </c>
+      <c r="M65" s="53"/>
+      <c r="N65" s="29"/>
+      <c r="O65" s="52"/>
+      <c r="P65" s="53"/>
+    </row>
+    <row r="66" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A66" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B66" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="29">
+        <v>2</v>
+      </c>
+      <c r="F66" s="83">
+        <v>1185</v>
+      </c>
+      <c r="G66" s="53"/>
+      <c r="H66" s="29"/>
+      <c r="I66" s="15">
+        <f t="shared" ref="I66:I67" si="8">C66+F66-G66</f>
+        <v>1185</v>
+      </c>
+      <c r="J66" s="15"/>
+      <c r="K66" s="29"/>
+      <c r="L66" s="57">
+        <v>1185</v>
+      </c>
+      <c r="M66" s="53"/>
+      <c r="N66" s="29"/>
+      <c r="O66" s="52"/>
+      <c r="P66" s="53"/>
+    </row>
+    <row r="67" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A67" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C67" s="15"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="29">
+        <v>3</v>
+      </c>
+      <c r="F67" s="83">
+        <v>7400</v>
+      </c>
+      <c r="G67" s="53"/>
+      <c r="H67" s="29"/>
+      <c r="I67" s="15">
+        <f t="shared" si="8"/>
+        <v>7400</v>
+      </c>
+      <c r="J67" s="15"/>
+      <c r="K67" s="29"/>
+      <c r="L67" s="57">
+        <v>7400</v>
+      </c>
+      <c r="M67" s="53"/>
+      <c r="N67" s="29"/>
+      <c r="O67" s="52"/>
+      <c r="P67" s="53"/>
+    </row>
+    <row r="68" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A68" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C68" s="15"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="29">
+        <v>4</v>
+      </c>
+      <c r="F68" s="84"/>
+      <c r="G68" s="84">
+        <v>260</v>
+      </c>
+      <c r="H68" s="29"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15">
+        <f>D68-F68+G68</f>
+        <v>260</v>
+      </c>
+      <c r="K68" s="29"/>
+      <c r="L68" s="52"/>
+      <c r="M68" s="53"/>
+      <c r="N68" s="29"/>
+      <c r="O68" s="52"/>
+      <c r="P68" s="53">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A69" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C69" s="15"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="29">
+        <v>5</v>
+      </c>
+      <c r="F69" s="52"/>
+      <c r="G69" s="84">
+        <v>830</v>
+      </c>
+      <c r="H69" s="29"/>
+      <c r="I69" s="15"/>
+      <c r="J69" s="15">
+        <f t="shared" ref="J69:J71" si="9">D69-F69+G69</f>
+        <v>830</v>
+      </c>
+      <c r="K69" s="29"/>
+      <c r="L69" s="52"/>
+      <c r="M69" s="53"/>
+      <c r="N69" s="29"/>
+      <c r="O69" s="52"/>
+      <c r="P69" s="53">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A70" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="29">
+        <v>6</v>
+      </c>
+      <c r="F70" s="52"/>
+      <c r="G70" s="84">
+        <v>425</v>
+      </c>
+      <c r="H70" s="29"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15">
+        <f t="shared" si="9"/>
+        <v>425</v>
+      </c>
+      <c r="K70" s="29"/>
+      <c r="L70" s="52"/>
+      <c r="M70" s="53"/>
+      <c r="N70" s="29"/>
+      <c r="O70" s="52"/>
+      <c r="P70" s="53">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A71" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="29">
+        <v>7</v>
+      </c>
+      <c r="F71" s="52"/>
+      <c r="G71" s="84">
+        <v>250</v>
+      </c>
+      <c r="H71" s="29"/>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15">
+        <f t="shared" si="9"/>
+        <v>250</v>
+      </c>
+      <c r="K71" s="29"/>
+      <c r="L71" s="52"/>
+      <c r="M71" s="53"/>
+      <c r="N71" s="29"/>
+      <c r="O71" s="52"/>
+      <c r="P71" s="53">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A72" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B72" s="29"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="29"/>
+      <c r="F72" s="52"/>
+      <c r="G72" s="53"/>
+      <c r="H72" s="29"/>
+      <c r="I72" s="15"/>
+      <c r="J72" s="15"/>
+      <c r="K72" s="29"/>
+      <c r="L72" s="52">
+        <v>29555</v>
+      </c>
+      <c r="M72" s="53"/>
+      <c r="N72" s="29"/>
+      <c r="O72" s="52"/>
+      <c r="P72" s="53">
+        <f>L72</f>
+        <v>29555</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A73" s="32"/>
+      <c r="B73" s="29"/>
+      <c r="C73" s="15"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="51"/>
+      <c r="F73" s="52"/>
+      <c r="G73" s="53"/>
+      <c r="H73" s="29"/>
+      <c r="I73" s="15"/>
+      <c r="J73" s="15"/>
+      <c r="K73" s="29"/>
+      <c r="L73" s="52"/>
+      <c r="M73" s="53"/>
+      <c r="N73" s="29"/>
+      <c r="O73" s="52"/>
+      <c r="P73" s="53"/>
+    </row>
+    <row r="74" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A74" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B74" s="29"/>
+      <c r="C74" s="50">
+        <f>SUM(C48:C63)</f>
+        <v>206640</v>
+      </c>
+      <c r="D74" s="50">
+        <f>SUM(D48:D63)</f>
+        <v>206640</v>
+      </c>
+      <c r="E74" s="29"/>
+      <c r="F74" s="55"/>
+      <c r="G74" s="55"/>
+      <c r="H74" s="56"/>
+      <c r="I74" s="55">
+        <f>SUM(I48:I73)</f>
+        <v>215805</v>
+      </c>
+      <c r="J74" s="55">
+        <f>SUM(J48:J73)</f>
+        <v>215805</v>
+      </c>
+      <c r="K74" s="56"/>
+      <c r="L74" s="55">
+        <f>SUM(L48:L73)</f>
+        <v>126500</v>
+      </c>
+      <c r="M74" s="55">
+        <f>SUM(M48:M73)</f>
+        <v>126500</v>
+      </c>
+      <c r="N74" s="56"/>
+      <c r="O74" s="55">
+        <f>SUM(O48:O73)</f>
+        <v>118860</v>
+      </c>
+      <c r="P74" s="55">
+        <f>SUM(P48:P73)</f>
+        <v>118860</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451FE678-24D7-4F17-8C17-332E4659A9B1}">
-  <dimension ref="A1:P35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:T76"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="37.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.59765625" customWidth="1"/>
-    <col min="3" max="4" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="3.53125" customWidth="1"/>
-    <col min="11" max="11" width="3.19921875" customWidth="1"/>
-    <col min="14" max="14" width="3.33203125" customWidth="1"/>
+    <col min="1" max="1" width="37.42578125" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" style="32" customWidth="1"/>
+    <col min="3" max="3" width="17" style="32" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="32" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" style="32" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="32"/>
+    <col min="8" max="8" width="3.5703125" style="32" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="32" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="32" customWidth="1"/>
+    <col min="11" max="11" width="3.140625" style="32" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="32" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="32" customWidth="1"/>
+    <col min="14" max="14" width="3.28515625" style="32" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" style="32" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" style="32" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="27" x14ac:dyDescent="0.65">
-      <c r="A1" s="14" t="s">
-        <v>124</v>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="19" t="s">
-        <v>63</v>
-      </c>
+      <c r="D1" s="19"/>
       <c r="E1" s="20"/>
       <c r="F1" s="19" t="s">
         <v>64</v>
@@ -4355,43 +5464,43 @@
       <c r="I1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="21"/>
+    </row>
+    <row r="2" spans="1:16" ht="42.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="107" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="19"/>
-      <c r="L1" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="M1" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="N1" s="21"/>
-      <c r="O1" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="P1" s="21"/>
-    </row>
-    <row r="2" spans="1:16" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A2" s="14"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="19"/>
+      <c r="D2" s="108"/>
       <c r="E2" s="20" t="s">
         <v>93</v>
       </c>
       <c r="F2" s="19"/>
       <c r="G2" s="19"/>
       <c r="H2" s="19"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="19"/>
+      <c r="I2" s="107" t="s">
+        <v>63</v>
+      </c>
+      <c r="J2" s="108"/>
       <c r="K2" s="19"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="21"/>
+      <c r="L2" s="105" t="s">
+        <v>206</v>
+      </c>
+      <c r="M2" s="106"/>
       <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-    </row>
-    <row r="3" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+      <c r="O2" s="107" t="s">
+        <v>67</v>
+      </c>
+      <c r="P2" s="108"/>
+    </row>
+    <row r="3" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A3" s="17" t="s">
         <v>94</v>
       </c>
@@ -4402,7 +5511,7 @@
       <c r="D3" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="20"/>
+      <c r="E3" s="101"/>
       <c r="F3" s="20" t="s">
         <v>45</v>
       </c>
@@ -4431,7 +5540,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="4" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A4" s="17" t="s">
         <v>77</v>
       </c>
@@ -4440,20 +5549,24 @@
         <v>5200</v>
       </c>
       <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
+      <c r="E4" s="86"/>
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
+      <c r="I4" s="15">
+        <v>5200</v>
+      </c>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
+      <c r="O4" s="15">
+        <v>5200</v>
+      </c>
       <c r="P4" s="15"/>
     </row>
-    <row r="5" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="5" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A5" s="17" t="s">
         <v>95</v>
       </c>
@@ -4462,20 +5575,24 @@
         <v>9260</v>
       </c>
       <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
+      <c r="E5" s="86"/>
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
+      <c r="I5" s="15">
+        <v>9260</v>
+      </c>
       <c r="J5" s="15"/>
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
+      <c r="O5" s="15">
+        <v>9260</v>
+      </c>
       <c r="P5" s="15"/>
     </row>
-    <row r="6" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="6" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A6" s="17" t="s">
         <v>96</v>
       </c>
@@ -4484,48 +5601,56 @@
         <v>920</v>
       </c>
       <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
+      <c r="E6" s="86"/>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
+      <c r="I6" s="15">
+        <v>920</v>
+      </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
+      <c r="O6" s="15">
+        <v>920</v>
+      </c>
       <c r="P6" s="15"/>
     </row>
-    <row r="7" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="7" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A7" s="17" t="s">
         <v>78</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="C7" s="15">
         <v>1140</v>
       </c>
       <c r="D7" s="15"/>
-      <c r="E7" s="15">
+      <c r="E7" s="86">
         <v>1</v>
       </c>
       <c r="F7" s="15"/>
-      <c r="G7" s="15">
+      <c r="G7" s="86">
         <v>720</v>
       </c>
       <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
+      <c r="I7" s="15">
+        <v>420</v>
+      </c>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
+      <c r="O7" s="15">
+        <v>420</v>
+      </c>
       <c r="P7" s="15"/>
     </row>
-    <row r="8" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="8" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A8" s="17" t="s">
         <v>97</v>
       </c>
@@ -4534,20 +5659,24 @@
         <v>60000</v>
       </c>
       <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
+      <c r="E8" s="86"/>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
+      <c r="I8" s="15">
+        <v>60000</v>
+      </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
+      <c r="O8" s="15">
+        <v>60000</v>
+      </c>
       <c r="P8" s="15"/>
     </row>
-    <row r="9" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="9" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A9" s="17" t="s">
         <v>98</v>
       </c>
@@ -4556,47 +5685,55 @@
         <v>152000</v>
       </c>
       <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
+      <c r="E9" s="86"/>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
+      <c r="I9" s="15">
+        <v>152000</v>
+      </c>
       <c r="J9" s="15"/>
       <c r="K9" s="15"/>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
+      <c r="O9" s="15">
+        <v>152000</v>
+      </c>
       <c r="P9" s="15"/>
     </row>
-    <row r="10" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="10" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A10" s="17" t="s">
-        <v>189</v>
+        <v>135</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
       <c r="D10" s="15">
         <v>64000</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="86">
         <v>3</v>
       </c>
       <c r="F10" s="15"/>
-      <c r="G10" s="15">
+      <c r="G10" s="86">
         <f>F26</f>
         <v>8760</v>
       </c>
       <c r="H10" s="15"/>
       <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
+      <c r="J10" s="90">
+        <v>72760</v>
+      </c>
       <c r="K10" s="15"/>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
       <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-    </row>
-    <row r="11" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+      <c r="P10" s="90">
+        <v>72760</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A11" s="17" t="s">
         <v>80</v>
       </c>
@@ -4605,47 +5742,55 @@
         <v>23400</v>
       </c>
       <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
+      <c r="E11" s="86"/>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
       <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
+      <c r="I11" s="15">
+        <v>23400</v>
+      </c>
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
+      <c r="O11" s="15">
+        <v>23400</v>
+      </c>
       <c r="P11" s="15"/>
     </row>
-    <row r="12" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="12" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A12" s="17" t="s">
-        <v>190</v>
+        <v>136</v>
       </c>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
       <c r="D12" s="15">
         <v>6420</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="86">
         <v>3</v>
       </c>
       <c r="F12" s="15"/>
-      <c r="G12" s="15">
+      <c r="G12" s="86">
         <f>F27</f>
         <v>2140</v>
       </c>
       <c r="H12" s="15"/>
       <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
+      <c r="J12" s="15">
+        <v>8560</v>
+      </c>
       <c r="K12" s="15"/>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
       <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-    </row>
-    <row r="13" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+      <c r="P12" s="15">
+        <v>8560</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A13" s="17" t="s">
         <v>99</v>
       </c>
@@ -4654,48 +5799,56 @@
       <c r="D13" s="15">
         <v>7960</v>
       </c>
-      <c r="E13" s="15"/>
+      <c r="E13" s="86"/>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
       <c r="H13" s="15"/>
       <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
+      <c r="J13" s="15">
+        <v>7960</v>
+      </c>
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-    </row>
-    <row r="14" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+      <c r="P13" s="15">
+        <v>7960</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A14" s="17" t="s">
         <v>100</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="C14" s="15"/>
       <c r="D14" s="15">
         <v>1560</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="86">
         <v>2</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="86">
         <v>1200</v>
       </c>
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
+      <c r="J14" s="15">
+        <v>360</v>
+      </c>
       <c r="K14" s="15"/>
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-    </row>
-    <row r="15" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+      <c r="P14" s="15">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A15" s="17" t="s">
         <v>101</v>
       </c>
@@ -4704,20 +5857,24 @@
       <c r="D15" s="15">
         <v>2000</v>
       </c>
-      <c r="E15" s="15"/>
+      <c r="E15" s="86"/>
       <c r="F15" s="15"/>
       <c r="G15" s="15"/>
       <c r="H15" s="15"/>
       <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
+      <c r="J15" s="15">
+        <v>2000</v>
+      </c>
       <c r="K15" s="15"/>
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-    </row>
-    <row r="16" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+      <c r="P15" s="15">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A16" s="17" t="s">
         <v>102</v>
       </c>
@@ -4726,20 +5883,24 @@
       <c r="D16" s="15">
         <v>88600</v>
       </c>
-      <c r="E16" s="15"/>
+      <c r="E16" s="86"/>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
       <c r="H16" s="15"/>
       <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
+      <c r="J16" s="15">
+        <v>88600</v>
+      </c>
       <c r="K16" s="15"/>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-    </row>
-    <row r="17" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+      <c r="P16" s="15">
+        <v>88600</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A17" s="17" t="s">
         <v>103</v>
       </c>
@@ -4748,20 +5909,24 @@
       <c r="D17" s="15">
         <v>71490</v>
       </c>
-      <c r="E17" s="15"/>
+      <c r="E17" s="86"/>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
       <c r="H17" s="15"/>
       <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
+      <c r="J17" s="15">
+        <v>71490</v>
+      </c>
       <c r="K17" s="15"/>
       <c r="L17" s="15"/>
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-    </row>
-    <row r="18" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+      <c r="P17" s="15">
+        <v>71490</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A18" s="17" t="s">
         <v>104</v>
       </c>
@@ -4770,48 +5935,62 @@
         <v>52780</v>
       </c>
       <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
+      <c r="E18" s="86"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
+      <c r="I18" s="15">
+        <v>52780</v>
+      </c>
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
+      <c r="O18" s="15">
+        <v>52780</v>
+      </c>
       <c r="P18" s="15"/>
     </row>
-    <row r="19" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+    <row r="19" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A19" s="17" t="s">
         <v>105</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>172</v>
+        <v>118</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="15">
         <v>156860</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="86">
         <v>2</v>
       </c>
       <c r="F19" s="15"/>
-      <c r="G19" s="15">
+      <c r="G19" s="86">
         <v>1200</v>
       </c>
       <c r="H19" s="15"/>
       <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
+      <c r="J19" s="15">
+        <v>158060</v>
+      </c>
       <c r="K19" s="15"/>
       <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
+      <c r="M19" s="100">
+        <v>158060</v>
+      </c>
       <c r="N19" s="15"/>
       <c r="O19" s="15"/>
       <c r="P19" s="15"/>
-    </row>
-    <row r="20" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+      <c r="S19" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="T19" s="32" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A20" s="17" t="s">
         <v>70</v>
       </c>
@@ -4820,24 +5999,36 @@
         <v>1660</v>
       </c>
       <c r="D20" s="15"/>
-      <c r="E20" s="15">
+      <c r="E20" s="86">
         <v>4</v>
       </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15">
+      <c r="F20" s="86">
+        <v>195</v>
+      </c>
+      <c r="G20" s="87">
         <v>585</v>
       </c>
       <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
+      <c r="I20" s="15">
+        <v>1855</v>
+      </c>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
+      <c r="L20" s="99">
+        <v>1855</v>
+      </c>
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
       <c r="P20" s="15"/>
-    </row>
-    <row r="21" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+      <c r="S20" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="T20" s="88" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A21" s="17" t="s">
         <v>84</v>
       </c>
@@ -4846,24 +6037,31 @@
         <v>87940</v>
       </c>
       <c r="D21" s="15"/>
-      <c r="E21" s="15">
+      <c r="E21" s="86">
         <v>7</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="86">
         <v>980</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
+      <c r="I21" s="15">
+        <v>88920</v>
+      </c>
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
+      <c r="L21" s="99">
+        <v>88920</v>
+      </c>
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
       <c r="O21" s="15"/>
       <c r="P21" s="15"/>
-    </row>
-    <row r="22" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+      <c r="T21" s="88" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A22" s="17" t="s">
         <v>88</v>
       </c>
@@ -4872,20 +6070,27 @@
         <v>760</v>
       </c>
       <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
+      <c r="E22" s="86"/>
       <c r="F22" s="15"/>
       <c r="G22" s="15"/>
       <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
+      <c r="I22" s="15">
+        <v>760</v>
+      </c>
       <c r="J22" s="15"/>
       <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
+      <c r="L22" s="99">
+        <v>760</v>
+      </c>
       <c r="M22" s="15"/>
       <c r="N22" s="15"/>
       <c r="O22" s="15"/>
       <c r="P22" s="15"/>
-    </row>
-    <row r="23" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+      <c r="T22" s="32" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A23" s="17" t="s">
         <v>90</v>
       </c>
@@ -4894,24 +6099,31 @@
         <v>2090</v>
       </c>
       <c r="D23" s="15"/>
-      <c r="E23" s="15">
+      <c r="E23" s="86">
         <v>5</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="86">
         <v>220</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
+      <c r="I23" s="15">
+        <v>2310</v>
+      </c>
       <c r="J23" s="15"/>
       <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
+      <c r="L23" s="99">
+        <v>2310</v>
+      </c>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
       <c r="O23" s="15"/>
       <c r="P23" s="15"/>
-    </row>
-    <row r="24" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+      <c r="T23" s="32" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A24" s="17" t="s">
         <v>106</v>
       </c>
@@ -4922,214 +6134,275 @@
       <c r="D24" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="86">
         <v>6</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="86">
         <v>320</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
+      <c r="I24" s="91" t="s">
+        <v>113</v>
+      </c>
       <c r="J24" s="15"/>
       <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
+      <c r="L24" s="102" t="s">
+        <v>113</v>
+      </c>
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
       <c r="O24" s="15"/>
       <c r="P24" s="15"/>
     </row>
-    <row r="25" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+    <row r="25" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A25" s="18" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>174</v>
+        <v>120</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="15"/>
-      <c r="E25" s="15">
+      <c r="E25" s="86">
         <v>1</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="86">
         <v>720</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
+      <c r="I25" s="15">
+        <v>720</v>
+      </c>
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
+      <c r="L25" s="99">
+        <v>720</v>
+      </c>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
       <c r="O25" s="15"/>
       <c r="P25" s="15"/>
-    </row>
-    <row r="26" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+      <c r="T25" s="88" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A26" s="18" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
-      <c r="E26" s="15">
+      <c r="E26" s="86">
         <v>3</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="86">
         <v>8760</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
+      <c r="I26" s="15">
+        <v>8760</v>
+      </c>
       <c r="J26" s="15"/>
       <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
+      <c r="L26" s="99">
+        <v>8760</v>
+      </c>
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
       <c r="O26" s="15"/>
       <c r="P26" s="15"/>
-    </row>
-    <row r="27" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+      <c r="T26" s="88" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A27" s="18" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
-      <c r="E27" s="15">
+      <c r="E27" s="86">
         <v>3</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="86">
         <v>2140</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
+      <c r="I27" s="15">
+        <v>2140</v>
+      </c>
       <c r="J27" s="15"/>
       <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
+      <c r="L27" s="99">
+        <v>2140</v>
+      </c>
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
       <c r="O27" s="15"/>
       <c r="P27" s="15"/>
     </row>
-    <row r="28" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+    <row r="28" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A28" s="18" t="s">
         <v>79</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
-      <c r="E28" s="15">
+      <c r="E28" s="86">
         <v>4</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="87">
         <v>585</v>
       </c>
-      <c r="G28" s="15"/>
+      <c r="G28" s="86">
+        <v>195</v>
+      </c>
       <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
+      <c r="I28" s="15">
+        <v>585</v>
+      </c>
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
       <c r="L28" s="15"/>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
+      <c r="O28" s="15">
+        <v>195</v>
+      </c>
       <c r="P28" s="15"/>
     </row>
-    <row r="29" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+    <row r="29" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A29" s="18" t="s">
         <v>75</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="15"/>
       <c r="D29" s="15"/>
-      <c r="E29" s="15">
+      <c r="E29" s="86">
         <v>5</v>
       </c>
       <c r="F29" s="15"/>
-      <c r="G29" s="15">
+      <c r="G29" s="86">
         <v>220</v>
       </c>
       <c r="H29" s="15"/>
       <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
+      <c r="J29" s="15">
+        <v>220</v>
+      </c>
       <c r="K29" s="15"/>
       <c r="L29" s="15"/>
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
       <c r="O29" s="15"/>
-      <c r="P29" s="15"/>
-    </row>
-    <row r="30" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+      <c r="P29" s="15">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" ht="39" x14ac:dyDescent="0.4">
       <c r="A30" s="18" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="15"/>
       <c r="D30" s="15"/>
-      <c r="E30" s="15">
+      <c r="E30" s="86">
         <v>6</v>
       </c>
       <c r="F30" s="15"/>
-      <c r="G30" s="15">
+      <c r="G30" s="86">
         <v>320</v>
       </c>
       <c r="H30" s="15"/>
       <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
+      <c r="J30" s="15">
+        <v>320</v>
+      </c>
       <c r="K30" s="15"/>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
       <c r="O30" s="15"/>
-      <c r="P30" s="15"/>
-    </row>
-    <row r="31" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+      <c r="P30" s="15">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A31" s="18" t="s">
         <v>72</v>
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
-      <c r="E31" s="15">
+      <c r="E31" s="86">
         <v>7</v>
       </c>
       <c r="F31" s="15"/>
-      <c r="G31" s="15">
+      <c r="G31" s="86">
         <v>980</v>
       </c>
       <c r="H31" s="15"/>
       <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
+      <c r="J31" s="15">
+        <v>980</v>
+      </c>
       <c r="K31" s="15"/>
       <c r="L31" s="15"/>
       <c r="M31" s="15"/>
       <c r="N31" s="15"/>
       <c r="O31" s="15"/>
-      <c r="P31" s="15"/>
-    </row>
-    <row r="32" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+      <c r="P31" s="15">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A32" s="18"/>
       <c r="B32" s="16"/>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
+      <c r="F32" s="15">
+        <v>14535</v>
+      </c>
+      <c r="G32" s="15">
+        <v>14535</v>
+      </c>
       <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
+      <c r="I32" s="103">
+        <f>SUM(I4:I31)</f>
+        <v>410030</v>
+      </c>
+      <c r="J32" s="103">
+        <f>SUM(J4:J31)</f>
+        <v>411310</v>
+      </c>
       <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
+      <c r="L32" s="15">
+        <f>SUM(L4:L31)</f>
+        <v>105465</v>
+      </c>
+      <c r="M32" s="15">
+        <v>158060</v>
+      </c>
       <c r="N32" s="15"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="15"/>
-    </row>
-    <row r="33" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.65">
+      <c r="O32" s="15">
+        <f>SUM(O4:O31)</f>
+        <v>304175</v>
+      </c>
+      <c r="P32" s="15">
+        <f>SUM(P4:P31)</f>
+        <v>253250</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A33" s="18" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="15"/>
@@ -5141,13 +6414,17 @@
       <c r="I33" s="15"/>
       <c r="J33" s="15"/>
       <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
+      <c r="L33" s="15">
+        <v>52595</v>
+      </c>
       <c r="M33" s="15"/>
       <c r="N33" s="15"/>
       <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
-    </row>
-    <row r="34" spans="1:16" ht="18.399999999999999" x14ac:dyDescent="0.7">
+      <c r="P33" s="15">
+        <v>52595</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A34" s="17"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -5159,14 +6436,25 @@
       <c r="I34" s="15"/>
       <c r="J34" s="15"/>
       <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
+      <c r="L34" s="15">
+        <f>SUM(L32:L33)</f>
+        <v>158060</v>
+      </c>
+      <c r="M34" s="15">
+        <v>158060</v>
+      </c>
       <c r="N34" s="15"/>
-      <c r="O34" s="15"/>
-      <c r="P34" s="15"/>
-    </row>
-    <row r="35" spans="1:16" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A35" s="14"/>
+      <c r="O34" s="15">
+        <f>SUM(O32)</f>
+        <v>304175</v>
+      </c>
+      <c r="P34" s="15">
+        <f>SUM(P32:P33)</f>
+        <v>305845</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A35" s="15"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15">
         <f>SUM(C4:C34)</f>
@@ -5189,7 +6477,838 @@
       <c r="O35" s="15"/>
       <c r="P35" s="15"/>
     </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A41" s="89" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A42" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" s="15"/>
+      <c r="C42" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="E42" s="20"/>
+      <c r="F42" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J42" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="K42" s="19"/>
+      <c r="L42" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M42" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="N42" s="21"/>
+      <c r="O42" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="P42" s="21"/>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A43" s="15"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="15"/>
+      <c r="M43" s="21"/>
+      <c r="N43" s="21"/>
+      <c r="O43" s="21"/>
+      <c r="P43" s="21"/>
+    </row>
+    <row r="44" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A44" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="15"/>
+      <c r="C44" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G44" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="J44" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="K44" s="21"/>
+      <c r="L44" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="M44" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="P44" s="20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A45" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15">
+        <v>5200</v>
+      </c>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
+      <c r="M45" s="15"/>
+      <c r="N45" s="15"/>
+      <c r="O45" s="15"/>
+      <c r="P45" s="15"/>
+    </row>
+    <row r="46" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A46" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15">
+        <v>9260</v>
+      </c>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="15"/>
+      <c r="M46" s="15"/>
+      <c r="N46" s="15"/>
+      <c r="O46" s="15"/>
+      <c r="P46" s="15"/>
+    </row>
+    <row r="47" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A47" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" s="15"/>
+      <c r="C47" s="15">
+        <v>920</v>
+      </c>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="15"/>
+      <c r="N47" s="15"/>
+      <c r="O47" s="15"/>
+      <c r="P47" s="15"/>
+    </row>
+    <row r="48" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A48" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="15">
+        <v>1140</v>
+      </c>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15">
+        <v>1</v>
+      </c>
+      <c r="F48" s="15"/>
+      <c r="G48" s="86"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+      <c r="M48" s="15"/>
+      <c r="N48" s="15"/>
+      <c r="O48" s="15"/>
+      <c r="P48" s="15"/>
+    </row>
+    <row r="49" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A49" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15">
+        <v>60000</v>
+      </c>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="15"/>
+      <c r="M49" s="15"/>
+      <c r="N49" s="15"/>
+      <c r="O49" s="15"/>
+      <c r="P49" s="15"/>
+    </row>
+    <row r="50" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A50" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="15"/>
+      <c r="C50" s="15">
+        <v>152000</v>
+      </c>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="15"/>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
+      <c r="K50" s="15"/>
+      <c r="L50" s="15"/>
+      <c r="M50" s="15"/>
+      <c r="N50" s="15"/>
+      <c r="O50" s="15"/>
+      <c r="P50" s="15"/>
+    </row>
+    <row r="51" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A51" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" s="15"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15">
+        <v>64000</v>
+      </c>
+      <c r="E51" s="15">
+        <v>3</v>
+      </c>
+      <c r="F51" s="86"/>
+      <c r="G51" s="86"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15"/>
+      <c r="L51" s="15"/>
+      <c r="M51" s="15"/>
+      <c r="N51" s="15"/>
+      <c r="O51" s="15"/>
+      <c r="P51" s="15"/>
+    </row>
+    <row r="52" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A52" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B52" s="15"/>
+      <c r="C52" s="15">
+        <v>23400</v>
+      </c>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="86"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+      <c r="K52" s="15"/>
+      <c r="L52" s="15"/>
+      <c r="M52" s="15"/>
+      <c r="N52" s="15"/>
+      <c r="O52" s="15"/>
+      <c r="P52" s="15"/>
+    </row>
+    <row r="53" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A53" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B53" s="15"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15">
+        <v>6420</v>
+      </c>
+      <c r="E53" s="15">
+        <v>3</v>
+      </c>
+      <c r="F53" s="86"/>
+      <c r="G53" s="86"/>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="15"/>
+      <c r="M53" s="15"/>
+      <c r="N53" s="15"/>
+      <c r="O53" s="15"/>
+      <c r="P53" s="15"/>
+    </row>
+    <row r="54" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A54" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B54" s="15"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="15">
+        <v>7960</v>
+      </c>
+      <c r="E54" s="15"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="15"/>
+      <c r="H54" s="15"/>
+      <c r="I54" s="15"/>
+      <c r="J54" s="15"/>
+      <c r="K54" s="15"/>
+      <c r="L54" s="15"/>
+      <c r="M54" s="15"/>
+      <c r="N54" s="15"/>
+      <c r="O54" s="15"/>
+      <c r="P54" s="15"/>
+    </row>
+    <row r="55" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A55" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15">
+        <v>1560</v>
+      </c>
+      <c r="E55" s="15">
+        <v>2</v>
+      </c>
+      <c r="F55" s="86"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15"/>
+      <c r="L55" s="15"/>
+      <c r="M55" s="15"/>
+      <c r="N55" s="15"/>
+      <c r="O55" s="15"/>
+      <c r="P55" s="15"/>
+    </row>
+    <row r="56" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A56" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B56" s="15"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15">
+        <v>2000</v>
+      </c>
+      <c r="E56" s="15"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="15"/>
+      <c r="H56" s="15"/>
+      <c r="I56" s="15"/>
+      <c r="J56" s="15"/>
+      <c r="K56" s="15"/>
+      <c r="L56" s="15"/>
+      <c r="M56" s="15"/>
+      <c r="N56" s="15"/>
+      <c r="O56" s="15"/>
+      <c r="P56" s="15"/>
+    </row>
+    <row r="57" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A57" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15">
+        <v>88600</v>
+      </c>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="15"/>
+      <c r="I57" s="15"/>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="15"/>
+      <c r="M57" s="15"/>
+      <c r="N57" s="15"/>
+      <c r="O57" s="15"/>
+      <c r="P57" s="15"/>
+    </row>
+    <row r="58" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A58" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B58" s="15"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15">
+        <v>71490</v>
+      </c>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="15"/>
+      <c r="H58" s="15"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="15"/>
+      <c r="M58" s="15"/>
+      <c r="N58" s="15"/>
+      <c r="O58" s="15"/>
+      <c r="P58" s="15"/>
+    </row>
+    <row r="59" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A59" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15">
+        <v>52780</v>
+      </c>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="15"/>
+      <c r="H59" s="15"/>
+      <c r="I59" s="15"/>
+      <c r="J59" s="15"/>
+      <c r="K59" s="15"/>
+      <c r="L59" s="15"/>
+      <c r="M59" s="15"/>
+      <c r="N59" s="15"/>
+      <c r="O59" s="15"/>
+      <c r="P59" s="15"/>
+    </row>
+    <row r="60" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A60" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C60" s="15"/>
+      <c r="D60" s="15">
+        <v>156860</v>
+      </c>
+      <c r="E60" s="15">
+        <v>2</v>
+      </c>
+      <c r="F60" s="15"/>
+      <c r="G60" s="86"/>
+      <c r="H60" s="15"/>
+      <c r="I60" s="15"/>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="15"/>
+      <c r="M60" s="15"/>
+      <c r="N60" s="15"/>
+      <c r="O60" s="15"/>
+      <c r="P60" s="15"/>
+    </row>
+    <row r="61" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A61" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61" s="15"/>
+      <c r="C61" s="15">
+        <v>1660</v>
+      </c>
+      <c r="D61" s="15"/>
+      <c r="E61" s="15">
+        <v>4</v>
+      </c>
+      <c r="F61" s="86"/>
+      <c r="G61" s="15"/>
+      <c r="H61" s="15"/>
+      <c r="I61" s="15"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+      <c r="L61" s="15"/>
+      <c r="M61" s="15"/>
+      <c r="N61" s="15"/>
+      <c r="O61" s="15"/>
+      <c r="P61" s="15"/>
+    </row>
+    <row r="62" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A62" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B62" s="15"/>
+      <c r="C62" s="15">
+        <v>87940</v>
+      </c>
+      <c r="D62" s="15"/>
+      <c r="E62" s="15">
+        <v>7</v>
+      </c>
+      <c r="F62" s="86"/>
+      <c r="G62" s="15"/>
+      <c r="H62" s="15"/>
+      <c r="I62" s="15"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+      <c r="L62" s="15"/>
+      <c r="M62" s="15"/>
+      <c r="N62" s="15"/>
+      <c r="O62" s="15"/>
+      <c r="P62" s="15"/>
+    </row>
+    <row r="63" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A63" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B63" s="15"/>
+      <c r="C63" s="15">
+        <v>760</v>
+      </c>
+      <c r="D63" s="15"/>
+      <c r="E63" s="15"/>
+      <c r="F63" s="15"/>
+      <c r="G63" s="15"/>
+      <c r="H63" s="15"/>
+      <c r="I63" s="15"/>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
+      <c r="L63" s="15"/>
+      <c r="M63" s="15"/>
+      <c r="N63" s="15"/>
+      <c r="O63" s="15"/>
+      <c r="P63" s="15"/>
+    </row>
+    <row r="64" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A64" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B64" s="15"/>
+      <c r="C64" s="15">
+        <v>2090</v>
+      </c>
+      <c r="D64" s="15"/>
+      <c r="E64" s="15">
+        <v>5</v>
+      </c>
+      <c r="F64" s="86"/>
+      <c r="G64" s="15"/>
+      <c r="H64" s="15"/>
+      <c r="I64" s="15"/>
+      <c r="J64" s="15"/>
+      <c r="K64" s="15"/>
+      <c r="L64" s="15"/>
+      <c r="M64" s="15"/>
+      <c r="N64" s="15"/>
+      <c r="O64" s="15"/>
+      <c r="P64" s="15"/>
+    </row>
+    <row r="65" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A65" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B65" s="15"/>
+      <c r="C65" s="15">
+        <v>1740</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E65" s="15">
+        <v>6</v>
+      </c>
+      <c r="F65" s="86"/>
+      <c r="G65" s="15"/>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
+      <c r="L65" s="15"/>
+      <c r="M65" s="15"/>
+      <c r="N65" s="15"/>
+      <c r="O65" s="15"/>
+      <c r="P65" s="15"/>
+    </row>
+    <row r="66" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A66" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="15">
+        <v>1</v>
+      </c>
+      <c r="F66" s="86"/>
+      <c r="G66" s="15"/>
+      <c r="H66" s="15"/>
+      <c r="I66" s="15"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
+      <c r="L66" s="15"/>
+      <c r="M66" s="15"/>
+      <c r="N66" s="15"/>
+      <c r="O66" s="15"/>
+      <c r="P66" s="15"/>
+    </row>
+    <row r="67" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A67" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B67" s="16"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="15">
+        <v>3</v>
+      </c>
+      <c r="F67" s="86"/>
+      <c r="G67" s="15"/>
+      <c r="H67" s="15"/>
+      <c r="I67" s="15"/>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
+      <c r="L67" s="15"/>
+      <c r="M67" s="15"/>
+      <c r="N67" s="15"/>
+      <c r="O67" s="15"/>
+      <c r="P67" s="15"/>
+    </row>
+    <row r="68" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A68" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B68" s="16"/>
+      <c r="C68" s="15"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="15">
+        <v>3</v>
+      </c>
+      <c r="F68" s="86"/>
+      <c r="G68" s="15"/>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
+      <c r="L68" s="15"/>
+      <c r="M68" s="15"/>
+      <c r="N68" s="15"/>
+      <c r="O68" s="15"/>
+      <c r="P68" s="15"/>
+    </row>
+    <row r="69" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A69" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B69" s="16"/>
+      <c r="C69" s="15"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="15">
+        <v>4</v>
+      </c>
+      <c r="F69" s="15"/>
+      <c r="G69" s="86"/>
+      <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
+      <c r="J69" s="15"/>
+      <c r="K69" s="15"/>
+      <c r="L69" s="15"/>
+      <c r="M69" s="15"/>
+      <c r="N69" s="15"/>
+      <c r="O69" s="15"/>
+      <c r="P69" s="15"/>
+    </row>
+    <row r="70" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A70" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B70" s="16"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15">
+        <v>5</v>
+      </c>
+      <c r="F70" s="15"/>
+      <c r="G70" s="86"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
+      <c r="L70" s="15"/>
+      <c r="M70" s="15"/>
+      <c r="N70" s="15"/>
+      <c r="O70" s="15"/>
+      <c r="P70" s="15"/>
+    </row>
+    <row r="71" spans="1:16" ht="39" x14ac:dyDescent="0.4">
+      <c r="A71" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B71" s="16"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
+      <c r="E71" s="15">
+        <v>6</v>
+      </c>
+      <c r="F71" s="15"/>
+      <c r="G71" s="86"/>
+      <c r="H71" s="15"/>
+      <c r="I71" s="15"/>
+      <c r="J71" s="15"/>
+      <c r="K71" s="15"/>
+      <c r="L71" s="15"/>
+      <c r="M71" s="15"/>
+      <c r="N71" s="15"/>
+      <c r="O71" s="15"/>
+      <c r="P71" s="15"/>
+    </row>
+    <row r="72" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A72" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B72" s="16"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="15"/>
+      <c r="E72" s="15">
+        <v>7</v>
+      </c>
+      <c r="F72" s="15"/>
+      <c r="G72" s="86"/>
+      <c r="H72" s="15"/>
+      <c r="I72" s="15"/>
+      <c r="J72" s="15"/>
+      <c r="K72" s="15"/>
+      <c r="L72" s="15"/>
+      <c r="M72" s="15"/>
+      <c r="N72" s="15"/>
+      <c r="O72" s="15"/>
+      <c r="P72" s="15"/>
+    </row>
+    <row r="73" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A73" s="18"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="15"/>
+      <c r="D73" s="15"/>
+      <c r="E73" s="15"/>
+      <c r="F73" s="15"/>
+      <c r="G73" s="15"/>
+      <c r="H73" s="15"/>
+      <c r="I73" s="15"/>
+      <c r="J73" s="15"/>
+      <c r="K73" s="15"/>
+      <c r="L73" s="15"/>
+      <c r="M73" s="15"/>
+      <c r="N73" s="15"/>
+      <c r="O73" s="15"/>
+      <c r="P73" s="15"/>
+    </row>
+    <row r="74" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A74" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B74" s="16"/>
+      <c r="C74" s="15"/>
+      <c r="D74" s="15"/>
+      <c r="E74" s="15"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="15"/>
+      <c r="H74" s="15"/>
+      <c r="I74" s="15"/>
+      <c r="J74" s="15"/>
+      <c r="K74" s="15"/>
+      <c r="L74" s="15"/>
+      <c r="M74" s="15"/>
+      <c r="N74" s="15"/>
+      <c r="O74" s="15"/>
+      <c r="P74" s="15"/>
+    </row>
+    <row r="75" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A75" s="17"/>
+      <c r="B75" s="15"/>
+      <c r="C75" s="15"/>
+      <c r="D75" s="15"/>
+      <c r="E75" s="15"/>
+      <c r="F75" s="15"/>
+      <c r="G75" s="15"/>
+      <c r="H75" s="15"/>
+      <c r="I75" s="15"/>
+      <c r="J75" s="15"/>
+      <c r="K75" s="15"/>
+      <c r="L75" s="15"/>
+      <c r="M75" s="15"/>
+      <c r="N75" s="15"/>
+      <c r="O75" s="15"/>
+      <c r="P75" s="15"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A76" s="15"/>
+      <c r="B76" s="15"/>
+      <c r="C76" s="15">
+        <f>SUM(C45:C75)</f>
+        <v>398890</v>
+      </c>
+      <c r="D76" s="15">
+        <f>SUM(D45:D75)</f>
+        <v>398890</v>
+      </c>
+      <c r="E76" s="15"/>
+      <c r="F76" s="15"/>
+      <c r="G76" s="15"/>
+      <c r="H76" s="15"/>
+      <c r="I76" s="15"/>
+      <c r="J76" s="15"/>
+      <c r="K76" s="15"/>
+      <c r="L76" s="15"/>
+      <c r="M76" s="15"/>
+      <c r="N76" s="15"/>
+      <c r="O76" s="15"/>
+      <c r="P76" s="15"/>
+    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="C2:D2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -5198,7 +7317,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB70836-D79F-4864-89CC-B27D7E0A03DC}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5207,13 +7326,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA4CDB96-6C4C-4200-8B12-486AAEF84CD0}">
   <dimension ref="A1:M35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="18.1328125" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B1" s="3"/>
       <c r="C1" s="4" t="s">
         <v>15</v>
@@ -5221,35 +7340,35 @@
       <c r="D1" s="4"/>
       <c r="E1" s="5"/>
       <c r="H1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>93</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C2" s="75" t="s">
-        <v>181</v>
-      </c>
-      <c r="D2" s="75" t="s">
-        <v>191</v>
+        <v>126</v>
+      </c>
+      <c r="C2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" t="s">
+        <v>137</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="74">
+      <c r="B3" s="73">
         <v>46387</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
       <c r="D3" s="4">
         <v>4940</v>
@@ -5259,36 +7378,35 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
       <c r="I3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="6"/>
-      <c r="C4" s="75" t="s">
-        <v>206</v>
-      </c>
-      <c r="D4" s="75"/>
+      <c r="C4" t="s">
+        <v>152</v>
+      </c>
       <c r="E4" s="7">
         <f>D3</f>
         <v>4940</v>
       </c>
-      <c r="G4" s="73" t="s">
-        <v>197</v>
+      <c r="G4" s="72" t="s">
+        <v>143</v>
       </c>
       <c r="H4" t="s">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="I4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11"/>
       <c r="C5" s="12" t="s">
-        <v>208</v>
+        <v>154</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="13"/>
@@ -5302,63 +7420,60 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="6"/>
-      <c r="C6" s="75"/>
-      <c r="D6" s="75"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
-      <c r="B7" s="74">
+      <c r="B7" s="73">
         <v>46387</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="D7" s="4">
         <v>1185</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="G7" s="73">
+      <c r="G7" s="72">
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>209</v>
+        <v>155</v>
       </c>
       <c r="I7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="6"/>
-      <c r="C8" s="75" t="s">
+      <c r="C8" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="75"/>
       <c r="E8" s="7">
         <v>1185</v>
       </c>
-      <c r="G8" s="73" t="s">
-        <v>197</v>
+      <c r="G8" s="72" t="s">
+        <v>143</v>
       </c>
       <c r="H8" t="s">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="I8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="11"/>
       <c r="C9" s="12" t="s">
-        <v>212</v>
+        <v>158</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="13"/>
-      <c r="G9" s="73">
+      <c r="G9" s="72">
         <v>4</v>
       </c>
       <c r="H9" t="s">
@@ -5368,400 +7483,388 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
       <c r="E10" s="7"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>3</v>
       </c>
-      <c r="B11" s="74">
+      <c r="B11" s="73">
         <v>46387</v>
       </c>
-      <c r="C11" s="86" t="s">
-        <v>214</v>
+      <c r="C11" s="4" t="s">
+        <v>160</v>
       </c>
       <c r="D11" s="4">
         <v>7400</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="G11" s="73">
+      <c r="G11" s="72">
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>213</v>
+        <v>159</v>
       </c>
       <c r="I11" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="6"/>
-      <c r="C12" s="85" t="s">
-        <v>213</v>
-      </c>
-      <c r="D12" s="75"/>
+      <c r="C12" t="s">
+        <v>159</v>
+      </c>
       <c r="E12" s="7">
         <v>7400</v>
       </c>
-      <c r="G12" s="73" t="s">
-        <v>197</v>
-      </c>
-      <c r="H12" s="72" t="s">
-        <v>201</v>
-      </c>
-      <c r="I12" s="72" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G12" s="72" t="s">
+        <v>143</v>
+      </c>
+      <c r="H12" s="71" t="s">
+        <v>147</v>
+      </c>
+      <c r="I12" s="71" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="11"/>
-      <c r="C13" s="87" t="s">
-        <v>217</v>
+      <c r="C13" s="12" t="s">
+        <v>163</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="13"/>
-      <c r="G13" s="73">
+      <c r="G13" s="72">
         <v>4</v>
       </c>
       <c r="H13" t="s">
-        <v>215</v>
+        <v>161</v>
       </c>
       <c r="I13" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="6"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="75"/>
       <c r="E14" s="7"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>4</v>
       </c>
-      <c r="B15" s="74">
+      <c r="B15" s="73">
         <v>46387</v>
       </c>
-      <c r="C15" s="86" t="s">
-        <v>218</v>
+      <c r="C15" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="D15" s="4">
         <v>260</v>
       </c>
       <c r="E15" s="5"/>
-      <c r="G15" s="73">
+      <c r="G15" s="72">
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="I15" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
-      <c r="C16" s="85" t="s">
-        <v>219</v>
-      </c>
-      <c r="D16" s="75"/>
+      <c r="C16" t="s">
+        <v>165</v>
+      </c>
       <c r="E16" s="7">
         <v>260</v>
       </c>
-      <c r="G16" s="73" t="s">
-        <v>197</v>
-      </c>
-      <c r="H16" s="72" t="s">
-        <v>200</v>
-      </c>
-      <c r="I16" s="72" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G16" s="72" t="s">
+        <v>143</v>
+      </c>
+      <c r="H16" s="71" t="s">
+        <v>146</v>
+      </c>
+      <c r="I16" s="71" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="11"/>
-      <c r="C17" s="87" t="s">
-        <v>221</v>
+      <c r="C17" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="13"/>
-      <c r="G17" s="73">
+      <c r="G17" s="72">
         <v>4</v>
       </c>
       <c r="H17" t="s">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="I17" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="6"/>
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
       <c r="E18" s="7"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>5</v>
       </c>
-      <c r="B19" s="74">
+      <c r="B19" s="73">
         <v>46387</v>
       </c>
-      <c r="C19" s="85" t="s">
-        <v>224</v>
-      </c>
-      <c r="D19" s="75">
+      <c r="C19" t="s">
+        <v>170</v>
+      </c>
+      <c r="D19">
         <v>830</v>
       </c>
       <c r="E19" s="7"/>
-      <c r="G19" s="73">
+      <c r="G19" s="72">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>222</v>
+        <v>168</v>
       </c>
       <c r="I19" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B20" s="6"/>
-      <c r="C20" s="85" t="s">
-        <v>225</v>
-      </c>
-      <c r="D20" s="75"/>
+      <c r="C20" t="s">
+        <v>171</v>
+      </c>
       <c r="E20" s="7">
         <v>830</v>
       </c>
-      <c r="G20" s="73" t="s">
-        <v>197</v>
-      </c>
-      <c r="H20" s="72" t="s">
-        <v>200</v>
-      </c>
-      <c r="I20" s="72" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="G20" s="72" t="s">
+        <v>143</v>
+      </c>
+      <c r="H20" s="71" t="s">
+        <v>146</v>
+      </c>
+      <c r="I20" s="71" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B21" s="6"/>
-      <c r="C21" s="85" t="s">
-        <v>226</v>
-      </c>
-      <c r="D21" s="75"/>
+      <c r="C21" t="s">
+        <v>172</v>
+      </c>
       <c r="E21" s="7"/>
-      <c r="G21" s="73">
+      <c r="G21" s="72">
         <v>4</v>
       </c>
       <c r="H21" t="s">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="I21" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="11"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
       <c r="E22" s="13"/>
     </row>
-    <row r="23" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>6</v>
       </c>
-      <c r="B24" s="74">
+      <c r="B24" s="73">
         <v>46387</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="D24" s="4">
         <v>425</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="G24" s="73">
+      <c r="G24" s="72">
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>227</v>
+        <v>173</v>
       </c>
       <c r="I24" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B25" s="6"/>
-      <c r="C25" s="75" t="s">
-        <v>228</v>
-      </c>
-      <c r="D25" s="75"/>
+      <c r="C25" t="s">
+        <v>174</v>
+      </c>
       <c r="E25" s="7">
         <v>425</v>
       </c>
-      <c r="G25" s="73" t="s">
-        <v>197</v>
-      </c>
-      <c r="H25" s="72" t="s">
-        <v>200</v>
-      </c>
-      <c r="I25" s="72" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G25" s="72" t="s">
+        <v>143</v>
+      </c>
+      <c r="H25" s="71" t="s">
+        <v>146</v>
+      </c>
+      <c r="I25" s="71" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="11"/>
       <c r="C26" s="12" t="s">
-        <v>229</v>
+        <v>175</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="13"/>
-      <c r="G26" s="73">
+      <c r="G26" s="72">
         <v>4</v>
       </c>
       <c r="H26" t="s">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="I26" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="28" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>7</v>
       </c>
-      <c r="B28" s="74">
+      <c r="B28" s="73">
         <v>46387</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>230</v>
+        <v>176</v>
       </c>
       <c r="D28" s="4">
         <v>250</v>
       </c>
       <c r="E28" s="5"/>
-      <c r="G28" s="73">
+      <c r="G28" s="72">
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>230</v>
+        <v>176</v>
       </c>
       <c r="I28" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B29" s="6"/>
-      <c r="C29" s="75" t="s">
-        <v>231</v>
-      </c>
-      <c r="D29" s="75"/>
+      <c r="C29" t="s">
+        <v>177</v>
+      </c>
       <c r="E29" s="4">
         <v>250</v>
       </c>
-      <c r="G29" s="73" t="s">
-        <v>197</v>
-      </c>
-      <c r="H29" s="72" t="s">
-        <v>200</v>
-      </c>
-      <c r="I29" s="72" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G29" s="72" t="s">
+        <v>143</v>
+      </c>
+      <c r="H29" s="71" t="s">
+        <v>146</v>
+      </c>
+      <c r="I29" s="71" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="11"/>
       <c r="C30" s="12" t="s">
-        <v>229</v>
+        <v>175</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="13"/>
-      <c r="G30" s="73">
+      <c r="G30" s="72">
         <v>4</v>
       </c>
       <c r="H30" t="s">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="I30" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>193</v>
+        <v>139</v>
       </c>
       <c r="I32" t="s">
-        <v>192</v>
-      </c>
-      <c r="K32" s="76"/>
-      <c r="L32" s="77" t="s">
+        <v>138</v>
+      </c>
+      <c r="K32" s="74"/>
+      <c r="L32" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="M32" s="78" t="s">
+      <c r="M32" s="76" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="7:13" x14ac:dyDescent="0.45">
+    <row r="33" spans="7:13" x14ac:dyDescent="0.25">
       <c r="G33">
         <v>2</v>
       </c>
       <c r="H33" t="s">
-        <v>194</v>
+        <v>140</v>
       </c>
       <c r="I33" t="s">
-        <v>194</v>
-      </c>
-      <c r="K33" s="79" t="s">
-        <v>202</v>
-      </c>
-      <c r="L33" s="80" t="s">
-        <v>204</v>
-      </c>
-      <c r="M33" s="81" t="s">
+        <v>140</v>
+      </c>
+      <c r="K33" s="77" t="s">
+        <v>148</v>
+      </c>
+      <c r="L33" s="78" t="s">
+        <v>150</v>
+      </c>
+      <c r="M33" s="79" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="7:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="34" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G34">
         <v>3</v>
       </c>
-      <c r="H34" s="72" t="s">
-        <v>196</v>
-      </c>
-      <c r="I34" s="72" t="s">
-        <v>196</v>
-      </c>
-      <c r="K34" s="82" t="s">
-        <v>203</v>
-      </c>
-      <c r="L34" s="83" t="s">
+      <c r="H34" s="71" t="s">
+        <v>142</v>
+      </c>
+      <c r="I34" s="71" t="s">
+        <v>142</v>
+      </c>
+      <c r="K34" s="80" t="s">
+        <v>149</v>
+      </c>
+      <c r="L34" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="M34" s="84" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="35" spans="7:13" x14ac:dyDescent="0.45">
+      <c r="M34" s="82" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="7:13" x14ac:dyDescent="0.25">
       <c r="G35">
         <v>4</v>
       </c>
       <c r="H35" t="s">
-        <v>195</v>
+        <v>141</v>
       </c>
       <c r="I35" t="s">
-        <v>195</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -5772,14 +7875,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14BBB4DE-EA90-4F91-8180-6C1E6B7C8861}">
   <dimension ref="A2:L32"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.06640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.796875" customWidth="1"/>
-    <col min="10" max="10" width="9.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>76</v>
       </c>
@@ -5807,7 +7910,7 @@
       </c>
       <c r="L2" s="14"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="14"/>
       <c r="B3" s="14" t="s">
         <v>63</v>
@@ -5824,7 +7927,7 @@
       <c r="K3" s="14"/>
       <c r="L3" s="14"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="14"/>
       <c r="B4" s="14" t="s">
         <v>45</v>
@@ -5858,7 +7961,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>77</v>
       </c>
@@ -5880,7 +7983,7 @@
       </c>
       <c r="L5" s="14"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>78</v>
       </c>
@@ -5906,7 +8009,7 @@
       </c>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>79</v>
       </c>
@@ -5932,7 +8035,7 @@
       </c>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>80</v>
       </c>
@@ -5954,7 +8057,7 @@
       </c>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>81</v>
       </c>
@@ -5980,7 +8083,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>82</v>
       </c>
@@ -6002,7 +8105,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>52</v>
       </c>
@@ -6024,7 +8127,7 @@
         <v>15540</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>53</v>
       </c>
@@ -6046,7 +8149,7 @@
       </c>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>83</v>
       </c>
@@ -6068,7 +8171,7 @@
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>84</v>
       </c>
@@ -6094,7 +8197,7 @@
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>85</v>
       </c>
@@ -6116,7 +8219,7 @@
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>86</v>
       </c>
@@ -6138,7 +8241,7 @@
       <c r="K16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>87</v>
       </c>
@@ -6160,7 +8263,7 @@
       <c r="K17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>88</v>
       </c>
@@ -6186,7 +8289,7 @@
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>89</v>
       </c>
@@ -6212,7 +8315,7 @@
       <c r="K19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>90</v>
       </c>
@@ -6238,7 +8341,7 @@
       <c r="K20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="14"/>
       <c r="B21" s="14">
         <v>206640</v>
@@ -6256,7 +8359,7 @@
       <c r="K21" s="14"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>69</v>
       </c>
@@ -6280,7 +8383,7 @@
       <c r="K22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>70</v>
       </c>
@@ -6304,7 +8407,7 @@
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>71</v>
       </c>
@@ -6328,7 +8431,7 @@
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>72</v>
       </c>
@@ -6352,7 +8455,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>73</v>
       </c>
@@ -6376,7 +8479,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>74</v>
       </c>
@@ -6400,7 +8503,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>75</v>
       </c>
@@ -6424,7 +8527,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>92</v>
       </c>
@@ -6448,7 +8551,7 @@
         <v>89305</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>91</v>
       </c>
@@ -6468,7 +8571,7 @@
         <v>29555</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -6482,7 +8585,7 @@
       <c r="K31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>68</v>
       </c>
@@ -6529,741 +8632,842 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F243036-475E-442E-9214-8F3E938FBBFF}">
-  <dimension ref="A2:K39"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:L45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.73046875" customWidth="1"/>
-    <col min="2" max="2" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" customWidth="1"/>
-    <col min="8" max="8" width="12.53125" customWidth="1"/>
-    <col min="9" max="9" width="11.19921875" customWidth="1"/>
-    <col min="10" max="10" width="10.46484375" customWidth="1"/>
-    <col min="11" max="11" width="10.796875" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="110"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="111"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="110" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="111"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="110" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32" t="s">
-        <v>131</v>
-      </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32" t="s">
-        <v>132</v>
-      </c>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32" t="s">
+      <c r="F2" s="111"/>
+      <c r="G2" s="110" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="111"/>
+      <c r="I2" s="110" t="s">
+        <v>206</v>
+      </c>
+      <c r="J2" s="111"/>
+      <c r="K2" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="K2" s="32"/>
-    </row>
-    <row r="3" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A3" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="B3" s="32" t="s">
+      <c r="L2" s="111"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="14"/>
+      <c r="B3" s="110" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="111"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="110" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" s="111"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="110"/>
+      <c r="L3" s="111"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C4" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D4" s="94" t="s">
+        <v>197</v>
+      </c>
+      <c r="E4" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="F4" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="32" t="s">
+      <c r="G4" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="H4" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="I3" s="32" t="s">
+      <c r="I4" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="K4" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="L4" s="14" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A4" s="32" t="s">
+    <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A5" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="K4" s="32"/>
-    </row>
-    <row r="5" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A5" s="32" t="s">
+      <c r="B5" s="15">
+        <v>12600</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="86"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15">
+        <v>12600</v>
+      </c>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15">
+        <v>12600</v>
+      </c>
+      <c r="L5" s="14"/>
+    </row>
+    <row r="6" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A6" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="K5" s="32"/>
-    </row>
-    <row r="6" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A6" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="32">
-        <v>920</v>
-      </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32">
-        <v>920</v>
-      </c>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32">
-        <v>920</v>
-      </c>
-      <c r="K6" s="32"/>
-    </row>
-    <row r="7" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A7" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="F7" s="32">
-        <v>420</v>
-      </c>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32">
-        <v>420</v>
-      </c>
-      <c r="K7" s="32"/>
-    </row>
-    <row r="8" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A8" s="32" t="s">
+      <c r="B6" s="15">
+        <v>11800</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="86"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15">
+        <v>11800</v>
+      </c>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15">
+        <v>11800</v>
+      </c>
+      <c r="L6" s="14"/>
+    </row>
+    <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A7" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="15">
+        <v>1800</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="86" t="s">
+        <v>195</v>
+      </c>
+      <c r="E7" s="15"/>
+      <c r="F7" s="86">
+        <v>1340</v>
+      </c>
+      <c r="G7" s="15">
+        <v>460</v>
+      </c>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15">
+        <v>460</v>
+      </c>
+      <c r="L7" s="14"/>
+    </row>
+    <row r="8" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A8" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="K8" s="32"/>
-    </row>
-    <row r="9" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A9" s="32" t="s">
+      <c r="B8" s="15">
+        <v>180200</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="86"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15">
+        <v>180200</v>
+      </c>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15">
+        <v>180200</v>
+      </c>
+      <c r="L8" s="14"/>
+    </row>
+    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A9" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="B9" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="K9" s="32"/>
-    </row>
-    <row r="10" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A10" s="32" t="s">
-        <v>136</v>
-      </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32" t="s">
-        <v>139</v>
-      </c>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A11" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="K11" s="32"/>
-    </row>
-    <row r="12" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A12" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32" t="s">
-        <v>142</v>
-      </c>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A13" s="32" t="s">
+      <c r="B9" s="15">
+        <v>196000</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15">
+        <v>196000</v>
+      </c>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15">
+        <v>196000</v>
+      </c>
+      <c r="L9" s="14"/>
+    </row>
+    <row r="10" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A10" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15">
+        <v>86900</v>
+      </c>
+      <c r="D10" s="86" t="s">
+        <v>196</v>
+      </c>
+      <c r="E10" s="15"/>
+      <c r="F10" s="86">
+        <v>9600</v>
+      </c>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15">
+        <v>96500</v>
+      </c>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15">
+        <v>96500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A11" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" s="15">
+        <v>32300</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="86"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15">
+        <v>32300</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15">
+        <v>32300</v>
+      </c>
+      <c r="L11" s="14"/>
+    </row>
+    <row r="12" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A12" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15">
+        <v>8800</v>
+      </c>
+      <c r="D12" s="86" t="s">
+        <v>196</v>
+      </c>
+      <c r="E12" s="15"/>
+      <c r="F12" s="86">
+        <v>3680</v>
+      </c>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15">
+        <v>12480</v>
+      </c>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15">
+        <v>12480</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A13" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A14" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A15" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32">
-        <v>360</v>
-      </c>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A16" s="32" t="s">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15">
+        <v>16400</v>
+      </c>
+      <c r="D13" s="86"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15">
+        <v>16400</v>
+      </c>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15">
+        <v>16400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A14" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A17" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A18" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="B18" s="32" t="s">
+      <c r="B14" s="15"/>
+      <c r="C14" s="15">
+        <v>64000</v>
+      </c>
+      <c r="D14" s="86"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15">
+        <v>64000</v>
+      </c>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15">
+        <v>64000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A15" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15">
+        <v>236950</v>
+      </c>
+      <c r="D15" s="86"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15">
+        <v>236950</v>
+      </c>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15">
+        <v>236950</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A16" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="B16" s="15">
+        <v>86500</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15">
+        <v>86500</v>
+      </c>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15">
+        <v>86500</v>
+      </c>
+      <c r="L16" s="14"/>
+    </row>
+    <row r="17" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A17" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15">
+        <v>262430</v>
+      </c>
+      <c r="D17" s="86" t="s">
+        <v>198</v>
+      </c>
+      <c r="E17" s="86">
+        <v>600</v>
+      </c>
+      <c r="F17" s="86"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15">
+        <v>261830</v>
+      </c>
+      <c r="I17" s="15"/>
+      <c r="J17" s="100">
+        <v>261830</v>
+      </c>
+      <c r="K17" s="15"/>
+      <c r="L17" s="14"/>
+    </row>
+    <row r="18" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A18" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15">
+        <v>14400</v>
+      </c>
+      <c r="D18" s="86"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15">
+        <v>14400</v>
+      </c>
+      <c r="I18" s="15"/>
+      <c r="J18" s="100">
+        <v>14400</v>
+      </c>
+      <c r="K18" s="15"/>
+      <c r="L18" s="14"/>
+    </row>
+    <row r="19" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A19" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="15">
+        <v>124600</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="86" t="s">
+        <v>194</v>
+      </c>
+      <c r="E19" s="86">
+        <v>2360</v>
+      </c>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15">
+        <v>126960</v>
+      </c>
+      <c r="H19" s="15"/>
+      <c r="I19" s="99">
+        <v>126960</v>
+      </c>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="14"/>
+    </row>
+    <row r="20" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A20" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="15">
+        <v>4520</v>
+      </c>
+      <c r="C20" s="15"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15">
+        <v>4520</v>
+      </c>
+      <c r="H20" s="15"/>
+      <c r="I20" s="99">
+        <v>4520</v>
+      </c>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="14"/>
+    </row>
+    <row r="21" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A21" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="15">
+        <v>3080</v>
+      </c>
+      <c r="C21" s="15"/>
+      <c r="D21" s="86" t="s">
+        <v>193</v>
+      </c>
+      <c r="E21" s="86">
+        <v>260</v>
+      </c>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15">
+        <v>3340</v>
+      </c>
+      <c r="H21" s="15"/>
+      <c r="I21" s="99">
+        <v>3340</v>
+      </c>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="14"/>
+    </row>
+    <row r="22" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A22" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="15">
+        <v>36480</v>
+      </c>
+      <c r="C22" s="15"/>
+      <c r="D22" s="86" t="s">
+        <v>195</v>
+      </c>
+      <c r="E22" s="86">
+        <v>1340</v>
+      </c>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15">
+        <v>37820</v>
+      </c>
+      <c r="H22" s="15"/>
+      <c r="I22" s="99">
+        <v>37820</v>
+      </c>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="14"/>
+    </row>
+    <row r="23" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="15"/>
+      <c r="B23" s="93">
+        <f>SUM(B5:B22)</f>
+        <v>689880</v>
+      </c>
+      <c r="C23" s="93">
+        <f>SUM(C5:C22)</f>
+        <v>689880</v>
+      </c>
+      <c r="D23" s="96"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="14"/>
+    </row>
+    <row r="24" spans="1:12" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B24" s="92"/>
+      <c r="C24" s="92"/>
+      <c r="D24" s="97" t="s">
+        <v>196</v>
+      </c>
+      <c r="E24" s="86">
+        <v>9600</v>
+      </c>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15">
+        <v>9600</v>
+      </c>
+      <c r="H24" s="15"/>
+      <c r="I24" s="99">
+        <v>9600</v>
+      </c>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="14"/>
+    </row>
+    <row r="25" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A25" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="97" t="s">
+        <v>196</v>
+      </c>
+      <c r="E25" s="86">
+        <v>3680</v>
+      </c>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15">
+        <v>3680</v>
+      </c>
+      <c r="H25" s="15"/>
+      <c r="I25" s="99">
+        <v>3680</v>
+      </c>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="14"/>
+    </row>
+    <row r="26" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A26" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="98" t="s">
+        <v>193</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="86">
+        <v>260</v>
+      </c>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15">
+        <v>260</v>
+      </c>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A27" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="86" t="s">
+        <v>194</v>
+      </c>
+      <c r="E27" s="15"/>
+      <c r="F27" s="86">
+        <v>2360</v>
+      </c>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15">
+        <v>2360</v>
+      </c>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A28" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="86" t="s">
+        <v>199</v>
+      </c>
+      <c r="E28" s="15"/>
+      <c r="F28" s="86">
+        <v>4820</v>
+      </c>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15">
+        <v>4820</v>
+      </c>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15">
+        <v>4820</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A29" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="86" t="s">
+        <v>198</v>
+      </c>
+      <c r="E29" s="86"/>
+      <c r="F29" s="86">
+        <v>600</v>
+      </c>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15">
+        <v>600</v>
+      </c>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A30" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="86" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" s="86">
+        <v>4820</v>
+      </c>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15">
+        <v>4820</v>
+      </c>
+      <c r="H30" s="15"/>
+      <c r="I30" s="99">
+        <v>4820</v>
+      </c>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="14"/>
+    </row>
+    <row r="31" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="86"/>
+      <c r="E31" s="93">
+        <f t="shared" ref="E31:L31" si="0">SUM(E5:E30)</f>
+        <v>22660</v>
+      </c>
+      <c r="F31" s="93">
+        <f t="shared" si="0"/>
+        <v>22660</v>
+      </c>
+      <c r="G31" s="93">
+        <f t="shared" si="0"/>
+        <v>710600</v>
+      </c>
+      <c r="H31" s="93">
+        <f t="shared" si="0"/>
+        <v>710600</v>
+      </c>
+      <c r="I31" s="15">
+        <f t="shared" si="0"/>
+        <v>190740</v>
+      </c>
+      <c r="J31" s="15">
+        <f t="shared" si="0"/>
+        <v>276230</v>
+      </c>
+      <c r="K31" s="15">
+        <f t="shared" si="0"/>
+        <v>519860</v>
+      </c>
+      <c r="L31" s="95">
+        <f t="shared" si="0"/>
+        <v>434370</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="K18" s="32"/>
-    </row>
-    <row r="19" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A19" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32" t="s">
-        <v>122</v>
-      </c>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32" t="s">
-        <v>144</v>
-      </c>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-    </row>
-    <row r="20" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A20" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="32" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="F20" s="32">
-        <v>1075</v>
-      </c>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32">
-        <v>1075</v>
-      </c>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-    </row>
-    <row r="21" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A21" s="32"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-    </row>
-    <row r="22" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A22" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="B22" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-    </row>
-    <row r="23" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A23" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="B23" s="32">
-        <v>760</v>
-      </c>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32">
-        <v>760</v>
-      </c>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32">
-        <v>760</v>
-      </c>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-    </row>
-    <row r="24" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A24" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="B24" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-    </row>
-    <row r="25" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A25" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="B25" s="32" t="s">
-        <v>151</v>
-      </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32" t="s">
-        <v>152</v>
-      </c>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-    </row>
-    <row r="26" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-    </row>
-    <row r="27" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A27" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32">
-        <v>720</v>
-      </c>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32">
-        <v>720</v>
-      </c>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-    </row>
-    <row r="28" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A28" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32" t="s">
-        <v>156</v>
-      </c>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32" t="s">
-        <v>156</v>
-      </c>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-    </row>
-    <row r="29" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A29" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-    </row>
-    <row r="30" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A30" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32">
-        <v>585</v>
-      </c>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="32">
-        <v>585</v>
-      </c>
-      <c r="K30" s="32"/>
-    </row>
-    <row r="31" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A31" s="32"/>
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
-    </row>
-    <row r="32" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A32" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32">
-        <v>220</v>
-      </c>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A33" s="32" t="s">
-        <v>128</v>
-      </c>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32">
-        <v>320</v>
-      </c>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A34" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32">
-        <v>980</v>
-      </c>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A35" s="32"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
-      <c r="H35" s="32">
-        <v>106745</v>
-      </c>
-      <c r="I35" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="J35" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="K35" s="32" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="92"/>
+      <c r="G32" s="92"/>
+      <c r="H32" s="92"/>
+      <c r="I32" s="15">
+        <v>85490</v>
+      </c>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15">
+        <v>85490</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="93">
+        <f>SUM(I31:I32)</f>
+        <v>276230</v>
+      </c>
+      <c r="J33" s="93">
+        <f>SUM(J31)</f>
+        <v>276230</v>
+      </c>
+      <c r="K33" s="93">
+        <f>SUM(K31)</f>
+        <v>519860</v>
+      </c>
+      <c r="L33" s="93">
+        <f>SUM(L31:L32)</f>
+        <v>519860</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="92"/>
+      <c r="J34" s="92"/>
+      <c r="K34" s="92"/>
+      <c r="L34" s="104"/>
+    </row>
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="14"/>
+    </row>
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A36" s="32"/>
       <c r="B36" s="32"/>
       <c r="C36" s="32"/>
@@ -7276,26 +9480,20 @@
       <c r="J36" s="32"/>
       <c r="K36" s="32"/>
     </row>
-    <row r="37" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A37" s="32" t="s">
-        <v>129</v>
-      </c>
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A37" s="32"/>
       <c r="B37" s="32"/>
       <c r="C37" s="32"/>
       <c r="D37" s="32"/>
       <c r="E37" s="32"/>
       <c r="F37" s="32"/>
       <c r="G37" s="32"/>
-      <c r="H37" s="32">
-        <v>51315</v>
-      </c>
+      <c r="H37" s="32"/>
       <c r="I37" s="32"/>
       <c r="J37" s="32"/>
-      <c r="K37" s="32">
-        <v>51315</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
+      <c r="K37" s="32"/>
+    </row>
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A38" s="32"/>
       <c r="B38" s="32"/>
       <c r="C38" s="32"/>
@@ -7308,42 +9506,64 @@
       <c r="J38" s="32"/>
       <c r="K38" s="32"/>
     </row>
-    <row r="39" spans="1:11" ht="16.899999999999999" x14ac:dyDescent="0.65">
-      <c r="A39" s="32" t="s">
-        <v>167</v>
-      </c>
-      <c r="B39" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="C39" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="D39" s="32">
-        <v>14925</v>
-      </c>
-      <c r="E39" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="F39" s="32" t="s">
-        <v>164</v>
-      </c>
-      <c r="G39" s="32" t="s">
-        <v>164</v>
-      </c>
-      <c r="H39" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="I39" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="J39" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="K39" s="32" t="s">
-        <v>165</v>
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A39" s="32"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H40" s="85" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H41" s="85" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H42" s="85" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H43" s="85" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H44" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H45" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G2:H2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/ACCY122/Session/S04/ACCY122 L4 Workbook.xlsx
+++ b/ACCY122/Session/S04/ACCY122 L4 Workbook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ACCY122\Session\S04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Session/S04/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF30FBF8-C934-4FFC-9F92-76FF30587EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004DB084-40DA-2645-AE0F-FE0158965D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{49300C88-9C68-40D1-BFDB-69B44FEEA068}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28940" windowHeight="18660" activeTab="4" xr2:uid="{49300C88-9C68-40D1-BFDB-69B44FEEA068}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="1" r:id="rId1"/>
@@ -71,8 +71,53 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={5E6F0BD9-910C-3F4C-936F-7857EBDF45EA}</author>
+    <author>tc={71876D82-1589-504B-B11D-5D75376CA001}</author>
+    <author>tc={2CB53C99-BE85-0445-8EC8-5631CA238D88}</author>
+    <author>tc={422ADACF-04A8-654A-96A7-E4089914C09C}</author>
+  </authors>
+  <commentList>
+    <comment ref="O19" authorId="0" shapeId="0" xr:uid="{5E6F0BD9-910C-3F4C-936F-7857EBDF45EA}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Drawings</t>
+      </text>
+    </comment>
+    <comment ref="M20" authorId="1" shapeId="0" xr:uid="{71876D82-1589-504B-B11D-5D75376CA001}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Total Revenue</t>
+      </text>
+    </comment>
+    <comment ref="L33" authorId="2" shapeId="0" xr:uid="{2CB53C99-BE85-0445-8EC8-5631CA238D88}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Total Expense</t>
+      </text>
+    </comment>
+    <comment ref="P34" authorId="3" shapeId="0" xr:uid="{422ADACF-04A8-654A-96A7-E4089914C09C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Profit &amp; Loss</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="240">
   <si>
     <t>Balanced Day Adjustments</t>
   </si>
@@ -612,9 +657,6 @@
   </si>
   <si>
     <t xml:space="preserve">PRACTICE </t>
-  </si>
-  <si>
-    <t>ref 6</t>
   </si>
   <si>
     <t>Acc. Depn – Building</t>
@@ -729,35 +771,113 @@
     <t>Income Statement</t>
   </si>
   <si>
-    <t>We still need to record the expense because it belongs to June.</t>
-  </si>
-  <si>
-    <t>Expense ($320 telecommunications) has been incurred in June</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dr Teleco Expense     320  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Cr Telco Expenses Payable    320  </t>
-  </si>
-  <si>
-    <t>Used but not billed → Accrued expense</t>
-  </si>
-  <si>
-    <t>Paid but not used → Unearned (prepaid)</t>
-  </si>
-  <si>
-    <t>ref 5</t>
-  </si>
-  <si>
-    <t>there is nothing to adjust for the princiapl since it hasnt been paid only if it says it is paid but not recorded</t>
+    <t>in bal sheet, we don’t put expense</t>
+  </si>
+  <si>
+    <t>only asset, liability, ending capital</t>
+  </si>
+  <si>
+    <t>income statement and bal sheet no dr/cr</t>
+  </si>
+  <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>REV</t>
+  </si>
+  <si>
+    <t>are closing entries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANSWER </t>
+  </si>
+  <si>
+    <t>4 STEPS TO CLOSE ENTRIES</t>
+  </si>
+  <si>
+    <t>1. Reset Revenue Account to 0</t>
+  </si>
+  <si>
+    <t>2. Reset Expense Account to 0</t>
+  </si>
+  <si>
+    <t>3. Transfer Profit/Loss to Capital Account</t>
+  </si>
+  <si>
+    <t>4. Close Drawings</t>
+  </si>
+  <si>
+    <t>Note:</t>
+  </si>
+  <si>
+    <t>General Journal</t>
+  </si>
+  <si>
+    <t>DR ($)</t>
+  </si>
+  <si>
+    <t>CR ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profit &amp; Loss Summary </t>
+  </si>
+  <si>
+    <t>158 060</t>
+  </si>
+  <si>
+    <t>(Close revenue accounts)</t>
+  </si>
+  <si>
+    <t>Depreciation Expense – Building </t>
+  </si>
+  <si>
+    <t>Depreciation Expense – Office Equipment </t>
+  </si>
+  <si>
+    <t>8 760</t>
+  </si>
+  <si>
+    <t>2 140</t>
+  </si>
+  <si>
+    <t>88 920</t>
+  </si>
+  <si>
+    <t>2 310</t>
+  </si>
+  <si>
+    <t>(Close expense accounts)</t>
+  </si>
+  <si>
+    <t>(Transfer P/L to Capital)</t>
+  </si>
+  <si>
+    <t>52 780</t>
+  </si>
+  <si>
+    <t>(Close drawings account)</t>
+  </si>
+  <si>
+    <t>now P/L summary account becomes 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Profit or Loss Summary account is a temporary account used at </t>
+  </si>
+  <si>
+    <t>the end of an accounting period to close revenue and expense accounts</t>
+  </si>
+  <si>
+    <t>Profit → Credit balance in P&amp;L Summary</t>
+  </si>
+  <si>
+    <t>Loss → Debit balance in P&amp;L Summary</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -865,13 +985,52 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial Black"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -935,12 +1094,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89999084444715716"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1281,7 +1434,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1456,7 +1609,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1473,26 +1625,10 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1504,6 +1640,69 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1550,8 +1749,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1029211" y="656694"/>
-          <a:ext cx="5413202" cy="5884404"/>
+          <a:off x="1089950" y="648411"/>
+          <a:ext cx="5959855" cy="5798817"/>
           <a:chOff x="0" y="78429"/>
           <a:chExt cx="6059328" cy="3928254"/>
         </a:xfrm>
@@ -2237,23 +2436,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>574722</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>202284</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>577905</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>84250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>192825</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>89192</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>470328</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>3882</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95DFACB0-0F5D-E299-816B-F625469737B2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92B13879-F6FF-D94E-B666-157FFCA93B4A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2276,8 +2475,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="11827829" y="1794320"/>
-          <a:ext cx="7578282" cy="2336193"/>
+          <a:off x="15160624" y="295917"/>
+          <a:ext cx="8742051" cy="2303667"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2357,6 +2556,7 @@
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Manek Mukesh" id="{D1B72572-4EE9-4B5D-AA50-003122841091}" userId="7baad15b6bef9919" providerId="Windows Live"/>
+  <person displayName="Joseph Koh" id="{B9C67BA8-3942-E14F-8EA7-6B64E0EF8E63}" userId="cf4f27787168282d" providerId="Windows Live"/>
 </personList>
 </file>
 
@@ -2687,10 +2887,27 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="O19" dT="2026-04-20T04:18:45.63" personId="{B9C67BA8-3942-E14F-8EA7-6B64E0EF8E63}" id="{5E6F0BD9-910C-3F4C-936F-7857EBDF45EA}">
+    <text>Drawings</text>
+  </threadedComment>
+  <threadedComment ref="M20" dT="2026-04-20T04:17:57.80" personId="{B9C67BA8-3942-E14F-8EA7-6B64E0EF8E63}" id="{71876D82-1589-504B-B11D-5D75376CA001}">
+    <text>Total Revenue</text>
+  </threadedComment>
+  <threadedComment ref="L33" dT="2026-04-20T04:17:02.30" personId="{B9C67BA8-3942-E14F-8EA7-6B64E0EF8E63}" id="{2CB53C99-BE85-0445-8EC8-5631CA238D88}">
+    <text>Total Expense</text>
+  </threadedComment>
+  <threadedComment ref="P34" dT="2026-04-20T04:18:22.22" personId="{B9C67BA8-3942-E14F-8EA7-6B64E0EF8E63}" id="{422ADACF-04A8-654A-96A7-E4089914C09C}">
+    <text>Profit &amp; Loss</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3154719-4B7A-4BD1-A273-F4DC249F84D4}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2700,27 +2917,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F923618A-53E6-4AA0-84BA-AB41705F9398}">
   <dimension ref="B1:O20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.2">
       <c r="G1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F3" t="s">
         <v>2</v>
       </c>
@@ -2737,7 +2954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2755,7 +2972,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="2" t="s">
@@ -2769,8 +2986,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C6" s="109" t="s">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C6" s="102" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="1"/>
@@ -2797,8 +3014,8 @@
       </c>
       <c r="O6" s="7"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C7" s="109"/>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C7" s="102"/>
       <c r="D7" s="1"/>
       <c r="E7" s="2" t="s">
         <v>11</v>
@@ -2810,8 +3027,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C8" s="109"/>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C8" s="102"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
         <v>21</v>
@@ -2824,8 +3041,8 @@
       </c>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C9" s="109"/>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C9" s="102"/>
       <c r="D9" s="1"/>
       <c r="E9" s="2" t="s">
         <v>11</v>
@@ -2833,8 +3050,8 @@
       <c r="M9" s="6"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C10" s="109"/>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="C10" s="102"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
         <v>23</v>
@@ -2862,7 +3079,7 @@
       </c>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -2882,7 +3099,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="2" t="s">
@@ -2899,7 +3116,7 @@
       </c>
       <c r="O12" s="7"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>32</v>
       </c>
@@ -2916,7 +3133,7 @@
       <c r="M13" s="6"/>
       <c r="O13" s="7"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
       <c r="F14" t="s">
         <v>114</v>
       </c>
@@ -2934,7 +3151,7 @@
       </c>
       <c r="O14" s="7"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="M15" s="6" t="s">
         <v>36</v>
       </c>
@@ -2942,17 +3159,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
       <c r="M16" s="6" t="s">
         <v>37</v>
       </c>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="11:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="11:15" x14ac:dyDescent="0.2">
       <c r="M17" s="6"/>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" spans="11:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="11:15" x14ac:dyDescent="0.2">
       <c r="K18">
         <v>4</v>
       </c>
@@ -2967,7 +3184,7 @@
       </c>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" spans="11:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="11:15" x14ac:dyDescent="0.2">
       <c r="M19" s="6" t="s">
         <v>40</v>
       </c>
@@ -2975,7 +3192,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="11:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="11:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="M20" s="11" t="s">
         <v>41</v>
       </c>
@@ -2996,13 +3213,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC50BE0-433C-401E-8C60-EBD47C86025A}">
   <dimension ref="A1:M35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="18.140625" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B1" s="3"/>
       <c r="C1" s="4" t="s">
         <v>15</v>
@@ -3013,7 +3230,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -3030,7 +3247,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3044,14 +3261,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="6"/>
       <c r="E4" s="7"/>
       <c r="G4" s="72" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -3060,11 +3277,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="6"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
@@ -3078,14 +3295,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B8" s="6"/>
       <c r="E8" s="7"/>
       <c r="G8" s="72" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11"/>
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
@@ -3094,11 +3311,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="6"/>
       <c r="E10" s="7"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>3</v>
       </c>
@@ -3112,7 +3329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="6"/>
       <c r="E12" s="7"/>
       <c r="G12" s="72" t="s">
@@ -3121,7 +3338,7 @@
       <c r="H12" s="71"/>
       <c r="I12" s="71"/>
     </row>
-    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
@@ -3130,11 +3347,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="6"/>
       <c r="E14" s="7"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>4</v>
       </c>
@@ -3148,7 +3365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="6"/>
       <c r="E16" s="7"/>
       <c r="G16" s="72" t="s">
@@ -3157,7 +3374,7 @@
       <c r="H16" s="71"/>
       <c r="I16" s="71"/>
     </row>
-    <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="11"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -3166,11 +3383,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="6"/>
       <c r="E18" s="7"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>5</v>
       </c>
@@ -3182,7 +3399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B20" s="6"/>
       <c r="E20" s="7"/>
       <c r="G20" s="72" t="s">
@@ -3191,21 +3408,21 @@
       <c r="H20" s="71"/>
       <c r="I20" s="71"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B21" s="6"/>
       <c r="E21" s="7"/>
       <c r="G21" s="72">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B22" s="11"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
       <c r="E22" s="13"/>
     </row>
-    <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>6</v>
       </c>
@@ -3219,7 +3436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B25" s="6"/>
       <c r="E25" s="7"/>
       <c r="G25" s="72" t="s">
@@ -3228,7 +3445,7 @@
       <c r="H25" s="71"/>
       <c r="I25" s="71"/>
     </row>
-    <row r="26" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="11"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
@@ -3237,8 +3454,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>7</v>
       </c>
@@ -3252,7 +3469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B29" s="6"/>
       <c r="E29" s="4"/>
       <c r="G29" s="72" t="s">
@@ -3261,7 +3478,7 @@
       <c r="H29" s="71"/>
       <c r="I29" s="71"/>
     </row>
-    <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B30" s="11"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
@@ -3270,8 +3487,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="G32">
         <v>1</v>
       </c>
@@ -3289,7 +3506,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="7:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:13" x14ac:dyDescent="0.2">
       <c r="G33">
         <v>2</v>
       </c>
@@ -3309,7 +3526,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="7:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G34">
         <v>3</v>
       </c>
@@ -3329,7 +3546,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="7:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:13" x14ac:dyDescent="0.2">
       <c r="G35">
         <v>4</v>
       </c>
@@ -3348,34 +3565,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{431369FE-F92F-4C37-9408-0538561CEBA7}">
   <dimension ref="A1:U74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.5703125" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" customWidth="1"/>
-    <col min="7" max="7" width="27.140625" customWidth="1"/>
-    <col min="8" max="8" width="2.7109375" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="31.5" customWidth="1"/>
+    <col min="2" max="2" width="6.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13.1640625" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" customWidth="1"/>
+    <col min="7" max="7" width="27.1640625" customWidth="1"/>
+    <col min="8" max="8" width="2.6640625" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="19" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" customWidth="1"/>
-    <col min="14" max="14" width="2.28515625" customWidth="1"/>
+    <col min="13" max="13" width="14.5" customWidth="1"/>
+    <col min="14" max="14" width="2.33203125" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="11.5703125" customWidth="1"/>
-    <col min="18" max="18" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.5703125" customWidth="1"/>
-    <col min="20" max="21" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5" customWidth="1"/>
+    <col min="18" max="18" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.5" customWidth="1"/>
+    <col min="20" max="21" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
       <c r="B1" s="14"/>
     </row>
-    <row r="2" spans="1:21" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="22" t="s">
         <v>42</v>
       </c>
@@ -3411,7 +3628,7 @@
       </c>
       <c r="P2" s="40"/>
     </row>
-    <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>43</v>
       </c>
@@ -3433,7 +3650,7 @@
       <c r="O3" s="47"/>
       <c r="P3" s="45"/>
     </row>
-    <row r="4" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>44</v>
       </c>
@@ -3476,7 +3693,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
         <v>47</v>
       </c>
@@ -3517,7 +3734,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="27" t="s">
         <v>48</v>
       </c>
@@ -3561,7 +3778,7 @@
       </c>
       <c r="U6" s="63"/>
     </row>
-    <row r="7" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
         <v>49</v>
       </c>
@@ -3603,7 +3820,7 @@
         <v>126500</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="27" t="s">
         <v>50</v>
       </c>
@@ -3638,7 +3855,7 @@
       <c r="T8" s="65"/>
       <c r="U8" s="66"/>
     </row>
-    <row r="9" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:21" ht="35" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="27" t="s">
         <v>51</v>
       </c>
@@ -3675,7 +3892,7 @@
       <c r="T9" s="32"/>
       <c r="U9" s="32"/>
     </row>
-    <row r="10" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="27" t="s">
         <v>123</v>
       </c>
@@ -3715,7 +3932,7 @@
       </c>
       <c r="U10" s="62"/>
     </row>
-    <row r="11" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
         <v>52</v>
       </c>
@@ -3752,7 +3969,7 @@
         <v>63510</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="27" t="s">
         <v>53</v>
       </c>
@@ -3789,7 +4006,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="30" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
         <v>54</v>
       </c>
@@ -3826,7 +4043,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="27" t="s">
         <v>55</v>
       </c>
@@ -3867,7 +4084,7 @@
         <v>7520</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
         <v>56</v>
       </c>
@@ -3904,7 +4121,7 @@
         <v>4235</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="27" t="s">
         <v>57</v>
       </c>
@@ -3941,7 +4158,7 @@
         <v>3045</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="27" t="s">
         <v>58</v>
       </c>
@@ -3978,7 +4195,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
         <v>59</v>
       </c>
@@ -4019,7 +4236,7 @@
         <v>4940</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="27" t="s">
         <v>60</v>
       </c>
@@ -4060,7 +4277,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="27" t="s">
         <v>61</v>
       </c>
@@ -4103,7 +4320,7 @@
         <v>7400</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="27"/>
       <c r="B21" s="28"/>
       <c r="C21" s="15"/>
@@ -4125,7 +4342,7 @@
       <c r="T21" s="32"/>
       <c r="U21" s="32"/>
     </row>
-    <row r="22" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="30" t="s">
         <v>69</v>
       </c>
@@ -4168,7 +4385,7 @@
       </c>
       <c r="U22" s="62"/>
     </row>
-    <row r="23" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="30" t="s">
         <v>70</v>
       </c>
@@ -4208,7 +4425,7 @@
         <v>29555</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="30" t="s">
         <v>71</v>
       </c>
@@ -4245,7 +4462,7 @@
       <c r="T24" s="65"/>
       <c r="U24" s="66"/>
     </row>
-    <row r="25" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="30" t="s">
         <v>72</v>
       </c>
@@ -4280,7 +4497,7 @@
       <c r="T25" s="32"/>
       <c r="U25" s="32"/>
     </row>
-    <row r="26" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A26" s="30" t="s">
         <v>73</v>
       </c>
@@ -4321,7 +4538,7 @@
       </c>
       <c r="U26" s="62"/>
     </row>
-    <row r="27" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A27" s="30" t="s">
         <v>74</v>
       </c>
@@ -4361,7 +4578,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="30" t="s">
         <v>75</v>
       </c>
@@ -4398,7 +4615,7 @@
       <c r="T28" s="12"/>
       <c r="U28" s="13"/>
     </row>
-    <row r="29" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>125</v>
       </c>
@@ -4423,7 +4640,7 @@
         <v>29555</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:21" ht="17" x14ac:dyDescent="0.25">
       <c r="A30" s="32"/>
       <c r="B30" s="29"/>
       <c r="C30" s="15"/>
@@ -4441,7 +4658,7 @@
       <c r="O30" s="52"/>
       <c r="P30" s="53"/>
     </row>
-    <row r="31" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
         <v>68</v>
       </c>
@@ -4491,18 +4708,18 @@
         <v>118860</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="L32">
         <f>M31-L31</f>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A44" s="85" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="22" t="s">
         <v>42</v>
       </c>
@@ -4538,7 +4755,7 @@
       </c>
       <c r="P45" s="40"/>
     </row>
-    <row r="46" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A46" s="22" t="s">
         <v>43</v>
       </c>
@@ -4560,7 +4777,7 @@
       <c r="O46" s="47"/>
       <c r="P46" s="45"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" ht="17" x14ac:dyDescent="0.2">
       <c r="A47" s="25" t="s">
         <v>44</v>
       </c>
@@ -4600,7 +4817,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A48" s="27" t="s">
         <v>47</v>
       </c>
@@ -4629,7 +4846,7 @@
       </c>
       <c r="P48" s="53"/>
     </row>
-    <row r="49" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
         <v>48</v>
       </c>
@@ -4662,7 +4879,7 @@
       </c>
       <c r="P49" s="53"/>
     </row>
-    <row r="50" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A50" s="27" t="s">
         <v>49</v>
       </c>
@@ -4695,7 +4912,7 @@
       </c>
       <c r="P50" s="53"/>
     </row>
-    <row r="51" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A51" s="27" t="s">
         <v>50</v>
       </c>
@@ -4724,7 +4941,7 @@
       </c>
       <c r="P51" s="53"/>
     </row>
-    <row r="52" spans="1:16" ht="30" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:16" ht="34" x14ac:dyDescent="0.25">
       <c r="A52" s="27" t="s">
         <v>51</v>
       </c>
@@ -4757,7 +4974,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A53" s="27" t="s">
         <v>123</v>
       </c>
@@ -4786,7 +5003,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A54" s="27" t="s">
         <v>52</v>
       </c>
@@ -4815,7 +5032,7 @@
         <v>15540</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A55" s="27" t="s">
         <v>53</v>
       </c>
@@ -4844,7 +5061,7 @@
       </c>
       <c r="P55" s="53"/>
     </row>
-    <row r="56" spans="1:16" ht="30" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A56" s="27" t="s">
         <v>54</v>
       </c>
@@ -4873,7 +5090,7 @@
       <c r="O56" s="52"/>
       <c r="P56" s="53"/>
     </row>
-    <row r="57" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A57" s="27" t="s">
         <v>55</v>
       </c>
@@ -4906,7 +5123,7 @@
       <c r="O57" s="52"/>
       <c r="P57" s="53"/>
     </row>
-    <row r="58" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A58" s="27" t="s">
         <v>56</v>
       </c>
@@ -4935,7 +5152,7 @@
       <c r="O58" s="52"/>
       <c r="P58" s="53"/>
     </row>
-    <row r="59" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A59" s="27" t="s">
         <v>57</v>
       </c>
@@ -4964,7 +5181,7 @@
       <c r="O59" s="52"/>
       <c r="P59" s="53"/>
     </row>
-    <row r="60" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A60" s="27" t="s">
         <v>58</v>
       </c>
@@ -4993,7 +5210,7 @@
       <c r="O60" s="52"/>
       <c r="P60" s="53"/>
     </row>
-    <row r="61" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A61" s="27" t="s">
         <v>59</v>
       </c>
@@ -5026,7 +5243,7 @@
       <c r="O61" s="52"/>
       <c r="P61" s="53"/>
     </row>
-    <row r="62" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A62" s="27" t="s">
         <v>60</v>
       </c>
@@ -5059,7 +5276,7 @@
       <c r="O62" s="52"/>
       <c r="P62" s="53"/>
     </row>
-    <row r="63" spans="1:16" ht="30" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A63" s="27" t="s">
         <v>61</v>
       </c>
@@ -5094,7 +5311,7 @@
       <c r="O63" s="52"/>
       <c r="P63" s="53"/>
     </row>
-    <row r="64" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A64" s="27"/>
       <c r="B64" s="28"/>
       <c r="C64" s="15"/>
@@ -5112,7 +5329,7 @@
       <c r="O64" s="52"/>
       <c r="P64" s="53"/>
     </row>
-    <row r="65" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A65" s="30" t="s">
         <v>69</v>
       </c>
@@ -5143,7 +5360,7 @@
       <c r="O65" s="52"/>
       <c r="P65" s="53"/>
     </row>
-    <row r="66" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A66" s="30" t="s">
         <v>70</v>
       </c>
@@ -5174,7 +5391,7 @@
       <c r="O66" s="52"/>
       <c r="P66" s="53"/>
     </row>
-    <row r="67" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A67" s="30" t="s">
         <v>71</v>
       </c>
@@ -5205,7 +5422,7 @@
       <c r="O67" s="52"/>
       <c r="P67" s="53"/>
     </row>
-    <row r="68" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A68" s="30" t="s">
         <v>72</v>
       </c>
@@ -5236,7 +5453,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A69" s="30" t="s">
         <v>73</v>
       </c>
@@ -5267,7 +5484,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A70" s="30" t="s">
         <v>74</v>
       </c>
@@ -5298,7 +5515,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A71" s="30" t="s">
         <v>75</v>
       </c>
@@ -5329,7 +5546,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="72" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A72" s="15" t="s">
         <v>125</v>
       </c>
@@ -5354,7 +5571,7 @@
         <v>29555</v>
       </c>
     </row>
-    <row r="73" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:16" ht="17" x14ac:dyDescent="0.25">
       <c r="A73" s="32"/>
       <c r="B73" s="29"/>
       <c r="C73" s="15"/>
@@ -5372,7 +5589,7 @@
       <c r="O73" s="52"/>
       <c r="P73" s="53"/>
     </row>
-    <row r="74" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="15" t="s">
         <v>68</v>
       </c>
@@ -5424,163 +5641,150 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451FE678-24D7-4F17-8C17-332E4659A9B1}">
-  <dimension ref="A1:T76"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451FE678-24D7-4F17-8C17-332E4659A9B1}">
+  <dimension ref="A1:W76"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.42578125" style="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="37.5" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5" style="32" customWidth="1"/>
     <col min="3" max="3" width="17" style="32" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="32" customWidth="1"/>
-    <col min="6" max="7" width="9.140625" style="32"/>
-    <col min="8" max="8" width="3.5703125" style="32" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="32" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="32" customWidth="1"/>
-    <col min="11" max="11" width="3.140625" style="32" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" style="32" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="32" customWidth="1"/>
-    <col min="14" max="14" width="3.28515625" style="32" customWidth="1"/>
-    <col min="15" max="15" width="15.7109375" style="32" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" style="32" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="32"/>
+    <col min="4" max="4" width="14.5" style="32" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="32" customWidth="1"/>
+    <col min="6" max="7" width="9.1640625" style="32" customWidth="1"/>
+    <col min="8" max="8" width="3.5" style="32" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" style="32" customWidth="1"/>
+    <col min="10" max="10" width="13.5" style="32" customWidth="1"/>
+    <col min="11" max="11" width="3.1640625" style="32" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" style="32" customWidth="1"/>
+    <col min="14" max="14" width="3.33203125" style="32" customWidth="1"/>
+    <col min="15" max="15" width="15.6640625" style="32" customWidth="1"/>
+    <col min="16" max="16" width="14.1640625" style="32" customWidth="1"/>
+    <col min="17" max="17" width="9.1640625" style="32"/>
+    <col min="18" max="18" width="14.83203125" style="32" customWidth="1"/>
+    <col min="19" max="16384" width="9.1640625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="88" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="19" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="19" t="s">
+      <c r="D2" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="20"/>
+      <c r="F2" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="21"/>
-    </row>
-    <row r="2" spans="1:16" ht="42.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="107" t="s">
-        <v>63</v>
-      </c>
-      <c r="D2" s="108"/>
-      <c r="E2" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="F2" s="19"/>
       <c r="G2" s="19"/>
       <c r="H2" s="19"/>
-      <c r="I2" s="107" t="s">
+      <c r="I2" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="J2" s="108"/>
       <c r="K2" s="19"/>
-      <c r="L2" s="105" t="s">
-        <v>206</v>
-      </c>
-      <c r="M2" s="106"/>
+      <c r="L2" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M2" s="21" t="s">
+        <v>66</v>
+      </c>
       <c r="N2" s="21"/>
-      <c r="O2" s="107" t="s">
+      <c r="O2" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="P2" s="108"/>
-    </row>
-    <row r="3" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A3" s="17" t="s">
+      <c r="P2" s="21"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="15"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="21"/>
+    </row>
+    <row r="4" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="20" t="s">
+      <c r="B4" s="15"/>
+      <c r="C4" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D4" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="101"/>
-      <c r="F3" s="20" t="s">
+      <c r="E4" s="20"/>
+      <c r="F4" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G4" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20" t="s">
+      <c r="H4" s="20"/>
+      <c r="I4" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J4" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="20" t="s">
+      <c r="K4" s="21"/>
+      <c r="L4" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="M3" s="20" t="s">
+      <c r="M4" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20" t="s">
+      <c r="N4" s="20"/>
+      <c r="O4" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="P3" s="20" t="s">
+      <c r="P4" s="20" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A4" s="17" t="s">
+    <row r="5" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
         <v>77</v>
-      </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15">
-        <v>5200</v>
-      </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15">
-        <v>5200</v>
-      </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15">
-        <v>5200</v>
-      </c>
-      <c r="P4" s="15"/>
-    </row>
-    <row r="5" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A5" s="17" t="s">
-        <v>95</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="15">
-        <v>9260</v>
+        <v>5200</v>
       </c>
       <c r="D5" s="15"/>
-      <c r="E5" s="86"/>
+      <c r="E5" s="15"/>
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
       <c r="I5" s="15">
-        <v>9260</v>
+        <v>5200</v>
       </c>
       <c r="J5" s="15"/>
       <c r="K5" s="15"/>
@@ -5588,25 +5792,25 @@
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
       <c r="O5" s="15">
-        <v>9260</v>
+        <v>5200</v>
       </c>
       <c r="P5" s="15"/>
     </row>
-    <row r="6" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" ht="19" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="15">
-        <v>920</v>
+        <v>9260</v>
       </c>
       <c r="D6" s="15"/>
-      <c r="E6" s="86"/>
+      <c r="E6" s="15"/>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
       <c r="I6" s="15">
-        <v>920</v>
+        <v>9260</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
@@ -5614,31 +5818,25 @@
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
       <c r="O6" s="15">
+        <v>9260</v>
+      </c>
+      <c r="P6" s="15"/>
+    </row>
+    <row r="7" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15">
         <v>920</v>
       </c>
-      <c r="P6" s="15"/>
-    </row>
-    <row r="7" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A7" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="15">
-        <v>1140</v>
-      </c>
       <c r="D7" s="15"/>
-      <c r="E7" s="86">
-        <v>1</v>
-      </c>
+      <c r="E7" s="15"/>
       <c r="F7" s="15"/>
-      <c r="G7" s="86">
-        <v>720</v>
-      </c>
+      <c r="G7" s="15"/>
       <c r="H7" s="15"/>
       <c r="I7" s="15">
-        <v>420</v>
+        <v>920</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
@@ -5646,25 +5844,31 @@
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
       <c r="O7" s="15">
-        <v>420</v>
+        <v>920</v>
       </c>
       <c r="P7" s="15"/>
     </row>
-    <row r="8" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" ht="19" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="15"/>
+        <v>78</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>117</v>
+      </c>
       <c r="C8" s="15">
-        <v>60000</v>
+        <v>1140</v>
       </c>
       <c r="D8" s="15"/>
-      <c r="E8" s="86"/>
+      <c r="E8" s="15">
+        <v>1</v>
+      </c>
       <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
+      <c r="G8" s="86">
+        <v>720</v>
+      </c>
       <c r="H8" s="15"/>
       <c r="I8" s="15">
-        <v>60000</v>
+        <v>420</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
@@ -5672,25 +5876,25 @@
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
       <c r="O8" s="15">
-        <v>60000</v>
+        <v>420</v>
       </c>
       <c r="P8" s="15"/>
     </row>
-    <row r="9" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" ht="19" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="15">
-        <v>152000</v>
+        <v>60000</v>
       </c>
       <c r="D9" s="15"/>
-      <c r="E9" s="86"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
       <c r="H9" s="15"/>
       <c r="I9" s="15">
-        <v>152000</v>
+        <v>60000</v>
       </c>
       <c r="J9" s="15"/>
       <c r="K9" s="15"/>
@@ -5698,114 +5902,112 @@
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
       <c r="O9" s="15">
+        <v>60000</v>
+      </c>
+      <c r="P9" s="15"/>
+    </row>
+    <row r="10" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15">
         <v>152000</v>
       </c>
-      <c r="P9" s="15"/>
-    </row>
-    <row r="10" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A10" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15">
-        <v>64000</v>
-      </c>
-      <c r="E10" s="86">
-        <v>3</v>
-      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
       <c r="F10" s="15"/>
-      <c r="G10" s="86">
-        <f>F26</f>
-        <v>8760</v>
-      </c>
+      <c r="G10" s="15"/>
       <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="90">
-        <v>72760</v>
-      </c>
+      <c r="I10" s="15">
+        <v>152000</v>
+      </c>
+      <c r="J10" s="15"/>
       <c r="K10" s="15"/>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="90">
+      <c r="O10" s="15">
+        <v>152000</v>
+      </c>
+      <c r="P10" s="15"/>
+    </row>
+    <row r="11" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+      <c r="A11" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15">
+        <v>64000</v>
+      </c>
+      <c r="E11" s="15">
+        <v>3</v>
+      </c>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86">
+        <v>8760</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="89">
         <v>72760</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A11" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15">
-        <v>23400</v>
-      </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="86"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15">
-        <v>23400</v>
-      </c>
-      <c r="J11" s="15"/>
       <c r="K11" s="15"/>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
-      <c r="O11" s="15">
+      <c r="O11" s="15"/>
+      <c r="P11" s="89">
+        <v>72760</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15">
         <v>23400</v>
       </c>
-      <c r="P11" s="15"/>
-    </row>
-    <row r="12" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A12" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15">
-        <v>6420</v>
-      </c>
-      <c r="E12" s="86">
-        <v>3</v>
-      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
       <c r="F12" s="15"/>
-      <c r="G12" s="86">
-        <f>F27</f>
-        <v>2140</v>
-      </c>
+      <c r="G12" s="86"/>
       <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15">
-        <v>8560</v>
-      </c>
+      <c r="I12" s="15">
+        <v>23400</v>
+      </c>
+      <c r="J12" s="15"/>
       <c r="K12" s="15"/>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15">
-        <v>8560</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="O12" s="15">
+        <v>23400</v>
+      </c>
+      <c r="P12" s="15"/>
+    </row>
+    <row r="13" spans="1:19" ht="19" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15">
-        <v>7960</v>
-      </c>
-      <c r="E13" s="86"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
+        <v>6420</v>
+      </c>
+      <c r="E13" s="15">
+        <v>3</v>
+      </c>
+      <c r="F13" s="86"/>
+      <c r="G13" s="86">
+        <v>2140</v>
+      </c>
       <c r="H13" s="15"/>
       <c r="I13" s="15"/>
       <c r="J13" s="15">
-        <v>7960</v>
+        <v>8560</v>
       </c>
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
@@ -5813,31 +6015,25 @@
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
       <c r="P13" s="15">
-        <v>7960</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+        <v>8560</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="19" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>121</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="B14" s="15"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15">
-        <v>1560</v>
-      </c>
-      <c r="E14" s="86">
-        <v>2</v>
-      </c>
-      <c r="F14" s="86">
-        <v>1200</v>
-      </c>
+        <v>7960</v>
+      </c>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
       <c r="G14" s="15"/>
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
       <c r="J14" s="15">
-        <v>360</v>
+        <v>7960</v>
       </c>
       <c r="K14" s="15"/>
       <c r="L14" s="15"/>
@@ -5845,25 +6041,35 @@
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
       <c r="P14" s="15">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+        <v>7960</v>
+      </c>
+      <c r="R14" s="109"/>
+      <c r="S14" s="32" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="19" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="B15" s="15"/>
+        <v>100</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>121</v>
+      </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15">
-        <v>2000</v>
-      </c>
-      <c r="E15" s="86"/>
-      <c r="F15" s="15"/>
+        <v>1560</v>
+      </c>
+      <c r="E15" s="15">
+        <v>2</v>
+      </c>
+      <c r="F15" s="86">
+        <v>1200</v>
+      </c>
       <c r="G15" s="15"/>
       <c r="H15" s="15"/>
       <c r="I15" s="15"/>
       <c r="J15" s="15">
-        <v>2000</v>
+        <v>360</v>
       </c>
       <c r="K15" s="15"/>
       <c r="L15" s="15"/>
@@ -5871,25 +6077,25 @@
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
       <c r="P15" s="15">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="19" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
       <c r="D16" s="15">
-        <v>88600</v>
-      </c>
-      <c r="E16" s="86"/>
+        <v>2000</v>
+      </c>
+      <c r="E16" s="15"/>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
       <c r="H16" s="15"/>
       <c r="I16" s="15"/>
       <c r="J16" s="15">
-        <v>88600</v>
+        <v>2000</v>
       </c>
       <c r="K16" s="15"/>
       <c r="L16" s="15"/>
@@ -5897,25 +6103,28 @@
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
       <c r="P16" s="15">
-        <v>88600</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
+        <v>2000</v>
+      </c>
+      <c r="R16" s="32" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="19" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15">
-        <v>71490</v>
-      </c>
-      <c r="E17" s="86"/>
+        <v>88600</v>
+      </c>
+      <c r="E17" s="15"/>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
       <c r="H17" s="15"/>
       <c r="I17" s="15"/>
       <c r="J17" s="15">
-        <v>71490</v>
+        <v>88600</v>
       </c>
       <c r="K17" s="15"/>
       <c r="L17" s="15"/>
@@ -5923,406 +6132,393 @@
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
       <c r="P17" s="15">
+        <v>88600</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+      <c r="A18" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15">
         <v>71490</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15">
-        <v>52780</v>
-      </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="86"/>
+      <c r="E18" s="15"/>
       <c r="F18" s="15"/>
       <c r="G18" s="15"/>
       <c r="H18" s="15"/>
-      <c r="I18" s="15">
-        <v>52780</v>
-      </c>
-      <c r="J18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15">
+        <v>71490</v>
+      </c>
       <c r="K18" s="15"/>
       <c r="L18" s="15"/>
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
-      <c r="O18" s="15">
+      <c r="O18" s="15"/>
+      <c r="P18" s="15">
+        <v>71490</v>
+      </c>
+      <c r="R18" s="32" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+      <c r="A19" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15">
         <v>52780</v>
       </c>
-      <c r="P18" s="15"/>
-    </row>
-    <row r="19" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A19" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15">
-        <v>156860</v>
-      </c>
-      <c r="E19" s="86">
-        <v>2</v>
-      </c>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
       <c r="F19" s="15"/>
-      <c r="G19" s="86">
-        <v>1200</v>
-      </c>
+      <c r="G19" s="15"/>
       <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15">
-        <v>158060</v>
-      </c>
+      <c r="I19" s="15">
+        <v>52780</v>
+      </c>
+      <c r="J19" s="15"/>
       <c r="K19" s="15"/>
       <c r="L19" s="15"/>
-      <c r="M19" s="100">
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="87">
+        <v>52780</v>
+      </c>
+      <c r="P19" s="15"/>
+      <c r="R19" s="32" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+      <c r="A20" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15">
+        <v>156860</v>
+      </c>
+      <c r="E20" s="15">
+        <v>2</v>
+      </c>
+      <c r="F20" s="86"/>
+      <c r="G20" s="86">
+        <v>1200</v>
+      </c>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15">
         <v>158060</v>
       </c>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="S19" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="T19" s="32" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A20" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15">
-        <v>1660</v>
-      </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="86">
-        <v>4</v>
-      </c>
-      <c r="F20" s="86">
-        <v>195</v>
-      </c>
-      <c r="G20" s="87">
-        <v>585</v>
-      </c>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15">
-        <v>1855</v>
-      </c>
-      <c r="J20" s="15"/>
       <c r="K20" s="15"/>
-      <c r="L20" s="99">
-        <v>1855</v>
-      </c>
-      <c r="M20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="87">
+        <v>158060</v>
+      </c>
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
       <c r="P20" s="15"/>
-      <c r="S20" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="T20" s="88" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:22" ht="19" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="15">
-        <v>87940</v>
+        <v>1660</v>
       </c>
       <c r="D21" s="15"/>
-      <c r="E21" s="86">
-        <v>7</v>
-      </c>
-      <c r="F21" s="86">
-        <v>980</v>
-      </c>
-      <c r="G21" s="15"/>
+      <c r="E21" s="15">
+        <v>4</v>
+      </c>
+      <c r="F21" s="86"/>
+      <c r="G21" s="86">
+        <v>585</v>
+      </c>
       <c r="H21" s="15"/>
       <c r="I21" s="15">
-        <v>88920</v>
+        <v>1075</v>
       </c>
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
-      <c r="L21" s="99">
-        <v>88920</v>
+      <c r="L21" s="98">
+        <v>1075</v>
       </c>
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
+      <c r="O21" s="106"/>
       <c r="P21" s="15"/>
-      <c r="T21" s="88" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:22" ht="19" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15">
-        <v>760</v>
+        <v>87940</v>
       </c>
       <c r="D22" s="15"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="15"/>
+      <c r="E22" s="15">
+        <v>7</v>
+      </c>
+      <c r="F22" s="86">
+        <v>980</v>
+      </c>
       <c r="G22" s="15"/>
       <c r="H22" s="15"/>
       <c r="I22" s="15">
-        <v>760</v>
+        <v>88920</v>
       </c>
       <c r="J22" s="15"/>
       <c r="K22" s="15"/>
-      <c r="L22" s="99">
-        <v>760</v>
+      <c r="L22" s="98">
+        <v>88920</v>
       </c>
       <c r="M22" s="15"/>
       <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
-      <c r="T22" s="32" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="O22" s="106"/>
+    </row>
+    <row r="23" spans="1:22" ht="19" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15">
-        <v>2090</v>
+        <v>760</v>
       </c>
       <c r="D23" s="15"/>
-      <c r="E23" s="86">
-        <v>5</v>
-      </c>
-      <c r="F23" s="86">
-        <v>220</v>
-      </c>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
       <c r="G23" s="15"/>
       <c r="H23" s="15"/>
       <c r="I23" s="15">
-        <v>2310</v>
+        <v>760</v>
       </c>
       <c r="J23" s="15"/>
       <c r="K23" s="15"/>
-      <c r="L23" s="99">
-        <v>2310</v>
+      <c r="L23" s="98">
+        <v>760</v>
       </c>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
+      <c r="O23" s="106"/>
       <c r="P23" s="15"/>
-      <c r="T23" s="32" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:22" ht="19" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="15">
-        <v>1740</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="86">
-        <v>6</v>
+        <v>2090</v>
+      </c>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15">
+        <v>5</v>
       </c>
       <c r="F24" s="86">
-        <v>320</v>
+        <v>220</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
-      <c r="I24" s="91" t="s">
-        <v>113</v>
+      <c r="I24" s="15">
+        <v>2310</v>
       </c>
       <c r="J24" s="15"/>
       <c r="K24" s="15"/>
-      <c r="L24" s="102" t="s">
-        <v>113</v>
+      <c r="L24" s="98">
+        <v>2310</v>
       </c>
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
-      <c r="O24" s="15"/>
+      <c r="O24" s="106"/>
       <c r="P24" s="15"/>
-    </row>
-    <row r="25" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A25" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="86">
-        <v>1</v>
+      <c r="R24" s="110" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+      <c r="A25" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15">
+        <v>1740</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="15">
+        <v>6</v>
       </c>
       <c r="F25" s="86">
-        <v>720</v>
+        <v>320</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15"/>
-      <c r="I25" s="15">
-        <v>720</v>
+      <c r="I25" s="90">
+        <v>2060</v>
       </c>
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
-      <c r="L25" s="99">
-        <v>720</v>
+      <c r="L25" s="100">
+        <v>2060</v>
       </c>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
+      <c r="O25" s="107"/>
       <c r="P25" s="15"/>
-      <c r="T25" s="88" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R25" s="111" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="20" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="B26" s="16"/>
+        <v>108</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>120</v>
+      </c>
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
-      <c r="E26" s="86">
-        <v>3</v>
+      <c r="E26" s="15">
+        <v>1</v>
       </c>
       <c r="F26" s="86">
-        <v>8760</v>
+        <v>720</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="15"/>
       <c r="I26" s="15">
-        <v>8760</v>
+        <v>720</v>
       </c>
       <c r="J26" s="15"/>
       <c r="K26" s="15"/>
-      <c r="L26" s="99">
-        <v>8760</v>
+      <c r="L26" s="98">
+        <v>720</v>
       </c>
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
+      <c r="O26" s="106"/>
       <c r="P26" s="15"/>
-      <c r="T26" s="88" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R26" s="111" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="20" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="15"/>
       <c r="D27" s="15"/>
-      <c r="E27" s="86">
+      <c r="E27" s="15">
         <v>3</v>
       </c>
       <c r="F27" s="86">
-        <v>2140</v>
+        <v>8760</v>
       </c>
       <c r="G27" s="15"/>
       <c r="H27" s="15"/>
       <c r="I27" s="15">
-        <v>2140</v>
+        <v>8760</v>
       </c>
       <c r="J27" s="15"/>
       <c r="K27" s="15"/>
-      <c r="L27" s="99">
-        <v>2140</v>
+      <c r="L27" s="98">
+        <v>8760</v>
       </c>
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
       <c r="O27" s="15"/>
       <c r="P27" s="15"/>
-    </row>
-    <row r="28" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R27" s="136" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="20" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="15"/>
       <c r="D28" s="15"/>
-      <c r="E28" s="86">
-        <v>4</v>
-      </c>
-      <c r="F28" s="87">
-        <v>585</v>
-      </c>
-      <c r="G28" s="86">
-        <v>195</v>
-      </c>
+      <c r="E28" s="15">
+        <v>3</v>
+      </c>
+      <c r="F28" s="86">
+        <v>2140</v>
+      </c>
+      <c r="G28" s="15"/>
       <c r="H28" s="15"/>
       <c r="I28" s="15">
-        <v>585</v>
+        <v>2140</v>
       </c>
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
+      <c r="L28" s="98">
+        <v>2140</v>
+      </c>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
-      <c r="O28" s="15">
-        <v>195</v>
-      </c>
+      <c r="O28" s="15"/>
       <c r="P28" s="15"/>
-    </row>
-    <row r="29" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R28" s="111" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="20" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="15"/>
       <c r="D29" s="15"/>
-      <c r="E29" s="86">
-        <v>5</v>
-      </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="86">
-        <v>220</v>
-      </c>
+      <c r="E29" s="15">
+        <v>4</v>
+      </c>
+      <c r="F29" s="86">
+        <v>585</v>
+      </c>
+      <c r="G29" s="86"/>
       <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15">
-        <v>220</v>
-      </c>
+      <c r="I29" s="15">
+        <v>585</v>
+      </c>
+      <c r="J29" s="15"/>
       <c r="K29" s="15"/>
       <c r="L29" s="15"/>
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="15">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" ht="39" x14ac:dyDescent="0.4">
+      <c r="O29" s="15">
+        <v>585</v>
+      </c>
+      <c r="P29" s="15"/>
+    </row>
+    <row r="30" spans="1:22" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="18" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="15"/>
       <c r="D30" s="15"/>
-      <c r="E30" s="86">
-        <v>6</v>
+      <c r="E30" s="15">
+        <v>5</v>
       </c>
       <c r="F30" s="15"/>
       <c r="G30" s="86">
-        <v>320</v>
+        <v>220</v>
       </c>
       <c r="H30" s="15"/>
       <c r="I30" s="15"/>
       <c r="J30" s="15">
-        <v>320</v>
+        <v>220</v>
       </c>
       <c r="K30" s="15"/>
       <c r="L30" s="15"/>
@@ -6330,27 +6526,27 @@
       <c r="N30" s="15"/>
       <c r="O30" s="15"/>
       <c r="P30" s="15">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="20" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="15"/>
       <c r="D31" s="15"/>
-      <c r="E31" s="86">
-        <v>7</v>
+      <c r="E31" s="15">
+        <v>6</v>
       </c>
       <c r="F31" s="15"/>
       <c r="G31" s="86">
-        <v>980</v>
+        <v>320</v>
       </c>
       <c r="H31" s="15"/>
       <c r="I31" s="15"/>
       <c r="J31" s="15">
-        <v>980</v>
+        <v>320</v>
       </c>
       <c r="K31" s="15"/>
       <c r="L31" s="15"/>
@@ -6358,75 +6554,88 @@
       <c r="N31" s="15"/>
       <c r="O31" s="15"/>
       <c r="P31" s="15">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A32" s="18"/>
+        <v>320</v>
+      </c>
+      <c r="R31" s="118" t="s">
+        <v>219</v>
+      </c>
+      <c r="S31" s="119"/>
+      <c r="T31" s="119"/>
+      <c r="U31" s="119"/>
+      <c r="V31" s="120"/>
+    </row>
+    <row r="32" spans="1:22" ht="20" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>72</v>
+      </c>
       <c r="B32" s="16"/>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15">
-        <v>14535</v>
-      </c>
-      <c r="G32" s="15">
-        <v>14535</v>
+      <c r="E32" s="15">
+        <v>7</v>
+      </c>
+      <c r="F32" s="15"/>
+      <c r="G32" s="86">
+        <v>980</v>
       </c>
       <c r="H32" s="15"/>
-      <c r="I32" s="103">
-        <f>SUM(I4:I31)</f>
-        <v>410030</v>
-      </c>
-      <c r="J32" s="103">
-        <f>SUM(J4:J31)</f>
-        <v>411310</v>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15">
+        <v>980</v>
       </c>
       <c r="K32" s="15"/>
-      <c r="L32" s="15">
-        <f>SUM(L4:L31)</f>
-        <v>105465</v>
-      </c>
-      <c r="M32" s="15">
-        <v>158060</v>
-      </c>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
       <c r="N32" s="15"/>
-      <c r="O32" s="15">
-        <f>SUM(O4:O31)</f>
-        <v>304175</v>
-      </c>
+      <c r="O32" s="15"/>
       <c r="P32" s="15">
-        <f>SUM(P4:P31)</f>
-        <v>253250</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A33" s="18" t="s">
-        <v>112</v>
-      </c>
+        <v>980</v>
+      </c>
+      <c r="R32" s="121" t="s">
+        <v>10</v>
+      </c>
+      <c r="S32" s="122"/>
+      <c r="T32" s="122"/>
+      <c r="U32" s="122"/>
+      <c r="V32" s="123"/>
+    </row>
+    <row r="33" spans="1:22" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="18"/>
       <c r="B33" s="16"/>
       <c r="C33" s="15"/>
       <c r="D33" s="15"/>
       <c r="E33" s="15"/>
       <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
+      <c r="G33" s="86"/>
       <c r="H33" s="15"/>
       <c r="I33" s="15"/>
       <c r="J33" s="15"/>
       <c r="K33" s="15"/>
-      <c r="L33" s="15">
-        <v>52595</v>
+      <c r="L33" s="108">
+        <f>SUM(L21:L28)</f>
+        <v>106745</v>
       </c>
       <c r="M33" s="15"/>
       <c r="N33" s="15"/>
       <c r="O33" s="15"/>
-      <c r="P33" s="15">
-        <v>52595</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A34" s="17"/>
-      <c r="B34" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="R33" s="121" t="s">
+        <v>127</v>
+      </c>
+      <c r="S33" s="122"/>
+      <c r="T33" s="122"/>
+      <c r="U33" s="124" t="s">
+        <v>220</v>
+      </c>
+      <c r="V33" s="125" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="21" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B34" s="16"/>
       <c r="C34" s="15"/>
       <c r="D34" s="15"/>
       <c r="E34" s="15"/>
@@ -6437,33 +6646,29 @@
       <c r="J34" s="15"/>
       <c r="K34" s="15"/>
       <c r="L34" s="15">
-        <f>SUM(L32:L33)</f>
-        <v>158060</v>
-      </c>
-      <c r="M34" s="15">
-        <v>158060</v>
-      </c>
+        <v>51315</v>
+      </c>
+      <c r="M34" s="15"/>
       <c r="N34" s="15"/>
-      <c r="O34" s="15">
-        <f>SUM(O32)</f>
-        <v>304175</v>
-      </c>
-      <c r="P34" s="15">
-        <f>SUM(P32:P33)</f>
-        <v>305845</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A35" s="15"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="87">
+        <v>51315</v>
+      </c>
+      <c r="R34" s="126" t="s">
+        <v>105</v>
+      </c>
+      <c r="S34" s="113"/>
+      <c r="T34" s="113"/>
+      <c r="U34" s="128" t="s">
+        <v>223</v>
+      </c>
+      <c r="V34" s="129"/>
+    </row>
+    <row r="35" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+      <c r="A35" s="17"/>
       <c r="B35" s="15"/>
-      <c r="C35" s="15">
-        <f>SUM(C4:C34)</f>
-        <v>398890</v>
-      </c>
-      <c r="D35" s="15">
-        <f>SUM(D4:D34)</f>
-        <v>398890</v>
-      </c>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
       <c r="E35" s="15"/>
       <c r="F35" s="15"/>
       <c r="G35" s="15"/>
@@ -6476,13 +6681,124 @@
       <c r="N35" s="15"/>
       <c r="O35" s="15"/>
       <c r="P35" s="15"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A41" s="89" t="s">
+      <c r="R35" s="127" t="s">
+        <v>222</v>
+      </c>
+      <c r="S35" s="113"/>
+      <c r="T35" s="113"/>
+      <c r="U35" s="128"/>
+      <c r="V35" s="129" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15">
+        <f>SUM(C5:C35)</f>
+        <v>398890</v>
+      </c>
+      <c r="D36" s="15">
+        <f>SUM(D5:D35)</f>
+        <v>398890</v>
+      </c>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15">
+        <f>SUM(F5:F35)</f>
+        <v>14925</v>
+      </c>
+      <c r="G36" s="15">
+        <f>SUM(G5:G35)</f>
+        <v>14925</v>
+      </c>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15">
+        <f>SUM(I5:I35)</f>
+        <v>411310</v>
+      </c>
+      <c r="J36" s="15">
+        <f>SUM(J5:J35)</f>
+        <v>411310</v>
+      </c>
+      <c r="K36" s="15"/>
+      <c r="L36" s="106">
+        <v>158060</v>
+      </c>
+      <c r="M36" s="106">
+        <v>158060</v>
+      </c>
+      <c r="N36" s="15"/>
+      <c r="O36" s="15">
+        <f>SUM(O5:O35)</f>
+        <v>304565</v>
+      </c>
+      <c r="P36" s="15">
+        <f>SUM(P5:P35)</f>
+        <v>304565</v>
+      </c>
+      <c r="R36" s="116" t="s">
+        <v>224</v>
+      </c>
+      <c r="S36" s="113"/>
+      <c r="T36" s="113"/>
+      <c r="U36" s="128"/>
+      <c r="V36" s="129"/>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="R37" s="114"/>
+      <c r="S37" s="113"/>
+      <c r="T37" s="113"/>
+      <c r="U37" s="128"/>
+      <c r="V37" s="129"/>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="R38" s="126" t="s">
+        <v>222</v>
+      </c>
+      <c r="S38" s="113"/>
+      <c r="T38" s="113"/>
+      <c r="U38" s="128">
+        <v>106745</v>
+      </c>
+      <c r="V38" s="129"/>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="R39" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="S39" s="113"/>
+      <c r="T39" s="113"/>
+      <c r="U39" s="128"/>
+      <c r="V39" s="133">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="R40" s="132" t="s">
+        <v>225</v>
+      </c>
+      <c r="S40" s="113"/>
+      <c r="T40" s="113"/>
+      <c r="U40" s="128"/>
+      <c r="V40" s="133" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A41" s="88" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="R41" s="132" t="s">
+        <v>226</v>
+      </c>
+      <c r="S41" s="113"/>
+      <c r="T41" s="113"/>
+      <c r="U41" s="128"/>
+      <c r="V41" s="133" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
         <v>107</v>
       </c>
@@ -6517,8 +6833,17 @@
         <v>67</v>
       </c>
       <c r="P42" s="21"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="R42" s="132" t="s">
+        <v>70</v>
+      </c>
+      <c r="S42" s="113"/>
+      <c r="T42" s="113"/>
+      <c r="U42" s="128"/>
+      <c r="V42" s="133">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="15"/>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -6537,8 +6862,17 @@
       <c r="N43" s="21"/>
       <c r="O43" s="21"/>
       <c r="P43" s="21"/>
-    </row>
-    <row r="44" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R43" s="132" t="s">
+        <v>84</v>
+      </c>
+      <c r="S43" s="113"/>
+      <c r="T43" s="113"/>
+      <c r="U43" s="128"/>
+      <c r="V43" s="133" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" ht="19" x14ac:dyDescent="0.3">
       <c r="A44" s="17" t="s">
         <v>94</v>
       </c>
@@ -6577,8 +6911,17 @@
       <c r="P44" s="20" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R44" s="132" t="s">
+        <v>88</v>
+      </c>
+      <c r="S44" s="113"/>
+      <c r="T44" s="113"/>
+      <c r="U44" s="128"/>
+      <c r="V44" s="133">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" ht="19" x14ac:dyDescent="0.3">
       <c r="A45" s="17" t="s">
         <v>77</v>
       </c>
@@ -6599,8 +6942,17 @@
       <c r="N45" s="15"/>
       <c r="O45" s="15"/>
       <c r="P45" s="15"/>
-    </row>
-    <row r="46" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R45" s="132" t="s">
+        <v>90</v>
+      </c>
+      <c r="S45" s="113"/>
+      <c r="T45" s="113"/>
+      <c r="U45" s="128"/>
+      <c r="V45" s="133" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="19" x14ac:dyDescent="0.3">
       <c r="A46" s="17" t="s">
         <v>95</v>
       </c>
@@ -6621,8 +6973,17 @@
       <c r="N46" s="15"/>
       <c r="O46" s="15"/>
       <c r="P46" s="15"/>
-    </row>
-    <row r="47" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R46" s="132" t="s">
+        <v>106</v>
+      </c>
+      <c r="S46" s="113"/>
+      <c r="T46" s="113"/>
+      <c r="U46" s="128"/>
+      <c r="V46" s="133" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="19" x14ac:dyDescent="0.3">
       <c r="A47" s="17" t="s">
         <v>96</v>
       </c>
@@ -6643,8 +7004,15 @@
       <c r="N47" s="15"/>
       <c r="O47" s="15"/>
       <c r="P47" s="15"/>
-    </row>
-    <row r="48" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R47" s="114" t="s">
+        <v>231</v>
+      </c>
+      <c r="S47" s="113"/>
+      <c r="T47" s="113"/>
+      <c r="U47" s="128"/>
+      <c r="V47" s="129"/>
+    </row>
+    <row r="48" spans="1:22" ht="19" x14ac:dyDescent="0.3">
       <c r="A48" s="17" t="s">
         <v>78</v>
       </c>
@@ -6669,8 +7037,13 @@
       <c r="N48" s="15"/>
       <c r="O48" s="15"/>
       <c r="P48" s="15"/>
-    </row>
-    <row r="49" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R48" s="114"/>
+      <c r="S48" s="113"/>
+      <c r="T48" s="113"/>
+      <c r="U48" s="128"/>
+      <c r="V48" s="129"/>
+    </row>
+    <row r="49" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A49" s="17" t="s">
         <v>97</v>
       </c>
@@ -6691,8 +7064,20 @@
       <c r="N49" s="15"/>
       <c r="O49" s="15"/>
       <c r="P49" s="15"/>
-    </row>
-    <row r="50" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R49" s="126" t="s">
+        <v>222</v>
+      </c>
+      <c r="S49" s="113"/>
+      <c r="T49" s="113"/>
+      <c r="U49" s="128">
+        <v>51315</v>
+      </c>
+      <c r="V49" s="129"/>
+      <c r="W49" s="112" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A50" s="17" t="s">
         <v>98</v>
       </c>
@@ -6713,8 +7098,17 @@
       <c r="N50" s="15"/>
       <c r="O50" s="15"/>
       <c r="P50" s="15"/>
-    </row>
-    <row r="51" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R50" s="132" t="s">
+        <v>103</v>
+      </c>
+      <c r="S50" s="113"/>
+      <c r="T50" s="113"/>
+      <c r="U50" s="128"/>
+      <c r="V50" s="129">
+        <v>51315</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A51" s="17" t="s">
         <v>135</v>
       </c>
@@ -6737,8 +7131,15 @@
       <c r="N51" s="15"/>
       <c r="O51" s="15"/>
       <c r="P51" s="15"/>
-    </row>
-    <row r="52" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R51" s="114" t="s">
+        <v>232</v>
+      </c>
+      <c r="S51" s="113"/>
+      <c r="T51" s="113"/>
+      <c r="U51" s="128"/>
+      <c r="V51" s="129"/>
+    </row>
+    <row r="52" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A52" s="17" t="s">
         <v>80</v>
       </c>
@@ -6759,8 +7160,13 @@
       <c r="N52" s="15"/>
       <c r="O52" s="15"/>
       <c r="P52" s="15"/>
-    </row>
-    <row r="53" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R52" s="114"/>
+      <c r="S52" s="113"/>
+      <c r="T52" s="113"/>
+      <c r="U52" s="128"/>
+      <c r="V52" s="129"/>
+    </row>
+    <row r="53" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A53" s="17" t="s">
         <v>136</v>
       </c>
@@ -6783,8 +7189,17 @@
       <c r="N53" s="15"/>
       <c r="O53" s="15"/>
       <c r="P53" s="15"/>
-    </row>
-    <row r="54" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R53" s="134" t="s">
+        <v>103</v>
+      </c>
+      <c r="S53" s="113"/>
+      <c r="T53" s="113"/>
+      <c r="U53" s="135" t="s">
+        <v>233</v>
+      </c>
+      <c r="V53" s="129"/>
+    </row>
+    <row r="54" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A54" s="17" t="s">
         <v>99</v>
       </c>
@@ -6805,8 +7220,17 @@
       <c r="N54" s="15"/>
       <c r="O54" s="15"/>
       <c r="P54" s="15"/>
-    </row>
-    <row r="55" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R54" s="132" t="s">
+        <v>104</v>
+      </c>
+      <c r="S54" s="113"/>
+      <c r="T54" s="113"/>
+      <c r="U54" s="128"/>
+      <c r="V54" s="129">
+        <v>52780</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" ht="20" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="17" t="s">
         <v>100</v>
       </c>
@@ -6831,8 +7255,15 @@
       <c r="N55" s="15"/>
       <c r="O55" s="15"/>
       <c r="P55" s="15"/>
-    </row>
-    <row r="56" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R55" s="117" t="s">
+        <v>234</v>
+      </c>
+      <c r="S55" s="115"/>
+      <c r="T55" s="115"/>
+      <c r="U55" s="130"/>
+      <c r="V55" s="131"/>
+    </row>
+    <row r="56" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A56" s="17" t="s">
         <v>101</v>
       </c>
@@ -6854,7 +7285,7 @@
       <c r="O56" s="15"/>
       <c r="P56" s="15"/>
     </row>
-    <row r="57" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A57" s="17" t="s">
         <v>102</v>
       </c>
@@ -6875,8 +7306,11 @@
       <c r="N57" s="15"/>
       <c r="O57" s="15"/>
       <c r="P57" s="15"/>
-    </row>
-    <row r="58" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R57" s="32" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A58" s="17" t="s">
         <v>103</v>
       </c>
@@ -6897,8 +7331,11 @@
       <c r="N58" s="15"/>
       <c r="O58" s="15"/>
       <c r="P58" s="15"/>
-    </row>
-    <row r="59" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R58" s="111" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A59" s="17" t="s">
         <v>104</v>
       </c>
@@ -6919,8 +7356,11 @@
       <c r="N59" s="15"/>
       <c r="O59" s="15"/>
       <c r="P59" s="15"/>
-    </row>
-    <row r="60" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R59" s="111" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A60" s="17" t="s">
         <v>105</v>
       </c>
@@ -6945,8 +7385,11 @@
       <c r="N60" s="15"/>
       <c r="O60" s="15"/>
       <c r="P60" s="15"/>
-    </row>
-    <row r="61" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R60" s="111" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A61" s="17" t="s">
         <v>70</v>
       </c>
@@ -6969,8 +7412,11 @@
       <c r="N61" s="15"/>
       <c r="O61" s="15"/>
       <c r="P61" s="15"/>
-    </row>
-    <row r="62" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="R61" s="111" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A62" s="17" t="s">
         <v>84</v>
       </c>
@@ -6994,7 +7440,7 @@
       <c r="O62" s="15"/>
       <c r="P62" s="15"/>
     </row>
-    <row r="63" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A63" s="17" t="s">
         <v>88</v>
       </c>
@@ -7016,7 +7462,7 @@
       <c r="O63" s="15"/>
       <c r="P63" s="15"/>
     </row>
-    <row r="64" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A64" s="17" t="s">
         <v>90</v>
       </c>
@@ -7040,7 +7486,7 @@
       <c r="O64" s="15"/>
       <c r="P64" s="15"/>
     </row>
-    <row r="65" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A65" s="17" t="s">
         <v>106</v>
       </c>
@@ -7066,7 +7512,7 @@
       <c r="O65" s="15"/>
       <c r="P65" s="15"/>
     </row>
-    <row r="66" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:16" ht="20" x14ac:dyDescent="0.25">
       <c r="A66" s="18" t="s">
         <v>108</v>
       </c>
@@ -7090,7 +7536,7 @@
       <c r="O66" s="15"/>
       <c r="P66" s="15"/>
     </row>
-    <row r="67" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:16" ht="20" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
         <v>109</v>
       </c>
@@ -7112,7 +7558,7 @@
       <c r="O67" s="15"/>
       <c r="P67" s="15"/>
     </row>
-    <row r="68" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:16" ht="20" x14ac:dyDescent="0.25">
       <c r="A68" s="18" t="s">
         <v>110</v>
       </c>
@@ -7134,7 +7580,7 @@
       <c r="O68" s="15"/>
       <c r="P68" s="15"/>
     </row>
-    <row r="69" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:16" ht="20" x14ac:dyDescent="0.25">
       <c r="A69" s="18" t="s">
         <v>79</v>
       </c>
@@ -7156,7 +7602,7 @@
       <c r="O69" s="15"/>
       <c r="P69" s="15"/>
     </row>
-    <row r="70" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:16" ht="20" x14ac:dyDescent="0.25">
       <c r="A70" s="18" t="s">
         <v>75</v>
       </c>
@@ -7178,7 +7624,7 @@
       <c r="O70" s="15"/>
       <c r="P70" s="15"/>
     </row>
-    <row r="71" spans="1:16" ht="39" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:16" ht="20" x14ac:dyDescent="0.25">
       <c r="A71" s="18" t="s">
         <v>111</v>
       </c>
@@ -7200,7 +7646,7 @@
       <c r="O71" s="15"/>
       <c r="P71" s="15"/>
     </row>
-    <row r="72" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:16" ht="20" x14ac:dyDescent="0.25">
       <c r="A72" s="18" t="s">
         <v>72</v>
       </c>
@@ -7222,7 +7668,7 @@
       <c r="O72" s="15"/>
       <c r="P72" s="15"/>
     </row>
-    <row r="73" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:16" ht="19" x14ac:dyDescent="0.25">
       <c r="A73" s="18"/>
       <c r="B73" s="16"/>
       <c r="C73" s="15"/>
@@ -7240,7 +7686,7 @@
       <c r="O73" s="15"/>
       <c r="P73" s="15"/>
     </row>
-    <row r="74" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:16" ht="20" x14ac:dyDescent="0.25">
       <c r="A74" s="18" t="s">
         <v>112</v>
       </c>
@@ -7260,7 +7706,7 @@
       <c r="O74" s="15"/>
       <c r="P74" s="15"/>
     </row>
-    <row r="75" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:16" ht="19" x14ac:dyDescent="0.3">
       <c r="A75" s="17"/>
       <c r="B75" s="15"/>
       <c r="C75" s="15"/>
@@ -7278,7 +7724,7 @@
       <c r="O75" s="15"/>
       <c r="P75" s="15"/>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="15"/>
       <c r="B76" s="15"/>
       <c r="C76" s="15">
@@ -7303,21 +7749,21 @@
       <c r="P76" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="C2:D2"/>
+  <mergeCells count="3">
+    <mergeCell ref="R32:V32"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="R31:V31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB70836-D79F-4864-89CC-B27D7E0A03DC}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7326,13 +7772,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA4CDB96-6C4C-4200-8B12-486AAEF84CD0}">
   <dimension ref="A1:M35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="18.140625" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.1640625" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B1" s="3"/>
       <c r="C1" s="4" t="s">
         <v>15</v>
@@ -7343,7 +7789,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -7360,7 +7806,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7384,7 +7830,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="6"/>
       <c r="C4" t="s">
         <v>152</v>
@@ -7403,7 +7849,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="11"/>
       <c r="C5" s="12" t="s">
         <v>154</v>
@@ -7420,11 +7866,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="6"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
@@ -7448,7 +7894,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B8" s="6"/>
       <c r="C8" t="s">
         <v>79</v>
@@ -7466,7 +7912,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11"/>
       <c r="C9" s="12" t="s">
         <v>158</v>
@@ -7483,11 +7929,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="6"/>
       <c r="E10" s="7"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>3</v>
       </c>
@@ -7511,7 +7957,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B12" s="6"/>
       <c r="C12" t="s">
         <v>159</v>
@@ -7529,7 +7975,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="11"/>
       <c r="C13" s="12" t="s">
         <v>163</v>
@@ -7546,11 +7992,11 @@
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="6"/>
       <c r="E14" s="7"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>4</v>
       </c>
@@ -7574,7 +8020,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="6"/>
       <c r="C16" t="s">
         <v>165</v>
@@ -7592,7 +8038,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="11"/>
       <c r="C17" s="12" t="s">
         <v>167</v>
@@ -7609,11 +8055,11 @@
         <v>161</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="6"/>
       <c r="E18" s="7"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>5</v>
       </c>
@@ -7637,7 +8083,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B20" s="6"/>
       <c r="C20" t="s">
         <v>171</v>
@@ -7655,7 +8101,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B21" s="6"/>
       <c r="C21" t="s">
         <v>172</v>
@@ -7671,14 +8117,14 @@
         <v>161</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B22" s="11"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
       <c r="E22" s="13"/>
     </row>
-    <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>6</v>
       </c>
@@ -7702,7 +8148,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B25" s="6"/>
       <c r="C25" t="s">
         <v>174</v>
@@ -7720,7 +8166,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="11"/>
       <c r="C26" s="12" t="s">
         <v>175</v>
@@ -7737,8 +8183,8 @@
         <v>161</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>7</v>
       </c>
@@ -7762,7 +8208,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B29" s="6"/>
       <c r="C29" t="s">
         <v>177</v>
@@ -7780,7 +8226,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B30" s="11"/>
       <c r="C30" s="12" t="s">
         <v>175</v>
@@ -7797,8 +8243,8 @@
         <v>161</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="G32">
         <v>1</v>
       </c>
@@ -7816,7 +8262,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="7:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:13" x14ac:dyDescent="0.2">
       <c r="G33">
         <v>2</v>
       </c>
@@ -7836,7 +8282,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="7:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="G34">
         <v>3</v>
       </c>
@@ -7856,7 +8302,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="7:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:13" x14ac:dyDescent="0.2">
       <c r="G35">
         <v>4</v>
       </c>
@@ -7875,14 +8321,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14BBB4DE-EA90-4F91-8180-6C1E6B7C8861}">
   <dimension ref="A2:L32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
         <v>76</v>
       </c>
@@ -7910,7 +8356,7 @@
       </c>
       <c r="L2" s="14"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="14"/>
       <c r="B3" s="14" t="s">
         <v>63</v>
@@ -7927,7 +8373,7 @@
       <c r="K3" s="14"/>
       <c r="L3" s="14"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="14"/>
       <c r="B4" s="14" t="s">
         <v>45</v>
@@ -7961,7 +8407,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
         <v>77</v>
       </c>
@@ -7983,7 +8429,7 @@
       </c>
       <c r="L5" s="14"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
         <v>78</v>
       </c>
@@ -8009,7 +8455,7 @@
       </c>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
         <v>79</v>
       </c>
@@ -8035,7 +8481,7 @@
       </c>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
         <v>80</v>
       </c>
@@ -8057,7 +8503,7 @@
       </c>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
         <v>81</v>
       </c>
@@ -8083,7 +8529,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
         <v>82</v>
       </c>
@@ -8105,7 +8551,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
         <v>52</v>
       </c>
@@ -8127,7 +8573,7 @@
         <v>15540</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
         <v>53</v>
       </c>
@@ -8149,7 +8595,7 @@
       </c>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
         <v>83</v>
       </c>
@@ -8171,7 +8617,7 @@
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
         <v>84</v>
       </c>
@@ -8197,7 +8643,7 @@
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
         <v>85</v>
       </c>
@@ -8219,7 +8665,7 @@
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
         <v>86</v>
       </c>
@@ -8241,7 +8687,7 @@
       <c r="K16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
         <v>87</v>
       </c>
@@ -8263,7 +8709,7 @@
       <c r="K17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
         <v>88</v>
       </c>
@@ -8289,7 +8735,7 @@
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
         <v>89</v>
       </c>
@@ -8315,7 +8761,7 @@
       <c r="K19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
         <v>90</v>
       </c>
@@ -8341,7 +8787,7 @@
       <c r="K20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="14"/>
       <c r="B21" s="14">
         <v>206640</v>
@@ -8359,7 +8805,7 @@
       <c r="K21" s="14"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="s">
         <v>69</v>
       </c>
@@ -8383,7 +8829,7 @@
       <c r="K22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="14" t="s">
         <v>70</v>
       </c>
@@ -8407,7 +8853,7 @@
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="14" t="s">
         <v>71</v>
       </c>
@@ -8431,7 +8877,7 @@
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="14" t="s">
         <v>72</v>
       </c>
@@ -8455,7 +8901,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="14" t="s">
         <v>73</v>
       </c>
@@ -8479,7 +8925,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="14" t="s">
         <v>74</v>
       </c>
@@ -8503,7 +8949,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="14" t="s">
         <v>75</v>
       </c>
@@ -8527,7 +8973,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="14" t="s">
         <v>92</v>
       </c>
@@ -8551,7 +8997,7 @@
         <v>89305</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="14" t="s">
         <v>91</v>
       </c>
@@ -8571,7 +9017,7 @@
         <v>29555</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="14"/>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -8585,7 +9031,7 @@
       <c r="K31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="14" t="s">
         <v>68</v>
       </c>
@@ -8633,81 +9079,81 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F243036-475E-442E-9214-8F3E938FBBFF}">
   <dimension ref="A1:L45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" customWidth="1"/>
+    <col min="1" max="1" width="32.6640625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" customWidth="1"/>
-    <col min="4" max="4" width="4.7109375" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" customWidth="1"/>
+    <col min="4" max="4" width="4.6640625" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="16.85546875" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" customWidth="1"/>
-    <col min="11" max="11" width="17.28515625" customWidth="1"/>
-    <col min="12" max="12" width="18.42578125" customWidth="1"/>
+    <col min="8" max="8" width="17.5" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.1640625" customWidth="1"/>
+    <col min="11" max="11" width="17.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="110"/>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="111"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" s="103"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="104"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="111"/>
+      <c r="C2" s="104"/>
       <c r="D2" s="14"/>
-      <c r="E2" s="110" t="s">
+      <c r="E2" s="103" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="111"/>
-      <c r="G2" s="110" t="s">
+      <c r="F2" s="104"/>
+      <c r="G2" s="103" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="111"/>
-      <c r="I2" s="110" t="s">
-        <v>206</v>
-      </c>
-      <c r="J2" s="111"/>
-      <c r="K2" s="110" t="s">
+      <c r="H2" s="104"/>
+      <c r="I2" s="103" t="s">
+        <v>205</v>
+      </c>
+      <c r="J2" s="104"/>
+      <c r="K2" s="103" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="111"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L2" s="104"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="14"/>
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="111"/>
+      <c r="C3" s="104"/>
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="110" t="s">
+      <c r="G3" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="111"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="110"/>
-      <c r="L3" s="111"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H3" s="104"/>
+      <c r="I3" s="103"/>
+      <c r="J3" s="104"/>
+      <c r="K3" s="103"/>
+      <c r="L3" s="104"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="14"/>
       <c r="B4" s="14" t="s">
         <v>45</v>
@@ -8715,8 +9161,8 @@
       <c r="C4" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="94" t="s">
-        <v>197</v>
+      <c r="D4" s="93" t="s">
+        <v>196</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>45</v>
@@ -8743,7 +9189,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>77</v>
       </c>
@@ -8765,7 +9211,7 @@
       </c>
       <c r="L5" s="14"/>
     </row>
-    <row r="6" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>95</v>
       </c>
@@ -8787,7 +9233,7 @@
       </c>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>79</v>
       </c>
@@ -8796,7 +9242,7 @@
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="86" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E7" s="15"/>
       <c r="F7" s="86">
@@ -8813,7 +9259,7 @@
       </c>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>97</v>
       </c>
@@ -8835,7 +9281,7 @@
       </c>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>98</v>
       </c>
@@ -8857,16 +9303,16 @@
       </c>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="15">
         <v>86900</v>
       </c>
       <c r="D10" s="86" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E10" s="15"/>
       <c r="F10" s="86">
@@ -8883,9 +9329,9 @@
         <v>96500</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B11" s="15">
         <v>32300</v>
@@ -8905,16 +9351,16 @@
       </c>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B12" s="15"/>
       <c r="C12" s="15">
         <v>8800</v>
       </c>
       <c r="D12" s="86" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="86">
@@ -8931,7 +9377,7 @@
         <v>12480</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>99</v>
       </c>
@@ -8953,7 +9399,7 @@
         <v>16400</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>102</v>
       </c>
@@ -8975,9 +9421,9 @@
         <v>64000</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B15" s="15"/>
       <c r="C15" s="15">
@@ -8997,9 +9443,9 @@
         <v>236950</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B16" s="15">
         <v>86500</v>
@@ -9019,16 +9465,16 @@
       </c>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B17" s="15"/>
       <c r="C17" s="15">
         <v>262430</v>
       </c>
       <c r="D17" s="86" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E17" s="86">
         <v>600</v>
@@ -9039,15 +9485,15 @@
         <v>261830</v>
       </c>
       <c r="I17" s="15"/>
-      <c r="J17" s="100">
+      <c r="J17" s="99">
         <v>261830</v>
       </c>
       <c r="K17" s="15"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B18" s="15"/>
       <c r="C18" s="15">
@@ -9061,13 +9507,13 @@
         <v>14400</v>
       </c>
       <c r="I18" s="15"/>
-      <c r="J18" s="100">
+      <c r="J18" s="99">
         <v>14400</v>
       </c>
       <c r="K18" s="15"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>84</v>
       </c>
@@ -9076,7 +9522,7 @@
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="86" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E19" s="86">
         <v>2360</v>
@@ -9086,14 +9532,14 @@
         <v>126960</v>
       </c>
       <c r="H19" s="15"/>
-      <c r="I19" s="99">
+      <c r="I19" s="98">
         <v>126960</v>
       </c>
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>89</v>
       </c>
@@ -9108,14 +9554,14 @@
         <v>4520</v>
       </c>
       <c r="H20" s="15"/>
-      <c r="I20" s="99">
+      <c r="I20" s="98">
         <v>4520</v>
       </c>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>90</v>
       </c>
@@ -9124,7 +9570,7 @@
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="86" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E21" s="86">
         <v>260</v>
@@ -9134,14 +9580,14 @@
         <v>3340</v>
       </c>
       <c r="H21" s="15"/>
-      <c r="I21" s="99">
+      <c r="I21" s="98">
         <v>3340</v>
       </c>
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>70</v>
       </c>
@@ -9150,7 +9596,7 @@
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="86" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E22" s="86">
         <v>1340</v>
@@ -9160,24 +9606,24 @@
         <v>37820</v>
       </c>
       <c r="H22" s="15"/>
-      <c r="I22" s="99">
+      <c r="I22" s="98">
         <v>37820</v>
       </c>
       <c r="J22" s="15"/>
       <c r="K22" s="15"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="15"/>
-      <c r="B23" s="93">
+      <c r="B23" s="92">
         <f>SUM(B5:B22)</f>
         <v>689880</v>
       </c>
-      <c r="C23" s="93">
+      <c r="C23" s="92">
         <f>SUM(C5:C22)</f>
         <v>689880</v>
       </c>
-      <c r="D23" s="96"/>
+      <c r="D23" s="95"/>
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
       <c r="G23" s="15"/>
@@ -9187,14 +9633,14 @@
       <c r="K23" s="15"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="1:12" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" ht="18" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="B24" s="92"/>
-      <c r="C24" s="92"/>
-      <c r="D24" s="97" t="s">
-        <v>196</v>
+        <v>187</v>
+      </c>
+      <c r="B24" s="91"/>
+      <c r="C24" s="91"/>
+      <c r="D24" s="96" t="s">
+        <v>195</v>
       </c>
       <c r="E24" s="86">
         <v>9600</v>
@@ -9204,21 +9650,21 @@
         <v>9600</v>
       </c>
       <c r="H24" s="15"/>
-      <c r="I24" s="99">
+      <c r="I24" s="98">
         <v>9600</v>
       </c>
       <c r="J24" s="15"/>
       <c r="K24" s="15"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
-      <c r="D25" s="97" t="s">
-        <v>196</v>
+      <c r="D25" s="96" t="s">
+        <v>195</v>
       </c>
       <c r="E25" s="86">
         <v>3680</v>
@@ -9228,21 +9674,21 @@
         <v>3680</v>
       </c>
       <c r="H25" s="15"/>
-      <c r="I25" s="99">
+      <c r="I25" s="98">
         <v>3680</v>
       </c>
       <c r="J25" s="15"/>
       <c r="K25" s="15"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>75</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
-      <c r="D26" s="98" t="s">
-        <v>193</v>
+      <c r="D26" s="97" t="s">
+        <v>192</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="86">
@@ -9259,14 +9705,14 @@
         <v>260</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>72</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
       <c r="D27" s="86" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="86">
@@ -9283,14 +9729,14 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
       <c r="D28" s="86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E28" s="15"/>
       <c r="F28" s="86">
@@ -9307,14 +9753,14 @@
         <v>4820</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
       <c r="D29" s="86" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E29" s="86"/>
       <c r="F29" s="86">
@@ -9331,14 +9777,14 @@
         <v>600</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
       <c r="D30" s="86" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E30" s="86">
         <v>4820</v>
@@ -9348,31 +9794,31 @@
         <v>4820</v>
       </c>
       <c r="H30" s="15"/>
-      <c r="I30" s="99">
+      <c r="I30" s="98">
         <v>4820</v>
       </c>
       <c r="J30" s="15"/>
       <c r="K30" s="15"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="15"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
       <c r="D31" s="86"/>
-      <c r="E31" s="93">
+      <c r="E31" s="92">
         <f t="shared" ref="E31:L31" si="0">SUM(E5:E30)</f>
         <v>22660</v>
       </c>
-      <c r="F31" s="93">
+      <c r="F31" s="92">
         <f t="shared" si="0"/>
         <v>22660</v>
       </c>
-      <c r="G31" s="93">
+      <c r="G31" s="92">
         <f t="shared" si="0"/>
         <v>710600</v>
       </c>
-      <c r="H31" s="93">
+      <c r="H31" s="92">
         <f t="shared" si="0"/>
         <v>710600</v>
       </c>
@@ -9388,22 +9834,22 @@
         <f t="shared" si="0"/>
         <v>519860</v>
       </c>
-      <c r="L31" s="95">
+      <c r="L31" s="94">
         <f t="shared" si="0"/>
         <v>434370</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:12" ht="18" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>112</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
-      <c r="E32" s="92"/>
-      <c r="F32" s="92"/>
-      <c r="G32" s="92"/>
-      <c r="H32" s="92"/>
+      <c r="E32" s="91"/>
+      <c r="F32" s="91"/>
+      <c r="G32" s="91"/>
+      <c r="H32" s="91"/>
       <c r="I32" s="15">
         <v>85490</v>
       </c>
@@ -9413,7 +9859,7 @@
         <v>85490</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="15"/>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -9422,24 +9868,24 @@
       <c r="F33" s="15"/>
       <c r="G33" s="15"/>
       <c r="H33" s="15"/>
-      <c r="I33" s="93">
+      <c r="I33" s="92">
         <f>SUM(I31:I32)</f>
         <v>276230</v>
       </c>
-      <c r="J33" s="93">
+      <c r="J33" s="92">
         <f>SUM(J31)</f>
         <v>276230</v>
       </c>
-      <c r="K33" s="93">
+      <c r="K33" s="92">
         <f>SUM(K31)</f>
         <v>519860</v>
       </c>
-      <c r="L33" s="93">
+      <c r="L33" s="92">
         <f>SUM(L31:L32)</f>
         <v>519860</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:12" ht="18" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -9448,12 +9894,12 @@
       <c r="F34" s="15"/>
       <c r="G34" s="15"/>
       <c r="H34" s="15"/>
-      <c r="I34" s="92"/>
-      <c r="J34" s="92"/>
-      <c r="K34" s="92"/>
-      <c r="L34" s="104"/>
-    </row>
-    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="I34" s="91"/>
+      <c r="J34" s="91"/>
+      <c r="K34" s="91"/>
+      <c r="L34" s="101"/>
+    </row>
+    <row r="35" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A35" s="15"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -9467,7 +9913,7 @@
       <c r="K35" s="15"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A36" s="32"/>
       <c r="B36" s="32"/>
       <c r="C36" s="32"/>
@@ -9480,7 +9926,7 @@
       <c r="J36" s="32"/>
       <c r="K36" s="32"/>
     </row>
-    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A37" s="32"/>
       <c r="B37" s="32"/>
       <c r="C37" s="32"/>
@@ -9493,7 +9939,7 @@
       <c r="J37" s="32"/>
       <c r="K37" s="32"/>
     </row>
-    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A38" s="32"/>
       <c r="B38" s="32"/>
       <c r="C38" s="32"/>
@@ -9506,7 +9952,7 @@
       <c r="J38" s="32"/>
       <c r="K38" s="32"/>
     </row>
-    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A39" s="32"/>
       <c r="B39" s="32"/>
       <c r="C39" s="32"/>
@@ -9519,34 +9965,34 @@
       <c r="J39" s="32"/>
       <c r="K39" s="32"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H40" s="85" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H41" s="85" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H41" s="85" t="s">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H42" s="85" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H42" s="85" t="s">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H43" s="85" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H44" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H43" s="85" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H44" t="s">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H45" t="s">
         <v>203</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H45" t="s">
-        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/ACCY122/Session/S04/ACCY122 L4 Workbook.xlsx
+++ b/ACCY122/Session/S04/ACCY122 L4 Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Session/S04/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004DB084-40DA-2645-AE0F-FE0158965D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A8D081-7CC5-B447-BF76-1030E2D53780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28940" windowHeight="18660" activeTab="4" xr2:uid="{49300C88-9C68-40D1-BFDB-69B44FEEA068}"/>
   </bookViews>
@@ -117,7 +117,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="246">
   <si>
     <t>Balanced Day Adjustments</t>
   </si>
@@ -871,6 +871,24 @@
   </si>
   <si>
     <t>Loss → Debit balance in P&amp;L Summary</t>
+  </si>
+  <si>
+    <t>ref 4 - the owner bought insurance but never record</t>
+  </si>
+  <si>
+    <t>but on 30 jun - need record but 3mths alr passed so</t>
+  </si>
+  <si>
+    <t>left 9mths worth of insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref 5 - mortagage payment not paid so no need to record </t>
+  </si>
+  <si>
+    <t>only record interest</t>
+  </si>
+  <si>
+    <t>ref 6 - telecom bill owed on credit</t>
   </si>
 </sst>
 </file>
@@ -1434,7 +1452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1648,6 +1666,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -5665,12 +5684,12 @@
     <col min="19" max="16384" width="9.1640625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="88" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>107</v>
       </c>
@@ -5706,7 +5725,7 @@
       </c>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="15"/>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
@@ -5730,7 +5749,7 @@
       <c r="O3" s="21"/>
       <c r="P3" s="21"/>
     </row>
-    <row r="4" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>94</v>
       </c>
@@ -5770,7 +5789,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
         <v>77</v>
       </c>
@@ -5796,7 +5815,7 @@
       </c>
       <c r="P5" s="15"/>
     </row>
-    <row r="6" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>95</v>
       </c>
@@ -5822,7 +5841,7 @@
       </c>
       <c r="P6" s="15"/>
     </row>
-    <row r="7" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A7" s="17" t="s">
         <v>96</v>
       </c>
@@ -5848,7 +5867,7 @@
       </c>
       <c r="P7" s="15"/>
     </row>
-    <row r="8" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>78</v>
       </c>
@@ -5880,7 +5899,7 @@
       </c>
       <c r="P8" s="15"/>
     </row>
-    <row r="9" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
         <v>97</v>
       </c>
@@ -5906,7 +5925,7 @@
       </c>
       <c r="P9" s="15"/>
     </row>
-    <row r="10" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>98</v>
       </c>
@@ -5932,7 +5951,7 @@
       </c>
       <c r="P10" s="15"/>
     </row>
-    <row r="11" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
         <v>135</v>
       </c>
@@ -5962,7 +5981,7 @@
         <v>72760</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>80</v>
       </c>
@@ -5988,7 +6007,7 @@
       </c>
       <c r="P12" s="15"/>
     </row>
-    <row r="13" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
         <v>136</v>
       </c>
@@ -6017,8 +6036,11 @@
       <c r="P13" s="15">
         <v>8560</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+      <c r="W13" s="111" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
         <v>99</v>
       </c>
@@ -6047,8 +6069,11 @@
       <c r="S14" s="32" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+      <c r="W14" s="111" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
         <v>100</v>
       </c>
@@ -6079,8 +6104,11 @@
       <c r="P15" s="15">
         <v>360</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" ht="19" x14ac:dyDescent="0.3">
+      <c r="W15" s="111" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
         <v>101</v>
       </c>
@@ -6108,8 +6136,11 @@
       <c r="R16" s="32" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+      <c r="W16" s="111" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
         <v>102</v>
       </c>
@@ -6134,8 +6165,11 @@
       <c r="P17" s="15">
         <v>88600</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+      <c r="W17" s="111" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
         <v>103</v>
       </c>
@@ -6163,8 +6197,11 @@
       <c r="R18" s="32" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+      <c r="W18" s="111" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
         <v>104</v>
       </c>
@@ -6193,7 +6230,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>105</v>
       </c>
@@ -6225,7 +6262,7 @@
       <c r="O20" s="15"/>
       <c r="P20" s="15"/>
     </row>
-    <row r="21" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
         <v>70</v>
       </c>
@@ -6255,7 +6292,7 @@
       <c r="O21" s="106"/>
       <c r="P21" s="15"/>
     </row>
-    <row r="22" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
         <v>84</v>
       </c>
@@ -6284,7 +6321,7 @@
       <c r="N22" s="15"/>
       <c r="O22" s="106"/>
     </row>
-    <row r="23" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
         <v>88</v>
       </c>
@@ -6310,7 +6347,7 @@
       <c r="O23" s="106"/>
       <c r="P23" s="15"/>
     </row>
-    <row r="24" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
         <v>90</v>
       </c>
@@ -6343,7 +6380,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A25" s="17" t="s">
         <v>106</v>
       </c>
@@ -6374,11 +6411,11 @@
       <c r="N25" s="15"/>
       <c r="O25" s="107"/>
       <c r="P25" s="15"/>
-      <c r="R25" s="111" t="s">
+      <c r="R25" s="112" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" ht="20" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>108</v>
       </c>
@@ -6407,11 +6444,11 @@
       <c r="N26" s="15"/>
       <c r="O26" s="106"/>
       <c r="P26" s="15"/>
-      <c r="R26" s="111" t="s">
+      <c r="R26" s="112" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" ht="20" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
         <v>109</v>
       </c>
@@ -6438,11 +6475,11 @@
       <c r="N27" s="15"/>
       <c r="O27" s="15"/>
       <c r="P27" s="15"/>
-      <c r="R27" s="136" t="s">
+      <c r="R27" s="137" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" ht="20" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
         <v>110</v>
       </c>
@@ -6469,11 +6506,11 @@
       <c r="N28" s="15"/>
       <c r="O28" s="15"/>
       <c r="P28" s="15"/>
-      <c r="R28" s="111" t="s">
+      <c r="R28" s="112" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="29" spans="1:22" ht="20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" ht="20" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
         <v>79</v>
       </c>
@@ -6501,7 +6538,7 @@
       </c>
       <c r="P29" s="15"/>
     </row>
-    <row r="30" spans="1:22" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="18" t="s">
         <v>75</v>
       </c>
@@ -6529,7 +6566,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" ht="20" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
         <v>111</v>
       </c>
@@ -6556,15 +6593,15 @@
       <c r="P31" s="15">
         <v>320</v>
       </c>
-      <c r="R31" s="118" t="s">
+      <c r="R31" s="119" t="s">
         <v>219</v>
       </c>
-      <c r="S31" s="119"/>
-      <c r="T31" s="119"/>
-      <c r="U31" s="119"/>
-      <c r="V31" s="120"/>
-    </row>
-    <row r="32" spans="1:22" ht="20" x14ac:dyDescent="0.25">
+      <c r="S31" s="120"/>
+      <c r="T31" s="120"/>
+      <c r="U31" s="120"/>
+      <c r="V31" s="121"/>
+    </row>
+    <row r="32" spans="1:23" ht="20" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
         <v>72</v>
       </c>
@@ -6591,13 +6628,13 @@
       <c r="P32" s="15">
         <v>980</v>
       </c>
-      <c r="R32" s="121" t="s">
+      <c r="R32" s="122" t="s">
         <v>10</v>
       </c>
-      <c r="S32" s="122"/>
-      <c r="T32" s="122"/>
-      <c r="U32" s="122"/>
-      <c r="V32" s="123"/>
+      <c r="S32" s="123"/>
+      <c r="T32" s="123"/>
+      <c r="U32" s="123"/>
+      <c r="V32" s="124"/>
     </row>
     <row r="33" spans="1:22" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="18"/>
@@ -6619,15 +6656,15 @@
       <c r="N33" s="15"/>
       <c r="O33" s="15"/>
       <c r="P33" s="15"/>
-      <c r="R33" s="121" t="s">
+      <c r="R33" s="122" t="s">
         <v>127</v>
       </c>
-      <c r="S33" s="122"/>
-      <c r="T33" s="122"/>
-      <c r="U33" s="124" t="s">
+      <c r="S33" s="123"/>
+      <c r="T33" s="123"/>
+      <c r="U33" s="125" t="s">
         <v>220</v>
       </c>
-      <c r="V33" s="125" t="s">
+      <c r="V33" s="126" t="s">
         <v>221</v>
       </c>
     </row>
@@ -6654,15 +6691,15 @@
       <c r="P34" s="87">
         <v>51315</v>
       </c>
-      <c r="R34" s="126" t="s">
+      <c r="R34" s="127" t="s">
         <v>105</v>
       </c>
-      <c r="S34" s="113"/>
-      <c r="T34" s="113"/>
-      <c r="U34" s="128" t="s">
+      <c r="S34" s="114"/>
+      <c r="T34" s="114"/>
+      <c r="U34" s="129" t="s">
         <v>223</v>
       </c>
-      <c r="V34" s="129"/>
+      <c r="V34" s="130"/>
     </row>
     <row r="35" spans="1:22" ht="19" x14ac:dyDescent="0.3">
       <c r="A35" s="17"/>
@@ -6681,13 +6718,13 @@
       <c r="N35" s="15"/>
       <c r="O35" s="15"/>
       <c r="P35" s="15"/>
-      <c r="R35" s="127" t="s">
+      <c r="R35" s="128" t="s">
         <v>222</v>
       </c>
-      <c r="S35" s="113"/>
-      <c r="T35" s="113"/>
-      <c r="U35" s="128"/>
-      <c r="V35" s="129" t="s">
+      <c r="S35" s="114"/>
+      <c r="T35" s="114"/>
+      <c r="U35" s="129"/>
+      <c r="V35" s="130" t="s">
         <v>223</v>
       </c>
     </row>
@@ -6736,51 +6773,51 @@
         <f>SUM(P5:P35)</f>
         <v>304565</v>
       </c>
-      <c r="R36" s="116" t="s">
+      <c r="R36" s="117" t="s">
         <v>224</v>
       </c>
-      <c r="S36" s="113"/>
-      <c r="T36" s="113"/>
-      <c r="U36" s="128"/>
-      <c r="V36" s="129"/>
+      <c r="S36" s="114"/>
+      <c r="T36" s="114"/>
+      <c r="U36" s="129"/>
+      <c r="V36" s="130"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="R37" s="114"/>
-      <c r="S37" s="113"/>
-      <c r="T37" s="113"/>
-      <c r="U37" s="128"/>
-      <c r="V37" s="129"/>
+      <c r="R37" s="115"/>
+      <c r="S37" s="114"/>
+      <c r="T37" s="114"/>
+      <c r="U37" s="129"/>
+      <c r="V37" s="130"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="R38" s="126" t="s">
+      <c r="R38" s="127" t="s">
         <v>222</v>
       </c>
-      <c r="S38" s="113"/>
-      <c r="T38" s="113"/>
-      <c r="U38" s="128">
+      <c r="S38" s="114"/>
+      <c r="T38" s="114"/>
+      <c r="U38" s="129">
         <v>106745</v>
       </c>
-      <c r="V38" s="129"/>
+      <c r="V38" s="130"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="R39" s="132" t="s">
+      <c r="R39" s="133" t="s">
         <v>108</v>
       </c>
-      <c r="S39" s="113"/>
-      <c r="T39" s="113"/>
-      <c r="U39" s="128"/>
-      <c r="V39" s="133">
+      <c r="S39" s="114"/>
+      <c r="T39" s="114"/>
+      <c r="U39" s="129"/>
+      <c r="V39" s="134">
         <v>720</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="R40" s="132" t="s">
+      <c r="R40" s="133" t="s">
         <v>225</v>
       </c>
-      <c r="S40" s="113"/>
-      <c r="T40" s="113"/>
-      <c r="U40" s="128"/>
-      <c r="V40" s="133" t="s">
+      <c r="S40" s="114"/>
+      <c r="T40" s="114"/>
+      <c r="U40" s="129"/>
+      <c r="V40" s="134" t="s">
         <v>227</v>
       </c>
     </row>
@@ -6788,13 +6825,13 @@
       <c r="A41" s="88" t="s">
         <v>179</v>
       </c>
-      <c r="R41" s="132" t="s">
+      <c r="R41" s="133" t="s">
         <v>226</v>
       </c>
-      <c r="S41" s="113"/>
-      <c r="T41" s="113"/>
-      <c r="U41" s="128"/>
-      <c r="V41" s="133" t="s">
+      <c r="S41" s="114"/>
+      <c r="T41" s="114"/>
+      <c r="U41" s="129"/>
+      <c r="V41" s="134" t="s">
         <v>228</v>
       </c>
     </row>
@@ -6833,13 +6870,13 @@
         <v>67</v>
       </c>
       <c r="P42" s="21"/>
-      <c r="R42" s="132" t="s">
+      <c r="R42" s="133" t="s">
         <v>70</v>
       </c>
-      <c r="S42" s="113"/>
-      <c r="T42" s="113"/>
-      <c r="U42" s="128"/>
-      <c r="V42" s="133">
+      <c r="S42" s="114"/>
+      <c r="T42" s="114"/>
+      <c r="U42" s="129"/>
+      <c r="V42" s="134">
         <v>1075</v>
       </c>
     </row>
@@ -6862,13 +6899,13 @@
       <c r="N43" s="21"/>
       <c r="O43" s="21"/>
       <c r="P43" s="21"/>
-      <c r="R43" s="132" t="s">
+      <c r="R43" s="133" t="s">
         <v>84</v>
       </c>
-      <c r="S43" s="113"/>
-      <c r="T43" s="113"/>
-      <c r="U43" s="128"/>
-      <c r="V43" s="133" t="s">
+      <c r="S43" s="114"/>
+      <c r="T43" s="114"/>
+      <c r="U43" s="129"/>
+      <c r="V43" s="134" t="s">
         <v>229</v>
       </c>
     </row>
@@ -6911,13 +6948,13 @@
       <c r="P44" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="R44" s="132" t="s">
+      <c r="R44" s="133" t="s">
         <v>88</v>
       </c>
-      <c r="S44" s="113"/>
-      <c r="T44" s="113"/>
-      <c r="U44" s="128"/>
-      <c r="V44" s="133">
+      <c r="S44" s="114"/>
+      <c r="T44" s="114"/>
+      <c r="U44" s="129"/>
+      <c r="V44" s="134">
         <v>760</v>
       </c>
     </row>
@@ -6942,13 +6979,13 @@
       <c r="N45" s="15"/>
       <c r="O45" s="15"/>
       <c r="P45" s="15"/>
-      <c r="R45" s="132" t="s">
+      <c r="R45" s="133" t="s">
         <v>90</v>
       </c>
-      <c r="S45" s="113"/>
-      <c r="T45" s="113"/>
-      <c r="U45" s="128"/>
-      <c r="V45" s="133" t="s">
+      <c r="S45" s="114"/>
+      <c r="T45" s="114"/>
+      <c r="U45" s="129"/>
+      <c r="V45" s="134" t="s">
         <v>230</v>
       </c>
     </row>
@@ -6973,13 +7010,13 @@
       <c r="N46" s="15"/>
       <c r="O46" s="15"/>
       <c r="P46" s="15"/>
-      <c r="R46" s="132" t="s">
+      <c r="R46" s="133" t="s">
         <v>106</v>
       </c>
-      <c r="S46" s="113"/>
-      <c r="T46" s="113"/>
-      <c r="U46" s="128"/>
-      <c r="V46" s="133" t="s">
+      <c r="S46" s="114"/>
+      <c r="T46" s="114"/>
+      <c r="U46" s="129"/>
+      <c r="V46" s="134" t="s">
         <v>113</v>
       </c>
     </row>
@@ -7004,13 +7041,13 @@
       <c r="N47" s="15"/>
       <c r="O47" s="15"/>
       <c r="P47" s="15"/>
-      <c r="R47" s="114" t="s">
+      <c r="R47" s="117" t="s">
         <v>231</v>
       </c>
-      <c r="S47" s="113"/>
-      <c r="T47" s="113"/>
-      <c r="U47" s="128"/>
-      <c r="V47" s="129"/>
+      <c r="S47" s="114"/>
+      <c r="T47" s="114"/>
+      <c r="U47" s="129"/>
+      <c r="V47" s="130"/>
     </row>
     <row r="48" spans="1:22" ht="19" x14ac:dyDescent="0.3">
       <c r="A48" s="17" t="s">
@@ -7037,11 +7074,11 @@
       <c r="N48" s="15"/>
       <c r="O48" s="15"/>
       <c r="P48" s="15"/>
-      <c r="R48" s="114"/>
-      <c r="S48" s="113"/>
-      <c r="T48" s="113"/>
-      <c r="U48" s="128"/>
-      <c r="V48" s="129"/>
+      <c r="R48" s="115"/>
+      <c r="S48" s="114"/>
+      <c r="T48" s="114"/>
+      <c r="U48" s="129"/>
+      <c r="V48" s="130"/>
     </row>
     <row r="49" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A49" s="17" t="s">
@@ -7064,16 +7101,16 @@
       <c r="N49" s="15"/>
       <c r="O49" s="15"/>
       <c r="P49" s="15"/>
-      <c r="R49" s="126" t="s">
+      <c r="R49" s="127" t="s">
         <v>222</v>
       </c>
-      <c r="S49" s="113"/>
-      <c r="T49" s="113"/>
-      <c r="U49" s="128">
+      <c r="S49" s="114"/>
+      <c r="T49" s="114"/>
+      <c r="U49" s="129">
         <v>51315</v>
       </c>
-      <c r="V49" s="129"/>
-      <c r="W49" s="112" t="s">
+      <c r="V49" s="130"/>
+      <c r="W49" s="113" t="s">
         <v>235</v>
       </c>
     </row>
@@ -7098,13 +7135,13 @@
       <c r="N50" s="15"/>
       <c r="O50" s="15"/>
       <c r="P50" s="15"/>
-      <c r="R50" s="132" t="s">
+      <c r="R50" s="133" t="s">
         <v>103</v>
       </c>
-      <c r="S50" s="113"/>
-      <c r="T50" s="113"/>
-      <c r="U50" s="128"/>
-      <c r="V50" s="129">
+      <c r="S50" s="114"/>
+      <c r="T50" s="114"/>
+      <c r="U50" s="129"/>
+      <c r="V50" s="130">
         <v>51315</v>
       </c>
     </row>
@@ -7131,13 +7168,13 @@
       <c r="N51" s="15"/>
       <c r="O51" s="15"/>
       <c r="P51" s="15"/>
-      <c r="R51" s="114" t="s">
+      <c r="R51" s="117" t="s">
         <v>232</v>
       </c>
-      <c r="S51" s="113"/>
-      <c r="T51" s="113"/>
-      <c r="U51" s="128"/>
-      <c r="V51" s="129"/>
+      <c r="S51" s="114"/>
+      <c r="T51" s="114"/>
+      <c r="U51" s="129"/>
+      <c r="V51" s="130"/>
     </row>
     <row r="52" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A52" s="17" t="s">
@@ -7160,11 +7197,11 @@
       <c r="N52" s="15"/>
       <c r="O52" s="15"/>
       <c r="P52" s="15"/>
-      <c r="R52" s="114"/>
-      <c r="S52" s="113"/>
-      <c r="T52" s="113"/>
-      <c r="U52" s="128"/>
-      <c r="V52" s="129"/>
+      <c r="R52" s="115"/>
+      <c r="S52" s="114"/>
+      <c r="T52" s="114"/>
+      <c r="U52" s="129"/>
+      <c r="V52" s="130"/>
     </row>
     <row r="53" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A53" s="17" t="s">
@@ -7189,15 +7226,15 @@
       <c r="N53" s="15"/>
       <c r="O53" s="15"/>
       <c r="P53" s="15"/>
-      <c r="R53" s="134" t="s">
+      <c r="R53" s="135" t="s">
         <v>103</v>
       </c>
-      <c r="S53" s="113"/>
-      <c r="T53" s="113"/>
-      <c r="U53" s="135" t="s">
+      <c r="S53" s="114"/>
+      <c r="T53" s="114"/>
+      <c r="U53" s="136" t="s">
         <v>233</v>
       </c>
-      <c r="V53" s="129"/>
+      <c r="V53" s="130"/>
     </row>
     <row r="54" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A54" s="17" t="s">
@@ -7220,13 +7257,13 @@
       <c r="N54" s="15"/>
       <c r="O54" s="15"/>
       <c r="P54" s="15"/>
-      <c r="R54" s="132" t="s">
+      <c r="R54" s="133" t="s">
         <v>104</v>
       </c>
-      <c r="S54" s="113"/>
-      <c r="T54" s="113"/>
-      <c r="U54" s="128"/>
-      <c r="V54" s="129">
+      <c r="S54" s="114"/>
+      <c r="T54" s="114"/>
+      <c r="U54" s="129"/>
+      <c r="V54" s="130">
         <v>52780</v>
       </c>
     </row>
@@ -7255,13 +7292,13 @@
       <c r="N55" s="15"/>
       <c r="O55" s="15"/>
       <c r="P55" s="15"/>
-      <c r="R55" s="117" t="s">
+      <c r="R55" s="118" t="s">
         <v>234</v>
       </c>
-      <c r="S55" s="115"/>
-      <c r="T55" s="115"/>
-      <c r="U55" s="130"/>
-      <c r="V55" s="131"/>
+      <c r="S55" s="116"/>
+      <c r="T55" s="116"/>
+      <c r="U55" s="131"/>
+      <c r="V55" s="132"/>
     </row>
     <row r="56" spans="1:23" ht="19" x14ac:dyDescent="0.3">
       <c r="A56" s="17" t="s">
@@ -7331,7 +7368,7 @@
       <c r="N58" s="15"/>
       <c r="O58" s="15"/>
       <c r="P58" s="15"/>
-      <c r="R58" s="111" t="s">
+      <c r="R58" s="112" t="s">
         <v>236</v>
       </c>
     </row>
@@ -7356,7 +7393,7 @@
       <c r="N59" s="15"/>
       <c r="O59" s="15"/>
       <c r="P59" s="15"/>
-      <c r="R59" s="111" t="s">
+      <c r="R59" s="112" t="s">
         <v>237</v>
       </c>
     </row>
@@ -7385,7 +7422,7 @@
       <c r="N60" s="15"/>
       <c r="O60" s="15"/>
       <c r="P60" s="15"/>
-      <c r="R60" s="111" t="s">
+      <c r="R60" s="112" t="s">
         <v>238</v>
       </c>
     </row>
@@ -7412,7 +7449,7 @@
       <c r="N61" s="15"/>
       <c r="O61" s="15"/>
       <c r="P61" s="15"/>
-      <c r="R61" s="111" t="s">
+      <c r="R61" s="112" t="s">
         <v>239</v>
       </c>
     </row>

--- a/ACCY122/Session/S04/ACCY122 L4 Workbook.xlsx
+++ b/ACCY122/Session/S04/ACCY122 L4 Workbook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Session/S04/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ACCY122\Session\S04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A8D081-7CC5-B447-BF76-1030E2D53780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9DF03C-3710-416F-9498-000A180BBFEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28940" windowHeight="18660" activeTab="4" xr2:uid="{49300C88-9C68-40D1-BFDB-69B44FEEA068}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="11" xr2:uid="{49300C88-9C68-40D1-BFDB-69B44FEEA068}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,9 @@
     <sheet name="5.1A" sheetId="8" r:id="rId7"/>
     <sheet name="P5.1 Answer" sheetId="5" r:id="rId8"/>
     <sheet name="P5.5" sheetId="7" r:id="rId9"/>
+    <sheet name="4.12 A" sheetId="10" r:id="rId10"/>
+    <sheet name="5.3 A" sheetId="11" r:id="rId11"/>
+    <sheet name="ex" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -117,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="352">
   <si>
     <t>Balanced Day Adjustments</t>
   </si>
@@ -889,6 +892,370 @@
   </si>
   <si>
     <t>ref 6 - telecom bill owed on credit</t>
+  </si>
+  <si>
+    <t>insurance expense</t>
+  </si>
+  <si>
+    <t>prepaid insurance</t>
+  </si>
+  <si>
+    <t>(3 mths of insurance expired (4500/12)x3 = 1125)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">supplies expense </t>
+  </si>
+  <si>
+    <t xml:space="preserve">supplies  </t>
+  </si>
+  <si>
+    <t>(supplies used up 720-430=290)</t>
+  </si>
+  <si>
+    <t>accumulated dep - shop shelving</t>
+  </si>
+  <si>
+    <t>depreciation expense</t>
+  </si>
+  <si>
+    <t>salaries expense</t>
+  </si>
+  <si>
+    <t>cash at bank</t>
+  </si>
+  <si>
+    <t>(dep accumulated ((24k-2k)/10)/2 = 1.1k)</t>
+  </si>
+  <si>
+    <t>salaries payable</t>
+  </si>
+  <si>
+    <t>(1mth earned from rental fees 4.8k/4=1.2k)</t>
+  </si>
+  <si>
+    <t>unearned rental fees</t>
+  </si>
+  <si>
+    <t>rental fees revenue</t>
+  </si>
+  <si>
+    <t>(accrued salaries)</t>
+  </si>
+  <si>
+    <t>a)</t>
+  </si>
+  <si>
+    <t>account title</t>
+  </si>
+  <si>
+    <t>DR</t>
+  </si>
+  <si>
+    <t>CR</t>
+  </si>
+  <si>
+    <t>Unadjusted trial bal</t>
+  </si>
+  <si>
+    <t>adjustments</t>
+  </si>
+  <si>
+    <t>adjusted trial bal</t>
+  </si>
+  <si>
+    <t>income statement</t>
+  </si>
+  <si>
+    <t>bal sheet</t>
+  </si>
+  <si>
+    <t>accounts receivable</t>
+  </si>
+  <si>
+    <t>equipment</t>
+  </si>
+  <si>
+    <t>accounts payable</t>
+  </si>
+  <si>
+    <t>heather harris - capital</t>
+  </si>
+  <si>
+    <t>heather harris - drawings</t>
+  </si>
+  <si>
+    <t>service revenue</t>
+  </si>
+  <si>
+    <t>wages exp</t>
+  </si>
+  <si>
+    <t>electricity exp</t>
+  </si>
+  <si>
+    <t>sundry exp</t>
+  </si>
+  <si>
+    <t>accum dep - equip</t>
+  </si>
+  <si>
+    <t>c)</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>details</t>
+  </si>
+  <si>
+    <t>(accrued wages)</t>
+  </si>
+  <si>
+    <t>insurance exp</t>
+  </si>
+  <si>
+    <t>(expired insurance)</t>
+  </si>
+  <si>
+    <t>dep exp</t>
+  </si>
+  <si>
+    <t>(dep on equip)</t>
+  </si>
+  <si>
+    <t>wages payable</t>
+  </si>
+  <si>
+    <t>dep exp - equip</t>
+  </si>
+  <si>
+    <t>profit/loss</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">in income statement - only </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>include</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> revenue and expense</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">in bal sheet - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>exclude</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> revenue, expense</t>
+    </r>
+  </si>
+  <si>
+    <t>b)</t>
+  </si>
+  <si>
+    <t>HEATHER’S H.R. SERVICES</t>
+  </si>
+  <si>
+    <t>for the year ended 30 June 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">income </t>
+  </si>
+  <si>
+    <t>expense</t>
+  </si>
+  <si>
+    <t>statement of changes in owner equity</t>
+  </si>
+  <si>
+    <t>profit for the year</t>
+  </si>
+  <si>
+    <t>heather harris - capital 1 july 2024</t>
+  </si>
+  <si>
+    <t>heather harris - capital 30 jun 2025</t>
+  </si>
+  <si>
+    <t>as at 30 June 2025</t>
+  </si>
+  <si>
+    <t>current assets</t>
+  </si>
+  <si>
+    <t>non current assets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LESS: heather harris - drawings </t>
+  </si>
+  <si>
+    <t>LESS: accum dep - equip</t>
+  </si>
+  <si>
+    <t>total assets</t>
+  </si>
+  <si>
+    <t>current liability</t>
+  </si>
+  <si>
+    <t>non current liability</t>
+  </si>
+  <si>
+    <t>total liability</t>
+  </si>
+  <si>
+    <t>net assets (ta-tl)</t>
+  </si>
+  <si>
+    <t>equity</t>
+  </si>
+  <si>
+    <t>total equity</t>
+  </si>
+  <si>
+    <t>closing entries</t>
+  </si>
+  <si>
+    <t>1. close income account</t>
+  </si>
+  <si>
+    <t>2. close expense account</t>
+  </si>
+  <si>
+    <t>3. xfer pnl to capital account</t>
+  </si>
+  <si>
+    <t>4. xfer drawings to capital account</t>
+  </si>
+  <si>
+    <t>profit/loss summary</t>
+  </si>
+  <si>
+    <t>(close income acc)</t>
+  </si>
+  <si>
+    <t>p/l summary acc is dr- and cr+</t>
+  </si>
+  <si>
+    <t>(close exp acc)</t>
+  </si>
+  <si>
+    <t>(xfer pnl to capital acc)</t>
+  </si>
+  <si>
+    <t>drawings is dr + and cr -</t>
+  </si>
+  <si>
+    <t>(xfer drawings to capital acc)</t>
+  </si>
+  <si>
+    <t>accrued exp = u got exp but havent paid so dr exp and cr payable (creditor)</t>
+  </si>
+  <si>
+    <t>accrued income = u got income but havent been paid so dr AR (debtor) and cr rev</t>
+  </si>
+  <si>
+    <t>dr</t>
+  </si>
+  <si>
+    <t>cr</t>
+  </si>
+  <si>
+    <t>accrued exp</t>
+  </si>
+  <si>
+    <t>unadjusted trial bal</t>
+  </si>
+  <si>
+    <t>adjustment</t>
+  </si>
+  <si>
+    <t>insurance expired</t>
+  </si>
+  <si>
+    <t>dep on equip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wages payable </t>
+  </si>
+  <si>
+    <t>p/l</t>
+  </si>
+  <si>
+    <t>income</t>
+  </si>
+  <si>
+    <t>Statement of Changes in Owner Equity</t>
+  </si>
+  <si>
+    <t>heather harris - capital 1July24</t>
+  </si>
+  <si>
+    <t>Less: heather harris - drawings</t>
+  </si>
+  <si>
+    <t>heather harris - capital 30Jun25</t>
+  </si>
+  <si>
+    <t>non-current assets</t>
+  </si>
+  <si>
+    <t>non-current liability</t>
+  </si>
+  <si>
+    <t>1. close income acc</t>
+  </si>
+  <si>
+    <t>2. close exp acc</t>
+  </si>
+  <si>
+    <t>3. xfer p/l to capital acc</t>
+  </si>
+  <si>
+    <t>4. xfer drawings to capital acc</t>
+  </si>
+  <si>
+    <t>p/l summary acc</t>
+  </si>
+  <si>
+    <t>(xfer p/l to capital acc)</t>
+  </si>
+  <si>
+    <t>drawings</t>
   </si>
 </sst>
 </file>
@@ -1003,12 +1370,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1046,6 +1407,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1116,7 +1485,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1448,11 +1817,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1647,8 +2027,91 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1659,70 +2122,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1768,8 +2169,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1089950" y="648411"/>
-          <a:ext cx="5959855" cy="5798817"/>
+          <a:off x="1004363" y="656694"/>
+          <a:ext cx="5189572" cy="5884404"/>
           <a:chOff x="0" y="78429"/>
           <a:chExt cx="6059328" cy="3928254"/>
         </a:xfrm>
@@ -2572,6 +2973,171 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>301046</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>158911</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>520075</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>159925</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B6F8A16-603C-7FB4-80A9-6A5C9405F0E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="301046" y="158911"/>
+          <a:ext cx="4495426" cy="3430014"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>301998</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1912</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>559973</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>187578</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B02AF9A9-0868-1FB6-0E94-2D6135E05F9A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="301998" y="192412"/>
+          <a:ext cx="6072366" cy="6033188"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>80597</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>146538</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>402981</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>89765</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A8C40406-E74C-4924-A20B-B840B1F78656}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="80597" y="146538"/>
+          <a:ext cx="5392615" cy="5357823"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Manek Mukesh" id="{D1B72572-4EE9-4B5D-AA50-003122841091}" userId="7baad15b6bef9919" providerId="Windows Live"/>
@@ -2926,8 +3492,2007 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3154719-4B7A-4BD1-A273-F4DC249F84D4}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39757E1D-A610-4C37-9A13-03A35315D65F}">
+  <dimension ref="B4:M25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="11" max="11" width="42" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I4" t="s">
+        <v>93</v>
+      </c>
+      <c r="J4" t="s">
+        <v>126</v>
+      </c>
+      <c r="K4" t="s">
+        <v>127</v>
+      </c>
+      <c r="L4" t="s">
+        <v>220</v>
+      </c>
+      <c r="M4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="127">
+        <v>46203</v>
+      </c>
+      <c r="K5" t="s">
+        <v>246</v>
+      </c>
+      <c r="L5">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="6" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="K6" s="128" t="s">
+        <v>247</v>
+      </c>
+      <c r="M6">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="7" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="K7" s="129" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="9" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9" s="127">
+        <v>46203</v>
+      </c>
+      <c r="K9" t="s">
+        <v>249</v>
+      </c>
+      <c r="L9">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="10" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="K10" s="128" t="s">
+        <v>250</v>
+      </c>
+      <c r="M10">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="K11" s="129" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13" s="127">
+        <v>46203</v>
+      </c>
+      <c r="K13" t="s">
+        <v>253</v>
+      </c>
+      <c r="L13">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="14" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="K14" s="128" t="s">
+        <v>252</v>
+      </c>
+      <c r="M14">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="15" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="K15" s="129" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="I17">
+        <v>4</v>
+      </c>
+      <c r="J17" s="127">
+        <v>46203</v>
+      </c>
+      <c r="K17" t="s">
+        <v>259</v>
+      </c>
+      <c r="L17">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K18" s="128" t="s">
+        <v>260</v>
+      </c>
+      <c r="M18">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K19" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="I21">
+        <v>5</v>
+      </c>
+      <c r="J21" s="127">
+        <v>46203</v>
+      </c>
+      <c r="K21" t="s">
+        <v>254</v>
+      </c>
+      <c r="L21">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B22" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="K22" s="128" t="s">
+        <v>257</v>
+      </c>
+      <c r="M22">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B23" s="85" t="s">
+        <v>328</v>
+      </c>
+      <c r="K23" s="129" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L24" s="131">
+        <f>SUM(L5:L23)</f>
+        <v>6115</v>
+      </c>
+      <c r="M24" s="131">
+        <f>SUM(M5:M23)</f>
+        <v>6115</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33FC6C69-AD84-443C-9977-C0C126AB0836}">
+  <dimension ref="B2:AJ79"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="22.85546875" customWidth="1"/>
+    <col min="10" max="10" width="23.85546875" customWidth="1"/>
+    <col min="13" max="13" width="22" customWidth="1"/>
+    <col min="26" max="26" width="28.42578125" customWidth="1"/>
+    <col min="30" max="30" width="37.7109375" customWidth="1"/>
+    <col min="34" max="34" width="22.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="12:36" x14ac:dyDescent="0.25">
+      <c r="M2" s="85" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="3" spans="12:36" x14ac:dyDescent="0.25">
+      <c r="M3" s="85" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="6" spans="12:36" x14ac:dyDescent="0.25">
+      <c r="L6" s="133" t="s">
+        <v>262</v>
+      </c>
+      <c r="M6" t="s">
+        <v>263</v>
+      </c>
+      <c r="N6" s="136" t="s">
+        <v>266</v>
+      </c>
+      <c r="O6" s="136"/>
+      <c r="P6" s="136" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q6" s="136"/>
+      <c r="R6" s="136" t="s">
+        <v>268</v>
+      </c>
+      <c r="S6" s="136"/>
+      <c r="T6" s="136" t="s">
+        <v>269</v>
+      </c>
+      <c r="U6" s="136"/>
+      <c r="V6" s="136" t="s">
+        <v>270</v>
+      </c>
+      <c r="W6" s="136"/>
+      <c r="Y6" s="133" t="s">
+        <v>294</v>
+      </c>
+      <c r="Z6" s="136" t="s">
+        <v>295</v>
+      </c>
+      <c r="AA6" s="136"/>
+      <c r="AB6" s="136"/>
+      <c r="AD6" s="136" t="s">
+        <v>295</v>
+      </c>
+      <c r="AE6" s="136"/>
+      <c r="AF6" s="136"/>
+      <c r="AH6" s="136" t="s">
+        <v>295</v>
+      </c>
+      <c r="AI6" s="136"/>
+      <c r="AJ6" s="136"/>
+    </row>
+    <row r="7" spans="12:36" x14ac:dyDescent="0.25">
+      <c r="N7" s="72" t="s">
+        <v>264</v>
+      </c>
+      <c r="O7" s="72" t="s">
+        <v>265</v>
+      </c>
+      <c r="P7" s="72" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q7" s="72" t="s">
+        <v>265</v>
+      </c>
+      <c r="R7" s="72" t="s">
+        <v>264</v>
+      </c>
+      <c r="S7" s="72" t="s">
+        <v>265</v>
+      </c>
+      <c r="T7" s="72" t="s">
+        <v>264</v>
+      </c>
+      <c r="U7" s="72" t="s">
+        <v>265</v>
+      </c>
+      <c r="V7" s="72" t="s">
+        <v>264</v>
+      </c>
+      <c r="W7" s="72" t="s">
+        <v>265</v>
+      </c>
+      <c r="Z7" s="136" t="s">
+        <v>269</v>
+      </c>
+      <c r="AA7" s="136"/>
+      <c r="AB7" s="136"/>
+      <c r="AD7" s="136" t="s">
+        <v>299</v>
+      </c>
+      <c r="AE7" s="136"/>
+      <c r="AF7" s="136"/>
+      <c r="AH7" s="136" t="s">
+        <v>299</v>
+      </c>
+      <c r="AI7" s="136"/>
+      <c r="AJ7" s="136"/>
+    </row>
+    <row r="8" spans="12:36" x14ac:dyDescent="0.25">
+      <c r="M8" t="s">
+        <v>255</v>
+      </c>
+      <c r="N8">
+        <v>80000</v>
+      </c>
+      <c r="R8">
+        <v>80000</v>
+      </c>
+      <c r="V8">
+        <v>80000</v>
+      </c>
+      <c r="Z8" s="136" t="s">
+        <v>296</v>
+      </c>
+      <c r="AA8" s="136"/>
+      <c r="AB8" s="136"/>
+      <c r="AD8" s="136" t="s">
+        <v>296</v>
+      </c>
+      <c r="AE8" s="136"/>
+      <c r="AF8" s="136"/>
+      <c r="AH8" s="136" t="s">
+        <v>303</v>
+      </c>
+      <c r="AI8" s="136"/>
+      <c r="AJ8" s="136"/>
+    </row>
+    <row r="9" spans="12:36" x14ac:dyDescent="0.25">
+      <c r="M9" t="s">
+        <v>271</v>
+      </c>
+      <c r="N9">
+        <v>74000</v>
+      </c>
+      <c r="R9">
+        <v>74000</v>
+      </c>
+      <c r="V9">
+        <v>74000</v>
+      </c>
+      <c r="Z9" s="132"/>
+      <c r="AA9" s="72" t="s">
+        <v>264</v>
+      </c>
+      <c r="AB9" s="72" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="10" spans="12:36" x14ac:dyDescent="0.25">
+      <c r="M10" t="s">
+        <v>247</v>
+      </c>
+      <c r="N10">
+        <v>24000</v>
+      </c>
+      <c r="Q10">
+        <v>16000</v>
+      </c>
+      <c r="R10">
+        <v>8000</v>
+      </c>
+      <c r="V10">
+        <v>8000</v>
+      </c>
+      <c r="Z10" s="134" t="s">
+        <v>297</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>301</v>
+      </c>
+      <c r="AF10">
+        <v>204000</v>
+      </c>
+      <c r="AH10" s="133" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="11" spans="12:36" x14ac:dyDescent="0.25">
+      <c r="M11" t="s">
+        <v>272</v>
+      </c>
+      <c r="N11">
+        <v>230000</v>
+      </c>
+      <c r="R11">
+        <v>230000</v>
+      </c>
+      <c r="V11">
+        <v>230000</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>276</v>
+      </c>
+      <c r="AB11">
+        <v>340000</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>300</v>
+      </c>
+      <c r="AF11">
+        <v>36000</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>255</v>
+      </c>
+      <c r="AI11">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="12" spans="12:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M12" t="s">
+        <v>280</v>
+      </c>
+      <c r="O12">
+        <v>60000</v>
+      </c>
+      <c r="Q12">
+        <v>60000</v>
+      </c>
+      <c r="S12">
+        <v>120000</v>
+      </c>
+      <c r="W12">
+        <v>120000</v>
+      </c>
+      <c r="AF12" s="131">
+        <f>SUM(AF10:AF11)</f>
+        <v>240000</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>271</v>
+      </c>
+      <c r="AI12">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="13" spans="12:36" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="M13" t="s">
+        <v>273</v>
+      </c>
+      <c r="O13">
+        <v>64000</v>
+      </c>
+      <c r="S13">
+        <v>64000</v>
+      </c>
+      <c r="W13">
+        <v>64000</v>
+      </c>
+      <c r="Z13" s="133" t="s">
+        <v>298</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>306</v>
+      </c>
+      <c r="AF13">
+        <v>50000</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>247</v>
+      </c>
+      <c r="AI13">
+        <v>8000</v>
+      </c>
+      <c r="AJ13">
+        <f>SUM(AI11:AI13)</f>
+        <v>162000</v>
+      </c>
+    </row>
+    <row r="14" spans="12:36" x14ac:dyDescent="0.25">
+      <c r="M14" t="s">
+        <v>274</v>
+      </c>
+      <c r="O14">
+        <v>204000</v>
+      </c>
+      <c r="S14">
+        <v>204000</v>
+      </c>
+      <c r="W14">
+        <v>204000</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA14">
+        <v>148000</v>
+      </c>
+    </row>
+    <row r="15" spans="12:36" x14ac:dyDescent="0.25">
+      <c r="M15" t="s">
+        <v>275</v>
+      </c>
+      <c r="N15">
+        <v>50000</v>
+      </c>
+      <c r="R15">
+        <v>50000</v>
+      </c>
+      <c r="V15">
+        <v>50000</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>278</v>
+      </c>
+      <c r="AA15">
+        <v>54000</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>302</v>
+      </c>
+      <c r="AF15">
+        <v>190000</v>
+      </c>
+      <c r="AH15" s="133" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="16" spans="12:36" x14ac:dyDescent="0.25">
+      <c r="M16" t="s">
+        <v>276</v>
+      </c>
+      <c r="O16">
+        <v>340000</v>
+      </c>
+      <c r="S16">
+        <v>340000</v>
+      </c>
+      <c r="U16">
+        <v>340000</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>279</v>
+      </c>
+      <c r="AA16">
+        <v>26000</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>272</v>
+      </c>
+      <c r="AI16">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="17" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="M17" t="s">
+        <v>277</v>
+      </c>
+      <c r="N17">
+        <v>130000</v>
+      </c>
+      <c r="P17">
+        <v>18000</v>
+      </c>
+      <c r="R17">
+        <v>148000</v>
+      </c>
+      <c r="T17">
+        <v>148000</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>285</v>
+      </c>
+      <c r="AA17">
+        <v>16000</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>307</v>
+      </c>
+      <c r="AI17">
+        <v>120000</v>
+      </c>
+      <c r="AJ17">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="18" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="M18" t="s">
+        <v>278</v>
+      </c>
+      <c r="N18">
+        <v>54000</v>
+      </c>
+      <c r="R18">
+        <v>54000</v>
+      </c>
+      <c r="T18">
+        <v>54000</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>290</v>
+      </c>
+      <c r="AA18">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="19" spans="10:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M19" t="s">
+        <v>279</v>
+      </c>
+      <c r="N19">
+        <v>26000</v>
+      </c>
+      <c r="R19">
+        <v>26000</v>
+      </c>
+      <c r="T19">
+        <v>26000</v>
+      </c>
+      <c r="AH19" s="133" t="s">
+        <v>308</v>
+      </c>
+      <c r="AJ19" s="131">
+        <f>SUM(AJ9:AJ18)</f>
+        <v>272000</v>
+      </c>
+    </row>
+    <row r="20" spans="10:36" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N20" s="131">
+        <f>SUM(N8:N19)</f>
+        <v>668000</v>
+      </c>
+      <c r="O20" s="131">
+        <f>SUM(O8:O19)</f>
+        <v>668000</v>
+      </c>
+      <c r="Z20" s="133" t="s">
+        <v>291</v>
+      </c>
+      <c r="AA20">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="21" spans="10:36" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M21" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q21">
+        <v>18000</v>
+      </c>
+      <c r="S21">
+        <v>18000</v>
+      </c>
+      <c r="W21">
+        <v>18000</v>
+      </c>
+      <c r="AA21" s="131">
+        <f>SUM(AA10:AA20)</f>
+        <v>340000</v>
+      </c>
+      <c r="AB21" s="131">
+        <f>SUM(AB10:AB20)</f>
+        <v>340000</v>
+      </c>
+      <c r="AH21" s="133" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="22" spans="10:36" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="M22" t="s">
+        <v>285</v>
+      </c>
+      <c r="P22">
+        <v>16000</v>
+      </c>
+      <c r="R22">
+        <v>16000</v>
+      </c>
+      <c r="T22">
+        <v>16000</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>273</v>
+      </c>
+      <c r="AI22">
+        <v>64000</v>
+      </c>
+    </row>
+    <row r="23" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="M23" t="s">
+        <v>290</v>
+      </c>
+      <c r="P23">
+        <v>60000</v>
+      </c>
+      <c r="R23">
+        <v>60000</v>
+      </c>
+      <c r="T23">
+        <v>60000</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>289</v>
+      </c>
+      <c r="AI23">
+        <v>18000</v>
+      </c>
+      <c r="AJ23">
+        <f>SUM(AI22:AI23)</f>
+        <v>82000</v>
+      </c>
+    </row>
+    <row r="24" spans="10:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P24" s="131">
+        <f t="shared" ref="P24:W24" si="0">SUM(P8:P23)</f>
+        <v>94000</v>
+      </c>
+      <c r="Q24" s="131">
+        <f t="shared" si="0"/>
+        <v>94000</v>
+      </c>
+      <c r="R24" s="131">
+        <f t="shared" si="0"/>
+        <v>746000</v>
+      </c>
+      <c r="S24" s="131">
+        <f t="shared" si="0"/>
+        <v>746000</v>
+      </c>
+      <c r="T24" s="131">
+        <f t="shared" si="0"/>
+        <v>304000</v>
+      </c>
+      <c r="U24" s="131">
+        <f t="shared" si="0"/>
+        <v>340000</v>
+      </c>
+      <c r="V24" s="131">
+        <f t="shared" si="0"/>
+        <v>442000</v>
+      </c>
+      <c r="W24" s="131">
+        <f t="shared" si="0"/>
+        <v>406000</v>
+      </c>
+    </row>
+    <row r="25" spans="10:36" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="M25" t="s">
+        <v>291</v>
+      </c>
+      <c r="T25">
+        <v>36000</v>
+      </c>
+      <c r="W25">
+        <v>36000</v>
+      </c>
+      <c r="AH25" s="133" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="26" spans="10:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="T26" s="131">
+        <f>SUM(T24:T25)</f>
+        <v>340000</v>
+      </c>
+      <c r="U26" s="131">
+        <v>340000</v>
+      </c>
+      <c r="V26" s="131">
+        <v>442000</v>
+      </c>
+      <c r="W26" s="131">
+        <f>SUM(W24:W25)</f>
+        <v>442000</v>
+      </c>
+    </row>
+    <row r="27" spans="10:36" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AH27" s="133" t="s">
+        <v>311</v>
+      </c>
+      <c r="AJ27" s="131">
+        <f>SUM(AJ21:AJ26)</f>
+        <v>82000</v>
+      </c>
+    </row>
+    <row r="28" spans="10:36" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="10:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J29" s="85" t="s">
+        <v>315</v>
+      </c>
+      <c r="K29" s="85"/>
+      <c r="AH29" s="133" t="s">
+        <v>312</v>
+      </c>
+      <c r="AJ29" s="135">
+        <f>AJ19-AJ27</f>
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="30" spans="10:36" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="J30" s="85" t="s">
+        <v>316</v>
+      </c>
+      <c r="K30" s="85"/>
+    </row>
+    <row r="31" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="J31" s="85" t="s">
+        <v>317</v>
+      </c>
+      <c r="K31" s="85"/>
+      <c r="L31" s="133"/>
+      <c r="AH31" s="133" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="32" spans="10:36" x14ac:dyDescent="0.25">
+      <c r="J32" s="85" t="s">
+        <v>318</v>
+      </c>
+      <c r="K32" s="85"/>
+      <c r="AH32" t="s">
+        <v>302</v>
+      </c>
+      <c r="AJ32">
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="J33" s="85" t="s">
+        <v>319</v>
+      </c>
+      <c r="K33" s="85"/>
+    </row>
+    <row r="34" spans="2:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AH34" s="133" t="s">
+        <v>314</v>
+      </c>
+      <c r="AJ34" s="135">
+        <f>SUM(AJ31:AJ33)</f>
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="35" spans="2:36" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="M35" s="85" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="36" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="B36" s="134" t="s">
+        <v>281</v>
+      </c>
+      <c r="C36" s="132" t="s">
+        <v>282</v>
+      </c>
+      <c r="D36" s="132" t="s">
+        <v>283</v>
+      </c>
+      <c r="E36" s="132" t="s">
+        <v>264</v>
+      </c>
+      <c r="F36" s="132" t="s">
+        <v>265</v>
+      </c>
+      <c r="G36" s="132"/>
+      <c r="I36" s="132" t="s">
+        <v>282</v>
+      </c>
+      <c r="J36" s="132" t="s">
+        <v>283</v>
+      </c>
+      <c r="K36" s="132" t="s">
+        <v>264</v>
+      </c>
+      <c r="L36" s="132" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="37" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="C37" s="127">
+        <v>46203</v>
+      </c>
+      <c r="D37" t="s">
+        <v>277</v>
+      </c>
+      <c r="E37">
+        <v>18000</v>
+      </c>
+      <c r="I37" s="127">
+        <v>46203</v>
+      </c>
+      <c r="J37" t="s">
+        <v>276</v>
+      </c>
+      <c r="K37">
+        <v>340000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="D38" s="128" t="s">
+        <v>336</v>
+      </c>
+      <c r="F38">
+        <v>18000</v>
+      </c>
+      <c r="J38" s="128" t="s">
+        <v>320</v>
+      </c>
+      <c r="L38">
+        <v>340000</v>
+      </c>
+    </row>
+    <row r="39" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="D39" s="129" t="s">
+        <v>284</v>
+      </c>
+      <c r="J39" s="129" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="41" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="C41" s="127">
+        <v>46203</v>
+      </c>
+      <c r="D41" t="s">
+        <v>285</v>
+      </c>
+      <c r="E41">
+        <v>16000</v>
+      </c>
+      <c r="I41" s="127">
+        <v>46203</v>
+      </c>
+      <c r="J41" t="s">
+        <v>320</v>
+      </c>
+      <c r="K41">
+        <f>SUM(L42:L46)</f>
+        <v>304000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="D42" s="128" t="s">
+        <v>247</v>
+      </c>
+      <c r="F42">
+        <v>16000</v>
+      </c>
+      <c r="J42" s="128" t="s">
+        <v>277</v>
+      </c>
+      <c r="L42">
+        <v>148000</v>
+      </c>
+    </row>
+    <row r="43" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="D43" s="129" t="s">
+        <v>286</v>
+      </c>
+      <c r="J43" s="128" t="s">
+        <v>278</v>
+      </c>
+      <c r="L43">
+        <v>54000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="J44" s="128" t="s">
+        <v>279</v>
+      </c>
+      <c r="L44">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="45" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="C45" s="127">
+        <v>46203</v>
+      </c>
+      <c r="D45" t="s">
+        <v>287</v>
+      </c>
+      <c r="E45">
+        <v>60000</v>
+      </c>
+      <c r="J45" s="128" t="s">
+        <v>285</v>
+      </c>
+      <c r="L45">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="46" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>280</v>
+      </c>
+      <c r="F46">
+        <v>60000</v>
+      </c>
+      <c r="J46" s="128" t="s">
+        <v>290</v>
+      </c>
+      <c r="L46">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:36" x14ac:dyDescent="0.25">
+      <c r="D47" s="129" t="s">
+        <v>288</v>
+      </c>
+      <c r="J47" s="129" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="48" spans="2:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E48" s="131">
+        <f>SUM(E37:E47)</f>
+        <v>94000</v>
+      </c>
+      <c r="F48" s="131">
+        <f>SUM(F37:F47)</f>
+        <v>94000</v>
+      </c>
+    </row>
+    <row r="49" spans="9:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="I49" s="127">
+        <v>46203</v>
+      </c>
+      <c r="J49" t="s">
+        <v>320</v>
+      </c>
+      <c r="K49">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="50" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="J50" s="128" t="s">
+        <v>274</v>
+      </c>
+      <c r="L50">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="51" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="J51" s="129" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="53" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I53" s="127">
+        <v>46203</v>
+      </c>
+      <c r="J53" t="s">
+        <v>274</v>
+      </c>
+      <c r="K53">
+        <v>50000</v>
+      </c>
+      <c r="M53" s="85" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="54" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="J54" s="128" t="s">
+        <v>275</v>
+      </c>
+      <c r="L54">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="55" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="J55" s="129" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="61" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I61" s="127"/>
+    </row>
+    <row r="62" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="J62" s="128"/>
+    </row>
+    <row r="63" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="J63" s="129"/>
+    </row>
+    <row r="65" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I65" s="127"/>
+    </row>
+    <row r="66" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="J66" s="128"/>
+    </row>
+    <row r="67" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="J67" s="128"/>
+    </row>
+    <row r="68" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="J68" s="128"/>
+    </row>
+    <row r="69" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="J69" s="128"/>
+    </row>
+    <row r="70" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="J70" s="128"/>
+    </row>
+    <row r="71" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="J71" s="129"/>
+    </row>
+    <row r="73" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I73" s="127"/>
+    </row>
+    <row r="74" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="J74" s="128"/>
+    </row>
+    <row r="75" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="J75" s="129"/>
+    </row>
+    <row r="77" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I77" s="127"/>
+    </row>
+    <row r="78" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="J78" s="128"/>
+    </row>
+    <row r="79" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="J79" s="129"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="AH6:AJ6"/>
+    <mergeCell ref="AH7:AJ7"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:S6"/>
+    <mergeCell ref="T6:U6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="Z7:AB7"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AD6:AF6"/>
+    <mergeCell ref="AD7:AF7"/>
+    <mergeCell ref="AD8:AF8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC8139AE-9094-4A8A-A768-34D7B4B5E1A7}">
+  <dimension ref="B3:Z60"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" customWidth="1"/>
+    <col min="23" max="23" width="31" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="10:26" x14ac:dyDescent="0.25">
+      <c r="J3" t="s">
+        <v>262</v>
+      </c>
+      <c r="K3" t="s">
+        <v>263</v>
+      </c>
+      <c r="L3" s="136" t="s">
+        <v>332</v>
+      </c>
+      <c r="M3" s="136"/>
+      <c r="N3" s="136" t="s">
+        <v>333</v>
+      </c>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="136" t="s">
+        <v>269</v>
+      </c>
+      <c r="S3" s="136"/>
+      <c r="T3" s="136" t="s">
+        <v>270</v>
+      </c>
+      <c r="U3" s="136"/>
+      <c r="W3" s="136" t="s">
+        <v>295</v>
+      </c>
+      <c r="X3" s="136"/>
+      <c r="Y3" s="136"/>
+      <c r="Z3" s="130"/>
+    </row>
+    <row r="4" spans="10:26" x14ac:dyDescent="0.25">
+      <c r="L4" t="s">
+        <v>329</v>
+      </c>
+      <c r="M4" t="s">
+        <v>330</v>
+      </c>
+      <c r="N4" t="s">
+        <v>329</v>
+      </c>
+      <c r="O4" t="s">
+        <v>330</v>
+      </c>
+      <c r="P4" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>330</v>
+      </c>
+      <c r="R4" t="s">
+        <v>329</v>
+      </c>
+      <c r="S4" t="s">
+        <v>330</v>
+      </c>
+      <c r="T4" t="s">
+        <v>329</v>
+      </c>
+      <c r="U4" t="s">
+        <v>330</v>
+      </c>
+      <c r="W4" s="136" t="s">
+        <v>205</v>
+      </c>
+      <c r="X4" s="136"/>
+      <c r="Y4" s="136"/>
+      <c r="Z4" s="130"/>
+    </row>
+    <row r="5" spans="10:26" x14ac:dyDescent="0.25">
+      <c r="K5" t="s">
+        <v>255</v>
+      </c>
+      <c r="L5">
+        <v>80</v>
+      </c>
+      <c r="P5">
+        <v>80</v>
+      </c>
+      <c r="T5">
+        <v>80</v>
+      </c>
+      <c r="W5" s="136" t="s">
+        <v>296</v>
+      </c>
+      <c r="X5" s="136"/>
+      <c r="Y5" s="136"/>
+      <c r="Z5" s="130"/>
+    </row>
+    <row r="6" spans="10:26" x14ac:dyDescent="0.25">
+      <c r="K6" t="s">
+        <v>271</v>
+      </c>
+      <c r="L6">
+        <v>74</v>
+      </c>
+      <c r="P6">
+        <v>74</v>
+      </c>
+      <c r="T6">
+        <v>74</v>
+      </c>
+      <c r="X6" s="147" t="s">
+        <v>329</v>
+      </c>
+      <c r="Y6" s="147" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="7" spans="10:26" x14ac:dyDescent="0.25">
+      <c r="K7" t="s">
+        <v>247</v>
+      </c>
+      <c r="L7">
+        <v>24</v>
+      </c>
+      <c r="O7">
+        <v>16</v>
+      </c>
+      <c r="P7">
+        <v>8</v>
+      </c>
+      <c r="T7">
+        <v>8</v>
+      </c>
+      <c r="W7" s="133" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="8" spans="10:26" x14ac:dyDescent="0.25">
+      <c r="K8" t="s">
+        <v>272</v>
+      </c>
+      <c r="L8">
+        <v>230</v>
+      </c>
+      <c r="P8">
+        <v>230</v>
+      </c>
+      <c r="T8">
+        <v>230</v>
+      </c>
+      <c r="W8" t="s">
+        <v>276</v>
+      </c>
+      <c r="Y8">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="9" spans="10:26" x14ac:dyDescent="0.25">
+      <c r="K9" t="s">
+        <v>280</v>
+      </c>
+      <c r="M9">
+        <v>60</v>
+      </c>
+      <c r="O9">
+        <v>60</v>
+      </c>
+      <c r="Q9">
+        <v>120</v>
+      </c>
+      <c r="U9">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="10:26" x14ac:dyDescent="0.25">
+      <c r="K10" t="s">
+        <v>273</v>
+      </c>
+      <c r="M10">
+        <v>64</v>
+      </c>
+      <c r="Q10">
+        <v>64</v>
+      </c>
+      <c r="U10">
+        <v>64</v>
+      </c>
+      <c r="W10" s="133" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="11" spans="10:26" x14ac:dyDescent="0.25">
+      <c r="K11" t="s">
+        <v>274</v>
+      </c>
+      <c r="M11">
+        <v>204</v>
+      </c>
+      <c r="Q11">
+        <v>204</v>
+      </c>
+      <c r="U11">
+        <v>204</v>
+      </c>
+      <c r="W11" t="s">
+        <v>277</v>
+      </c>
+      <c r="X11">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="10:26" x14ac:dyDescent="0.25">
+      <c r="K12" t="s">
+        <v>275</v>
+      </c>
+      <c r="L12">
+        <v>50</v>
+      </c>
+      <c r="P12">
+        <v>50</v>
+      </c>
+      <c r="T12">
+        <v>50</v>
+      </c>
+      <c r="W12" t="s">
+        <v>278</v>
+      </c>
+      <c r="X12">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="10:26" x14ac:dyDescent="0.25">
+      <c r="K13" t="s">
+        <v>276</v>
+      </c>
+      <c r="M13">
+        <v>340</v>
+      </c>
+      <c r="Q13">
+        <v>340</v>
+      </c>
+      <c r="S13">
+        <v>340</v>
+      </c>
+      <c r="W13" t="s">
+        <v>279</v>
+      </c>
+      <c r="X13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="10:26" x14ac:dyDescent="0.25">
+      <c r="K14" t="s">
+        <v>277</v>
+      </c>
+      <c r="L14">
+        <v>130</v>
+      </c>
+      <c r="N14">
+        <v>18</v>
+      </c>
+      <c r="P14">
+        <v>148</v>
+      </c>
+      <c r="R14">
+        <v>148</v>
+      </c>
+      <c r="W14" t="s">
+        <v>285</v>
+      </c>
+      <c r="X14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="10:26" x14ac:dyDescent="0.25">
+      <c r="K15" t="s">
+        <v>278</v>
+      </c>
+      <c r="L15">
+        <v>54</v>
+      </c>
+      <c r="P15">
+        <v>54</v>
+      </c>
+      <c r="R15">
+        <v>54</v>
+      </c>
+      <c r="W15" t="s">
+        <v>287</v>
+      </c>
+      <c r="X15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="10:26" x14ac:dyDescent="0.25">
+      <c r="K16" t="s">
+        <v>279</v>
+      </c>
+      <c r="L16">
+        <v>26</v>
+      </c>
+      <c r="P16">
+        <v>26</v>
+      </c>
+      <c r="R16">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="11:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L17" s="131">
+        <f>SUM(L5:L16)</f>
+        <v>668</v>
+      </c>
+      <c r="M17" s="131">
+        <f>SUM(M5:M16)</f>
+        <v>668</v>
+      </c>
+      <c r="W17" t="s">
+        <v>337</v>
+      </c>
+      <c r="X17">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="11:25" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K18" t="s">
+        <v>289</v>
+      </c>
+      <c r="O18">
+        <v>18</v>
+      </c>
+      <c r="Q18">
+        <v>18</v>
+      </c>
+      <c r="U18">
+        <v>18</v>
+      </c>
+      <c r="X18" s="131">
+        <f>SUM(X7:X17)</f>
+        <v>340</v>
+      </c>
+      <c r="Y18" s="131">
+        <f>SUM(Y8:Y17)</f>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="19" spans="11:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="K19" t="s">
+        <v>285</v>
+      </c>
+      <c r="N19">
+        <v>16</v>
+      </c>
+      <c r="P19">
+        <v>16</v>
+      </c>
+      <c r="R19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="11:25" x14ac:dyDescent="0.25">
+      <c r="K20" t="s">
+        <v>287</v>
+      </c>
+      <c r="N20">
+        <v>60</v>
+      </c>
+      <c r="P20">
+        <v>60</v>
+      </c>
+      <c r="R20">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="11:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N21" s="131">
+        <f>SUM(N5:N20)</f>
+        <v>94</v>
+      </c>
+      <c r="O21" s="131">
+        <f>SUM(O5:O20)</f>
+        <v>94</v>
+      </c>
+      <c r="P21" s="131">
+        <f>SUM(P5:P20)</f>
+        <v>746</v>
+      </c>
+      <c r="Q21" s="131">
+        <f>SUM(Q5:Q20)</f>
+        <v>746</v>
+      </c>
+      <c r="W21" s="136" t="s">
+        <v>295</v>
+      </c>
+      <c r="X21" s="136"/>
+      <c r="Y21" s="136"/>
+    </row>
+    <row r="22" spans="11:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="K22" t="s">
+        <v>337</v>
+      </c>
+      <c r="R22">
+        <v>36</v>
+      </c>
+      <c r="U22">
+        <v>36</v>
+      </c>
+      <c r="W22" s="136" t="s">
+        <v>339</v>
+      </c>
+      <c r="X22" s="136"/>
+      <c r="Y22" s="136"/>
+    </row>
+    <row r="23" spans="11:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R23" s="131">
+        <v>340</v>
+      </c>
+      <c r="S23" s="131">
+        <f>SUM(S5:S22)</f>
+        <v>340</v>
+      </c>
+      <c r="T23" s="131">
+        <f>SUM(T5:T22)</f>
+        <v>442</v>
+      </c>
+      <c r="U23" s="131">
+        <f>SUM(U5:U22)</f>
+        <v>442</v>
+      </c>
+      <c r="W23" s="136" t="s">
+        <v>296</v>
+      </c>
+      <c r="X23" s="136"/>
+      <c r="Y23" s="136"/>
+    </row>
+    <row r="24" spans="11:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="11:25" x14ac:dyDescent="0.25">
+      <c r="W25" t="s">
+        <v>340</v>
+      </c>
+      <c r="Y25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="11:25" x14ac:dyDescent="0.25">
+      <c r="W26" t="s">
+        <v>300</v>
+      </c>
+      <c r="Y26">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="11:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Y27" s="131">
+        <f>SUM(Y25:Y26)</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="11:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="K28" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="29" spans="11:25" x14ac:dyDescent="0.25">
+      <c r="K29" t="s">
+        <v>345</v>
+      </c>
+      <c r="W29" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="11:25" x14ac:dyDescent="0.25">
+      <c r="K30" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="31" spans="11:25" x14ac:dyDescent="0.25">
+      <c r="K31" t="s">
+        <v>347</v>
+      </c>
+      <c r="W31" t="s">
+        <v>342</v>
+      </c>
+      <c r="Y31">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="32" spans="11:25" x14ac:dyDescent="0.25">
+      <c r="K32" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>281</v>
+      </c>
+      <c r="C33" t="s">
+        <v>282</v>
+      </c>
+      <c r="D33" t="s">
+        <v>283</v>
+      </c>
+      <c r="E33" t="s">
+        <v>329</v>
+      </c>
+      <c r="F33" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="C34" s="127">
+        <v>46203</v>
+      </c>
+      <c r="D34" t="s">
+        <v>277</v>
+      </c>
+      <c r="E34">
+        <v>18</v>
+      </c>
+      <c r="J34" t="s">
+        <v>282</v>
+      </c>
+      <c r="K34" t="s">
+        <v>283</v>
+      </c>
+      <c r="L34" t="s">
+        <v>329</v>
+      </c>
+      <c r="M34" t="s">
+        <v>330</v>
+      </c>
+      <c r="W34" s="136" t="s">
+        <v>295</v>
+      </c>
+      <c r="X34" s="136"/>
+      <c r="Y34" s="136"/>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D35" s="128" t="s">
+        <v>289</v>
+      </c>
+      <c r="F35">
+        <v>18</v>
+      </c>
+      <c r="J35" s="127">
+        <v>46203</v>
+      </c>
+      <c r="K35" t="s">
+        <v>276</v>
+      </c>
+      <c r="L35">
+        <v>340</v>
+      </c>
+      <c r="W35" s="136" t="s">
+        <v>67</v>
+      </c>
+      <c r="X35" s="136"/>
+      <c r="Y35" s="136"/>
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D36" s="129" t="s">
+        <v>331</v>
+      </c>
+      <c r="K36" s="128" t="s">
+        <v>349</v>
+      </c>
+      <c r="M36">
+        <v>340</v>
+      </c>
+      <c r="W36" s="136" t="s">
+        <v>303</v>
+      </c>
+      <c r="X36" s="136"/>
+      <c r="Y36" s="136"/>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="K37" s="129" t="s">
+        <v>321</v>
+      </c>
+      <c r="W37" s="133" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="38" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="C38" s="127">
+        <v>46203</v>
+      </c>
+      <c r="D38" t="s">
+        <v>285</v>
+      </c>
+      <c r="E38">
+        <v>16</v>
+      </c>
+      <c r="W38" t="s">
+        <v>255</v>
+      </c>
+      <c r="X38">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D39" s="128" t="s">
+        <v>247</v>
+      </c>
+      <c r="F39">
+        <v>16</v>
+      </c>
+      <c r="J39" s="127">
+        <v>46203</v>
+      </c>
+      <c r="K39" t="s">
+        <v>349</v>
+      </c>
+      <c r="L39">
+        <v>304</v>
+      </c>
+      <c r="W39" t="s">
+        <v>271</v>
+      </c>
+      <c r="X39">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D40" s="129" t="s">
+        <v>334</v>
+      </c>
+      <c r="K40" s="128" t="s">
+        <v>277</v>
+      </c>
+      <c r="M40">
+        <v>148</v>
+      </c>
+      <c r="W40" t="s">
+        <v>247</v>
+      </c>
+      <c r="X40">
+        <v>8</v>
+      </c>
+      <c r="Y40">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="K41" s="128" t="s">
+        <v>278</v>
+      </c>
+      <c r="M41">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="C42" s="127">
+        <v>46203</v>
+      </c>
+      <c r="D42" t="s">
+        <v>287</v>
+      </c>
+      <c r="E42">
+        <v>60</v>
+      </c>
+      <c r="K42" s="128" t="s">
+        <v>279</v>
+      </c>
+      <c r="M42">
+        <v>26</v>
+      </c>
+      <c r="W42" s="133" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D43" s="128" t="s">
+        <v>280</v>
+      </c>
+      <c r="F43">
+        <v>60</v>
+      </c>
+      <c r="K43" s="128" t="s">
+        <v>285</v>
+      </c>
+      <c r="M43">
+        <v>16</v>
+      </c>
+      <c r="W43" t="s">
+        <v>272</v>
+      </c>
+      <c r="X43">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="D44" s="129" t="s">
+        <v>335</v>
+      </c>
+      <c r="K44" s="128" t="s">
+        <v>287</v>
+      </c>
+      <c r="M44">
+        <v>60</v>
+      </c>
+      <c r="W44" t="s">
+        <v>307</v>
+      </c>
+      <c r="X44">
+        <v>120</v>
+      </c>
+      <c r="Y44">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="K45" s="129" t="s">
+        <v>323</v>
+      </c>
+      <c r="W45" s="133" t="s">
+        <v>308</v>
+      </c>
+      <c r="Y45">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="J46" s="127"/>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="J47" s="127">
+        <v>46203</v>
+      </c>
+      <c r="K47" t="s">
+        <v>349</v>
+      </c>
+      <c r="L47">
+        <v>36</v>
+      </c>
+      <c r="W47" s="133" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.25">
+      <c r="K48" s="128" t="s">
+        <v>274</v>
+      </c>
+      <c r="M48">
+        <v>36</v>
+      </c>
+      <c r="W48" t="s">
+        <v>273</v>
+      </c>
+      <c r="X48">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="10:25" x14ac:dyDescent="0.25">
+      <c r="K49" s="129" t="s">
+        <v>350</v>
+      </c>
+      <c r="W49" t="s">
+        <v>289</v>
+      </c>
+      <c r="X49">
+        <v>18</v>
+      </c>
+      <c r="Y49">
+        <f>SUM(X48:X49)</f>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51" spans="10:25" x14ac:dyDescent="0.25">
+      <c r="J51" s="127">
+        <v>46203</v>
+      </c>
+      <c r="K51" s="132" t="s">
+        <v>274</v>
+      </c>
+      <c r="L51">
+        <v>50</v>
+      </c>
+      <c r="W51" s="133" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="52" spans="10:25" x14ac:dyDescent="0.25">
+      <c r="K52" s="128" t="s">
+        <v>351</v>
+      </c>
+      <c r="M52">
+        <v>50</v>
+      </c>
+      <c r="W52" s="133" t="s">
+        <v>311</v>
+      </c>
+      <c r="Y52">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" spans="10:25" x14ac:dyDescent="0.25">
+      <c r="K53" s="129" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="54" spans="10:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="W54" s="133" t="s">
+        <v>312</v>
+      </c>
+      <c r="Y54" s="131">
+        <f>Y45-Y52</f>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="55" spans="10:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="10:25" x14ac:dyDescent="0.25">
+      <c r="W56" s="133" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="57" spans="10:25" x14ac:dyDescent="0.25">
+      <c r="W57" t="s">
+        <v>342</v>
+      </c>
+      <c r="Y57" s="148">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="59" spans="10:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="W59" s="133" t="s">
+        <v>314</v>
+      </c>
+      <c r="Y59" s="131">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="60" spans="10:25" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="W35:Y35"/>
+    <mergeCell ref="W36:Y36"/>
+    <mergeCell ref="W4:Y4"/>
+    <mergeCell ref="W5:Y5"/>
+    <mergeCell ref="W21:Y21"/>
+    <mergeCell ref="W22:Y22"/>
+    <mergeCell ref="W23:Y23"/>
+    <mergeCell ref="W34:Y34"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="W3:Y3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2936,27 +5501,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F923618A-53E6-4AA0-84BA-AB41705F9398}">
   <dimension ref="B1:O20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F3" t="s">
         <v>2</v>
       </c>
@@ -2973,7 +5538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2991,7 +5556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="2" t="s">
@@ -3005,8 +5570,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C6" s="102" t="s">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C6" s="137" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="1"/>
@@ -3033,8 +5598,8 @@
       </c>
       <c r="O6" s="7"/>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C7" s="102"/>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C7" s="137"/>
       <c r="D7" s="1"/>
       <c r="E7" s="2" t="s">
         <v>11</v>
@@ -3046,8 +5611,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C8" s="102"/>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C8" s="137"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
         <v>21</v>
@@ -3060,8 +5625,8 @@
       </c>
       <c r="O8" s="7"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C9" s="102"/>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C9" s="137"/>
       <c r="D9" s="1"/>
       <c r="E9" s="2" t="s">
         <v>11</v>
@@ -3069,8 +5634,8 @@
       <c r="M9" s="6"/>
       <c r="O9" s="7"/>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="C10" s="102"/>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C10" s="137"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
         <v>23</v>
@@ -3098,7 +5663,7 @@
       </c>
       <c r="O10" s="7"/>
     </row>
-    <row r="11" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -3118,7 +5683,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="2" t="s">
@@ -3135,7 +5700,7 @@
       </c>
       <c r="O12" s="7"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
         <v>32</v>
       </c>
@@ -3152,7 +5717,7 @@
       <c r="M13" s="6"/>
       <c r="O13" s="7"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
         <v>114</v>
       </c>
@@ -3170,7 +5735,7 @@
       </c>
       <c r="O14" s="7"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="M15" s="6" t="s">
         <v>36</v>
       </c>
@@ -3178,17 +5743,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="M16" s="6" t="s">
         <v>37</v>
       </c>
       <c r="O16" s="7"/>
     </row>
-    <row r="17" spans="11:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="11:15" x14ac:dyDescent="0.25">
       <c r="M17" s="6"/>
       <c r="O17" s="7"/>
     </row>
-    <row r="18" spans="11:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="11:15" x14ac:dyDescent="0.25">
       <c r="K18">
         <v>4</v>
       </c>
@@ -3203,7 +5768,7 @@
       </c>
       <c r="O18" s="7"/>
     </row>
-    <row r="19" spans="11:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="11:15" x14ac:dyDescent="0.25">
       <c r="M19" s="6" t="s">
         <v>40</v>
       </c>
@@ -3211,7 +5776,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="11:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="11:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M20" s="11" t="s">
         <v>41</v>
       </c>
@@ -3232,13 +5797,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC50BE0-433C-401E-8C60-EBD47C86025A}">
   <dimension ref="A1:M35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="18.1640625" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B1" s="3"/>
       <c r="C1" s="4" t="s">
         <v>15</v>
@@ -3249,7 +5814,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -3266,7 +5831,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3280,14 +5845,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="6"/>
       <c r="E4" s="7"/>
       <c r="G4" s="72" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -3296,11 +5861,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="6"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
@@ -3314,14 +5879,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="6"/>
       <c r="E8" s="7"/>
       <c r="G8" s="72" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="11"/>
       <c r="C9" s="12"/>
       <c r="D9" s="12"/>
@@ -3330,11 +5895,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6"/>
       <c r="E10" s="7"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>3</v>
       </c>
@@ -3348,7 +5913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="6"/>
       <c r="E12" s="7"/>
       <c r="G12" s="72" t="s">
@@ -3357,7 +5922,7 @@
       <c r="H12" s="71"/>
       <c r="I12" s="71"/>
     </row>
-    <row r="13" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="11"/>
       <c r="C13" s="12"/>
       <c r="D13" s="12"/>
@@ -3366,11 +5931,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="6"/>
       <c r="E14" s="7"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>4</v>
       </c>
@@ -3384,7 +5949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
       <c r="E16" s="7"/>
       <c r="G16" s="72" t="s">
@@ -3393,7 +5958,7 @@
       <c r="H16" s="71"/>
       <c r="I16" s="71"/>
     </row>
-    <row r="17" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="11"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
@@ -3402,11 +5967,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="6"/>
       <c r="E18" s="7"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>5</v>
       </c>
@@ -3418,7 +5983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B20" s="6"/>
       <c r="E20" s="7"/>
       <c r="G20" s="72" t="s">
@@ -3427,21 +5992,21 @@
       <c r="H20" s="71"/>
       <c r="I20" s="71"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B21" s="6"/>
       <c r="E21" s="7"/>
       <c r="G21" s="72">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="11"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
       <c r="E22" s="13"/>
     </row>
-    <row r="23" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>6</v>
       </c>
@@ -3455,7 +6020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B25" s="6"/>
       <c r="E25" s="7"/>
       <c r="G25" s="72" t="s">
@@ -3464,7 +6029,7 @@
       <c r="H25" s="71"/>
       <c r="I25" s="71"/>
     </row>
-    <row r="26" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="11"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
@@ -3473,8 +6038,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>7</v>
       </c>
@@ -3488,7 +6053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B29" s="6"/>
       <c r="E29" s="4"/>
       <c r="G29" s="72" t="s">
@@ -3497,7 +6062,7 @@
       <c r="H29" s="71"/>
       <c r="I29" s="71"/>
     </row>
-    <row r="30" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="11"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
@@ -3506,8 +6071,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G32">
         <v>1</v>
       </c>
@@ -3525,7 +6090,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="7:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="7:13" x14ac:dyDescent="0.25">
       <c r="G33">
         <v>2</v>
       </c>
@@ -3545,7 +6110,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="7:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G34">
         <v>3</v>
       </c>
@@ -3565,7 +6130,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="7:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="7:13" x14ac:dyDescent="0.25">
       <c r="G35">
         <v>4</v>
       </c>
@@ -3584,34 +6149,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{431369FE-F92F-4C37-9408-0538561CEBA7}">
   <dimension ref="A1:U74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.5" customWidth="1"/>
-    <col min="2" max="2" width="6.6640625" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.6640625" customWidth="1"/>
-    <col min="5" max="5" width="13.1640625" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" customWidth="1"/>
-    <col min="7" max="7" width="27.1640625" customWidth="1"/>
-    <col min="8" max="8" width="2.6640625" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="27.140625" customWidth="1"/>
+    <col min="8" max="8" width="2.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
     <col min="11" max="11" width="19" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="14.5" customWidth="1"/>
-    <col min="14" max="14" width="2.33203125" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" customWidth="1"/>
+    <col min="14" max="14" width="2.28515625" customWidth="1"/>
     <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="11.5" customWidth="1"/>
-    <col min="18" max="18" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.5" customWidth="1"/>
-    <col min="20" max="21" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" customWidth="1"/>
+    <col min="18" max="18" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.42578125" customWidth="1"/>
+    <col min="20" max="21" width="9.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14"/>
       <c r="B1" s="14"/>
     </row>
-    <row r="2" spans="1:21" ht="14.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="14.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>42</v>
       </c>
@@ -3647,7 +6212,7 @@
       </c>
       <c r="P2" s="40"/>
     </row>
-    <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
         <v>43</v>
       </c>
@@ -3669,7 +6234,7 @@
       <c r="O3" s="47"/>
       <c r="P3" s="45"/>
     </row>
-    <row r="4" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="25" t="s">
         <v>44</v>
       </c>
@@ -3712,7 +6277,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A5" s="27" t="s">
         <v>47</v>
       </c>
@@ -3753,7 +6318,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A6" s="27" t="s">
         <v>48</v>
       </c>
@@ -3797,7 +6362,7 @@
       </c>
       <c r="U6" s="63"/>
     </row>
-    <row r="7" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A7" s="27" t="s">
         <v>49</v>
       </c>
@@ -3839,7 +6404,7 @@
         <v>126500</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="27" t="s">
         <v>50</v>
       </c>
@@ -3874,7 +6439,7 @@
       <c r="T8" s="65"/>
       <c r="U8" s="66"/>
     </row>
-    <row r="9" spans="1:21" ht="35" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="27" t="s">
         <v>51</v>
       </c>
@@ -3911,7 +6476,7 @@
       <c r="T9" s="32"/>
       <c r="U9" s="32"/>
     </row>
-    <row r="10" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A10" s="27" t="s">
         <v>123</v>
       </c>
@@ -3951,7 +6516,7 @@
       </c>
       <c r="U10" s="62"/>
     </row>
-    <row r="11" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A11" s="27" t="s">
         <v>52</v>
       </c>
@@ -3988,7 +6553,7 @@
         <v>63510</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A12" s="27" t="s">
         <v>53</v>
       </c>
@@ -4025,7 +6590,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="30" x14ac:dyDescent="0.4">
       <c r="A13" s="27" t="s">
         <v>54</v>
       </c>
@@ -4062,7 +6627,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A14" s="27" t="s">
         <v>55</v>
       </c>
@@ -4103,7 +6668,7 @@
         <v>7520</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A15" s="27" t="s">
         <v>56</v>
       </c>
@@ -4140,7 +6705,7 @@
         <v>4235</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A16" s="27" t="s">
         <v>57</v>
       </c>
@@ -4177,7 +6742,7 @@
         <v>3045</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A17" s="27" t="s">
         <v>58</v>
       </c>
@@ -4214,7 +6779,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A18" s="27" t="s">
         <v>59</v>
       </c>
@@ -4255,7 +6820,7 @@
         <v>4940</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A19" s="27" t="s">
         <v>60</v>
       </c>
@@ -4296,7 +6861,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" ht="30.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="27" t="s">
         <v>61</v>
       </c>
@@ -4339,7 +6904,7 @@
         <v>7400</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="27"/>
       <c r="B21" s="28"/>
       <c r="C21" s="15"/>
@@ -4361,7 +6926,7 @@
       <c r="T21" s="32"/>
       <c r="U21" s="32"/>
     </row>
-    <row r="22" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A22" s="30" t="s">
         <v>69</v>
       </c>
@@ -4404,7 +6969,7 @@
       </c>
       <c r="U22" s="62"/>
     </row>
-    <row r="23" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A23" s="30" t="s">
         <v>70</v>
       </c>
@@ -4444,7 +7009,7 @@
         <v>29555</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="30" t="s">
         <v>71</v>
       </c>
@@ -4481,7 +7046,7 @@
       <c r="T24" s="65"/>
       <c r="U24" s="66"/>
     </row>
-    <row r="25" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="30" t="s">
         <v>72</v>
       </c>
@@ -4516,7 +7081,7 @@
       <c r="T25" s="32"/>
       <c r="U25" s="32"/>
     </row>
-    <row r="26" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A26" s="30" t="s">
         <v>73</v>
       </c>
@@ -4557,7 +7122,7 @@
       </c>
       <c r="U26" s="62"/>
     </row>
-    <row r="27" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A27" s="30" t="s">
         <v>74</v>
       </c>
@@ -4597,7 +7162,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="30" t="s">
         <v>75</v>
       </c>
@@ -4634,7 +7199,7 @@
       <c r="T28" s="12"/>
       <c r="U28" s="13"/>
     </row>
-    <row r="29" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A29" s="15" t="s">
         <v>125</v>
       </c>
@@ -4659,7 +7224,7 @@
         <v>29555</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A30" s="32"/>
       <c r="B30" s="29"/>
       <c r="C30" s="15"/>
@@ -4677,7 +7242,7 @@
       <c r="O30" s="52"/>
       <c r="P30" s="53"/>
     </row>
-    <row r="31" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="15" t="s">
         <v>68</v>
       </c>
@@ -4727,18 +7292,18 @@
         <v>118860</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="L32">
         <f>M31-L31</f>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="85" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="22" t="s">
         <v>42</v>
       </c>
@@ -4774,7 +7339,7 @@
       </c>
       <c r="P45" s="40"/>
     </row>
-    <row r="46" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A46" s="22" t="s">
         <v>43</v>
       </c>
@@ -4796,7 +7361,7 @@
       <c r="O46" s="47"/>
       <c r="P46" s="45"/>
     </row>
-    <row r="47" spans="1:16" ht="17" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="25" t="s">
         <v>44</v>
       </c>
@@ -4836,7 +7401,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A48" s="27" t="s">
         <v>47</v>
       </c>
@@ -4865,7 +7430,7 @@
       </c>
       <c r="P48" s="53"/>
     </row>
-    <row r="49" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A49" s="27" t="s">
         <v>48</v>
       </c>
@@ -4898,7 +7463,7 @@
       </c>
       <c r="P49" s="53"/>
     </row>
-    <row r="50" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A50" s="27" t="s">
         <v>49</v>
       </c>
@@ -4931,7 +7496,7 @@
       </c>
       <c r="P50" s="53"/>
     </row>
-    <row r="51" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A51" s="27" t="s">
         <v>50</v>
       </c>
@@ -4960,7 +7525,7 @@
       </c>
       <c r="P51" s="53"/>
     </row>
-    <row r="52" spans="1:16" ht="34" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="30" x14ac:dyDescent="0.4">
       <c r="A52" s="27" t="s">
         <v>51</v>
       </c>
@@ -4993,7 +7558,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A53" s="27" t="s">
         <v>123</v>
       </c>
@@ -5022,7 +7587,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A54" s="27" t="s">
         <v>52</v>
       </c>
@@ -5051,7 +7616,7 @@
         <v>15540</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A55" s="27" t="s">
         <v>53</v>
       </c>
@@ -5080,7 +7645,7 @@
       </c>
       <c r="P55" s="53"/>
     </row>
-    <row r="56" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" ht="30" x14ac:dyDescent="0.4">
       <c r="A56" s="27" t="s">
         <v>54</v>
       </c>
@@ -5109,7 +7674,7 @@
       <c r="O56" s="52"/>
       <c r="P56" s="53"/>
     </row>
-    <row r="57" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A57" s="27" t="s">
         <v>55</v>
       </c>
@@ -5142,7 +7707,7 @@
       <c r="O57" s="52"/>
       <c r="P57" s="53"/>
     </row>
-    <row r="58" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A58" s="27" t="s">
         <v>56</v>
       </c>
@@ -5171,7 +7736,7 @@
       <c r="O58" s="52"/>
       <c r="P58" s="53"/>
     </row>
-    <row r="59" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A59" s="27" t="s">
         <v>57</v>
       </c>
@@ -5200,7 +7765,7 @@
       <c r="O59" s="52"/>
       <c r="P59" s="53"/>
     </row>
-    <row r="60" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A60" s="27" t="s">
         <v>58</v>
       </c>
@@ -5229,7 +7794,7 @@
       <c r="O60" s="52"/>
       <c r="P60" s="53"/>
     </row>
-    <row r="61" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A61" s="27" t="s">
         <v>59</v>
       </c>
@@ -5262,7 +7827,7 @@
       <c r="O61" s="52"/>
       <c r="P61" s="53"/>
     </row>
-    <row r="62" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A62" s="27" t="s">
         <v>60</v>
       </c>
@@ -5295,7 +7860,7 @@
       <c r="O62" s="52"/>
       <c r="P62" s="53"/>
     </row>
-    <row r="63" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" ht="30" x14ac:dyDescent="0.4">
       <c r="A63" s="27" t="s">
         <v>61</v>
       </c>
@@ -5330,7 +7895,7 @@
       <c r="O63" s="52"/>
       <c r="P63" s="53"/>
     </row>
-    <row r="64" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A64" s="27"/>
       <c r="B64" s="28"/>
       <c r="C64" s="15"/>
@@ -5348,7 +7913,7 @@
       <c r="O64" s="52"/>
       <c r="P64" s="53"/>
     </row>
-    <row r="65" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A65" s="30" t="s">
         <v>69</v>
       </c>
@@ -5379,7 +7944,7 @@
       <c r="O65" s="52"/>
       <c r="P65" s="53"/>
     </row>
-    <row r="66" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A66" s="30" t="s">
         <v>70</v>
       </c>
@@ -5410,7 +7975,7 @@
       <c r="O66" s="52"/>
       <c r="P66" s="53"/>
     </row>
-    <row r="67" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A67" s="30" t="s">
         <v>71</v>
       </c>
@@ -5441,7 +8006,7 @@
       <c r="O67" s="52"/>
       <c r="P67" s="53"/>
     </row>
-    <row r="68" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A68" s="30" t="s">
         <v>72</v>
       </c>
@@ -5472,7 +8037,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A69" s="30" t="s">
         <v>73</v>
       </c>
@@ -5503,7 +8068,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A70" s="30" t="s">
         <v>74</v>
       </c>
@@ -5534,7 +8099,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="71" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A71" s="30" t="s">
         <v>75</v>
       </c>
@@ -5565,7 +8130,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="72" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A72" s="15" t="s">
         <v>125</v>
       </c>
@@ -5590,7 +8155,7 @@
         <v>29555</v>
       </c>
     </row>
-    <row r="73" spans="1:16" ht="17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A73" s="32"/>
       <c r="B73" s="29"/>
       <c r="C73" s="15"/>
@@ -5608,7 +8173,7 @@
       <c r="O73" s="52"/>
       <c r="P73" s="53"/>
     </row>
-    <row r="74" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A74" s="15" t="s">
         <v>68</v>
       </c>
@@ -5662,34 +8227,34 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{451FE678-24D7-4F17-8C17-332E4659A9B1}">
   <dimension ref="A1:W76"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="37.5" style="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5" style="32" customWidth="1"/>
+    <col min="1" max="1" width="37.42578125" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.42578125" style="32" customWidth="1"/>
     <col min="3" max="3" width="17" style="32" customWidth="1"/>
-    <col min="4" max="4" width="14.5" style="32" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="32" customWidth="1"/>
-    <col min="6" max="7" width="9.1640625" style="32" customWidth="1"/>
-    <col min="8" max="8" width="3.5" style="32" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" style="32" customWidth="1"/>
-    <col min="10" max="10" width="13.5" style="32" customWidth="1"/>
-    <col min="11" max="11" width="3.1640625" style="32" customWidth="1"/>
-    <col min="12" max="12" width="9.83203125" style="32" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" style="32" customWidth="1"/>
-    <col min="14" max="14" width="3.33203125" style="32" customWidth="1"/>
-    <col min="15" max="15" width="15.6640625" style="32" customWidth="1"/>
-    <col min="16" max="16" width="14.1640625" style="32" customWidth="1"/>
-    <col min="17" max="17" width="9.1640625" style="32"/>
-    <col min="18" max="18" width="14.83203125" style="32" customWidth="1"/>
-    <col min="19" max="16384" width="9.1640625" style="32"/>
+    <col min="4" max="4" width="14.42578125" style="32" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" style="32" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="32" customWidth="1"/>
+    <col min="8" max="8" width="3.42578125" style="32" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="32" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="32" customWidth="1"/>
+    <col min="11" max="11" width="3.140625" style="32" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="32" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="32" customWidth="1"/>
+    <col min="14" max="14" width="3.28515625" style="32" customWidth="1"/>
+    <col min="15" max="15" width="15.7109375" style="32" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" style="32" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" style="32"/>
+    <col min="18" max="18" width="14.85546875" style="32" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="32"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A1" s="88" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A2" s="15" t="s">
         <v>107</v>
       </c>
@@ -5725,7 +8290,7 @@
       </c>
       <c r="P2" s="21"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.4">
       <c r="A3" s="15"/>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
@@ -5749,7 +8314,7 @@
       <c r="O3" s="21"/>
       <c r="P3" s="21"/>
     </row>
-    <row r="4" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A4" s="17" t="s">
         <v>94</v>
       </c>
@@ -5789,7 +8354,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A5" s="17" t="s">
         <v>77</v>
       </c>
@@ -5815,7 +8380,7 @@
       </c>
       <c r="P5" s="15"/>
     </row>
-    <row r="6" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A6" s="17" t="s">
         <v>95</v>
       </c>
@@ -5841,7 +8406,7 @@
       </c>
       <c r="P6" s="15"/>
     </row>
-    <row r="7" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A7" s="17" t="s">
         <v>96</v>
       </c>
@@ -5867,7 +8432,7 @@
       </c>
       <c r="P7" s="15"/>
     </row>
-    <row r="8" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A8" s="17" t="s">
         <v>78</v>
       </c>
@@ -5899,7 +8464,7 @@
       </c>
       <c r="P8" s="15"/>
     </row>
-    <row r="9" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A9" s="17" t="s">
         <v>97</v>
       </c>
@@ -5925,7 +8490,7 @@
       </c>
       <c r="P9" s="15"/>
     </row>
-    <row r="10" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A10" s="17" t="s">
         <v>98</v>
       </c>
@@ -5951,7 +8516,7 @@
       </c>
       <c r="P10" s="15"/>
     </row>
-    <row r="11" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A11" s="17" t="s">
         <v>135</v>
       </c>
@@ -5981,7 +8546,7 @@
         <v>72760</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A12" s="17" t="s">
         <v>80</v>
       </c>
@@ -6007,7 +8572,7 @@
       </c>
       <c r="P12" s="15"/>
     </row>
-    <row r="13" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A13" s="17" t="s">
         <v>136</v>
       </c>
@@ -6036,11 +8601,11 @@
       <c r="P13" s="15">
         <v>8560</v>
       </c>
-      <c r="W13" s="111" t="s">
+      <c r="W13" s="107" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A14" s="17" t="s">
         <v>99</v>
       </c>
@@ -6065,15 +8630,15 @@
       <c r="P14" s="15">
         <v>7960</v>
       </c>
-      <c r="R14" s="109"/>
+      <c r="R14" s="105"/>
       <c r="S14" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="W14" s="111" t="s">
+      <c r="W14" s="107" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A15" s="17" t="s">
         <v>100</v>
       </c>
@@ -6104,11 +8669,11 @@
       <c r="P15" s="15">
         <v>360</v>
       </c>
-      <c r="W15" s="111" t="s">
+      <c r="W15" s="107" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A16" s="17" t="s">
         <v>101</v>
       </c>
@@ -6136,11 +8701,11 @@
       <c r="R16" s="32" t="s">
         <v>208</v>
       </c>
-      <c r="W16" s="111" t="s">
+      <c r="W16" s="107" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A17" s="17" t="s">
         <v>102</v>
       </c>
@@ -6165,11 +8730,11 @@
       <c r="P17" s="15">
         <v>88600</v>
       </c>
-      <c r="W17" s="111" t="s">
+      <c r="W17" s="107" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A18" s="17" t="s">
         <v>103</v>
       </c>
@@ -6197,11 +8762,11 @@
       <c r="R18" s="32" t="s">
         <v>206</v>
       </c>
-      <c r="W18" s="111" t="s">
+      <c r="W18" s="107" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A19" s="17" t="s">
         <v>104</v>
       </c>
@@ -6230,7 +8795,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A20" s="17" t="s">
         <v>105</v>
       </c>
@@ -6262,7 +8827,7 @@
       <c r="O20" s="15"/>
       <c r="P20" s="15"/>
     </row>
-    <row r="21" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A21" s="17" t="s">
         <v>70</v>
       </c>
@@ -6289,10 +8854,10 @@
       </c>
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
-      <c r="O21" s="106"/>
+      <c r="O21" s="102"/>
       <c r="P21" s="15"/>
     </row>
-    <row r="22" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A22" s="17" t="s">
         <v>84</v>
       </c>
@@ -6319,9 +8884,9 @@
       </c>
       <c r="M22" s="15"/>
       <c r="N22" s="15"/>
-      <c r="O22" s="106"/>
-    </row>
-    <row r="23" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+      <c r="O22" s="102"/>
+    </row>
+    <row r="23" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A23" s="17" t="s">
         <v>88</v>
       </c>
@@ -6344,10 +8909,10 @@
       </c>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
-      <c r="O23" s="106"/>
+      <c r="O23" s="102"/>
       <c r="P23" s="15"/>
     </row>
-    <row r="24" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A24" s="17" t="s">
         <v>90</v>
       </c>
@@ -6374,13 +8939,13 @@
       </c>
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
-      <c r="O24" s="106"/>
+      <c r="O24" s="102"/>
       <c r="P24" s="15"/>
-      <c r="R24" s="110" t="s">
+      <c r="R24" s="106" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A25" s="17" t="s">
         <v>106</v>
       </c>
@@ -6409,13 +8974,13 @@
       </c>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
-      <c r="O25" s="107"/>
+      <c r="O25" s="103"/>
       <c r="P25" s="15"/>
-      <c r="R25" s="112" t="s">
+      <c r="R25" s="108" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A26" s="18" t="s">
         <v>108</v>
       </c>
@@ -6442,13 +9007,13 @@
       </c>
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
-      <c r="O26" s="106"/>
+      <c r="O26" s="102"/>
       <c r="P26" s="15"/>
-      <c r="R26" s="112" t="s">
+      <c r="R26" s="108" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A27" s="18" t="s">
         <v>109</v>
       </c>
@@ -6475,11 +9040,11 @@
       <c r="N27" s="15"/>
       <c r="O27" s="15"/>
       <c r="P27" s="15"/>
-      <c r="R27" s="137" t="s">
+      <c r="R27" s="126" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A28" s="18" t="s">
         <v>110</v>
       </c>
@@ -6506,11 +9071,11 @@
       <c r="N28" s="15"/>
       <c r="O28" s="15"/>
       <c r="P28" s="15"/>
-      <c r="R28" s="112" t="s">
+      <c r="R28" s="108" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A29" s="18" t="s">
         <v>79</v>
       </c>
@@ -6538,7 +9103,7 @@
       </c>
       <c r="P29" s="15"/>
     </row>
-    <row r="30" spans="1:23" ht="21" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" ht="20.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="18" t="s">
         <v>75</v>
       </c>
@@ -6566,7 +9131,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" ht="39" x14ac:dyDescent="0.4">
       <c r="A31" s="18" t="s">
         <v>111</v>
       </c>
@@ -6593,15 +9158,15 @@
       <c r="P31" s="15">
         <v>320</v>
       </c>
-      <c r="R31" s="119" t="s">
+      <c r="R31" s="141" t="s">
         <v>219</v>
       </c>
-      <c r="S31" s="120"/>
-      <c r="T31" s="120"/>
-      <c r="U31" s="120"/>
-      <c r="V31" s="121"/>
-    </row>
-    <row r="32" spans="1:23" ht="20" x14ac:dyDescent="0.25">
+      <c r="S31" s="142"/>
+      <c r="T31" s="142"/>
+      <c r="U31" s="142"/>
+      <c r="V31" s="143"/>
+    </row>
+    <row r="32" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A32" s="18" t="s">
         <v>72</v>
       </c>
@@ -6628,15 +9193,15 @@
       <c r="P32" s="15">
         <v>980</v>
       </c>
-      <c r="R32" s="122" t="s">
+      <c r="R32" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="S32" s="123"/>
-      <c r="T32" s="123"/>
-      <c r="U32" s="123"/>
-      <c r="V32" s="124"/>
-    </row>
-    <row r="33" spans="1:22" ht="20" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S32" s="139"/>
+      <c r="T32" s="139"/>
+      <c r="U32" s="139"/>
+      <c r="V32" s="140"/>
+    </row>
+    <row r="33" spans="1:22" ht="20.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="18"/>
       <c r="B33" s="16"/>
       <c r="C33" s="15"/>
@@ -6648,7 +9213,7 @@
       <c r="I33" s="15"/>
       <c r="J33" s="15"/>
       <c r="K33" s="15"/>
-      <c r="L33" s="108">
+      <c r="L33" s="104">
         <f>SUM(L21:L28)</f>
         <v>106745</v>
       </c>
@@ -6656,19 +9221,19 @@
       <c r="N33" s="15"/>
       <c r="O33" s="15"/>
       <c r="P33" s="15"/>
-      <c r="R33" s="122" t="s">
+      <c r="R33" s="138" t="s">
         <v>127</v>
       </c>
-      <c r="S33" s="123"/>
-      <c r="T33" s="123"/>
-      <c r="U33" s="125" t="s">
+      <c r="S33" s="139"/>
+      <c r="T33" s="139"/>
+      <c r="U33" s="114" t="s">
         <v>220</v>
       </c>
-      <c r="V33" s="126" t="s">
+      <c r="V33" s="115" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="34" spans="1:22" ht="21" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" ht="20.25" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A34" s="18" t="s">
         <v>112</v>
       </c>
@@ -6691,17 +9256,17 @@
       <c r="P34" s="87">
         <v>51315</v>
       </c>
-      <c r="R34" s="127" t="s">
+      <c r="R34" s="116" t="s">
         <v>105</v>
       </c>
-      <c r="S34" s="114"/>
-      <c r="T34" s="114"/>
-      <c r="U34" s="129" t="s">
+      <c r="S34" s="108"/>
+      <c r="T34" s="108"/>
+      <c r="U34" s="118" t="s">
         <v>223</v>
       </c>
-      <c r="V34" s="130"/>
-    </row>
-    <row r="35" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+      <c r="V34" s="119"/>
+    </row>
+    <row r="35" spans="1:22" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A35" s="17"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -6718,17 +9283,17 @@
       <c r="N35" s="15"/>
       <c r="O35" s="15"/>
       <c r="P35" s="15"/>
-      <c r="R35" s="128" t="s">
+      <c r="R35" s="117" t="s">
         <v>222</v>
       </c>
-      <c r="S35" s="114"/>
-      <c r="T35" s="114"/>
-      <c r="U35" s="129"/>
-      <c r="V35" s="130" t="s">
+      <c r="S35" s="108"/>
+      <c r="T35" s="108"/>
+      <c r="U35" s="118"/>
+      <c r="V35" s="119" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A36" s="15"/>
       <c r="B36" s="15"/>
       <c r="C36" s="15">
@@ -6758,10 +9323,10 @@
         <v>411310</v>
       </c>
       <c r="K36" s="15"/>
-      <c r="L36" s="106">
+      <c r="L36" s="102">
         <v>158060</v>
       </c>
-      <c r="M36" s="106">
+      <c r="M36" s="102">
         <v>158060</v>
       </c>
       <c r="N36" s="15"/>
@@ -6773,69 +9338,69 @@
         <f>SUM(P5:P35)</f>
         <v>304565</v>
       </c>
-      <c r="R36" s="117" t="s">
+      <c r="R36" s="112" t="s">
         <v>224</v>
       </c>
-      <c r="S36" s="114"/>
-      <c r="T36" s="114"/>
-      <c r="U36" s="129"/>
-      <c r="V36" s="130"/>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="R37" s="115"/>
-      <c r="S37" s="114"/>
-      <c r="T37" s="114"/>
-      <c r="U37" s="129"/>
-      <c r="V37" s="130"/>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="R38" s="127" t="s">
+      <c r="S36" s="108"/>
+      <c r="T36" s="108"/>
+      <c r="U36" s="118"/>
+      <c r="V36" s="119"/>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="R37" s="110"/>
+      <c r="S37" s="108"/>
+      <c r="T37" s="108"/>
+      <c r="U37" s="118"/>
+      <c r="V37" s="119"/>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="R38" s="116" t="s">
         <v>222</v>
       </c>
-      <c r="S38" s="114"/>
-      <c r="T38" s="114"/>
-      <c r="U38" s="129">
+      <c r="S38" s="108"/>
+      <c r="T38" s="108"/>
+      <c r="U38" s="118">
         <v>106745</v>
       </c>
-      <c r="V38" s="130"/>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="R39" s="133" t="s">
+      <c r="V38" s="119"/>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="R39" s="122" t="s">
         <v>108</v>
       </c>
-      <c r="S39" s="114"/>
-      <c r="T39" s="114"/>
-      <c r="U39" s="129"/>
-      <c r="V39" s="134">
+      <c r="S39" s="108"/>
+      <c r="T39" s="108"/>
+      <c r="U39" s="118"/>
+      <c r="V39" s="123">
         <v>720</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="R40" s="133" t="s">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.4">
+      <c r="R40" s="122" t="s">
         <v>225</v>
       </c>
-      <c r="S40" s="114"/>
-      <c r="T40" s="114"/>
-      <c r="U40" s="129"/>
-      <c r="V40" s="134" t="s">
+      <c r="S40" s="108"/>
+      <c r="T40" s="108"/>
+      <c r="U40" s="118"/>
+      <c r="V40" s="123" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A41" s="88" t="s">
         <v>179</v>
       </c>
-      <c r="R41" s="133" t="s">
+      <c r="R41" s="122" t="s">
         <v>226</v>
       </c>
-      <c r="S41" s="114"/>
-      <c r="T41" s="114"/>
-      <c r="U41" s="129"/>
-      <c r="V41" s="134" t="s">
+      <c r="S41" s="108"/>
+      <c r="T41" s="108"/>
+      <c r="U41" s="118"/>
+      <c r="V41" s="123" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A42" s="15" t="s">
         <v>107</v>
       </c>
@@ -6870,17 +9435,17 @@
         <v>67</v>
       </c>
       <c r="P42" s="21"/>
-      <c r="R42" s="133" t="s">
+      <c r="R42" s="122" t="s">
         <v>70</v>
       </c>
-      <c r="S42" s="114"/>
-      <c r="T42" s="114"/>
-      <c r="U42" s="129"/>
-      <c r="V42" s="134">
+      <c r="S42" s="108"/>
+      <c r="T42" s="108"/>
+      <c r="U42" s="118"/>
+      <c r="V42" s="123">
         <v>1075</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.4">
       <c r="A43" s="15"/>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -6899,17 +9464,17 @@
       <c r="N43" s="21"/>
       <c r="O43" s="21"/>
       <c r="P43" s="21"/>
-      <c r="R43" s="133" t="s">
+      <c r="R43" s="122" t="s">
         <v>84</v>
       </c>
-      <c r="S43" s="114"/>
-      <c r="T43" s="114"/>
-      <c r="U43" s="129"/>
-      <c r="V43" s="134" t="s">
+      <c r="S43" s="108"/>
+      <c r="T43" s="108"/>
+      <c r="U43" s="118"/>
+      <c r="V43" s="123" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="44" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:22" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A44" s="17" t="s">
         <v>94</v>
       </c>
@@ -6948,17 +9513,17 @@
       <c r="P44" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="R44" s="133" t="s">
+      <c r="R44" s="122" t="s">
         <v>88</v>
       </c>
-      <c r="S44" s="114"/>
-      <c r="T44" s="114"/>
-      <c r="U44" s="129"/>
-      <c r="V44" s="134">
+      <c r="S44" s="108"/>
+      <c r="T44" s="108"/>
+      <c r="U44" s="118"/>
+      <c r="V44" s="123">
         <v>760</v>
       </c>
     </row>
-    <row r="45" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:22" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A45" s="17" t="s">
         <v>77</v>
       </c>
@@ -6979,17 +9544,17 @@
       <c r="N45" s="15"/>
       <c r="O45" s="15"/>
       <c r="P45" s="15"/>
-      <c r="R45" s="133" t="s">
+      <c r="R45" s="122" t="s">
         <v>90</v>
       </c>
-      <c r="S45" s="114"/>
-      <c r="T45" s="114"/>
-      <c r="U45" s="129"/>
-      <c r="V45" s="134" t="s">
+      <c r="S45" s="108"/>
+      <c r="T45" s="108"/>
+      <c r="U45" s="118"/>
+      <c r="V45" s="123" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="46" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:22" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A46" s="17" t="s">
         <v>95</v>
       </c>
@@ -7010,17 +9575,17 @@
       <c r="N46" s="15"/>
       <c r="O46" s="15"/>
       <c r="P46" s="15"/>
-      <c r="R46" s="133" t="s">
+      <c r="R46" s="122" t="s">
         <v>106</v>
       </c>
-      <c r="S46" s="114"/>
-      <c r="T46" s="114"/>
-      <c r="U46" s="129"/>
-      <c r="V46" s="134" t="s">
+      <c r="S46" s="108"/>
+      <c r="T46" s="108"/>
+      <c r="U46" s="118"/>
+      <c r="V46" s="123" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="47" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:22" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A47" s="17" t="s">
         <v>96</v>
       </c>
@@ -7041,15 +9606,15 @@
       <c r="N47" s="15"/>
       <c r="O47" s="15"/>
       <c r="P47" s="15"/>
-      <c r="R47" s="117" t="s">
+      <c r="R47" s="112" t="s">
         <v>231</v>
       </c>
-      <c r="S47" s="114"/>
-      <c r="T47" s="114"/>
-      <c r="U47" s="129"/>
-      <c r="V47" s="130"/>
-    </row>
-    <row r="48" spans="1:22" ht="19" x14ac:dyDescent="0.3">
+      <c r="S47" s="108"/>
+      <c r="T47" s="108"/>
+      <c r="U47" s="118"/>
+      <c r="V47" s="119"/>
+    </row>
+    <row r="48" spans="1:22" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A48" s="17" t="s">
         <v>78</v>
       </c>
@@ -7074,13 +9639,13 @@
       <c r="N48" s="15"/>
       <c r="O48" s="15"/>
       <c r="P48" s="15"/>
-      <c r="R48" s="115"/>
-      <c r="S48" s="114"/>
-      <c r="T48" s="114"/>
-      <c r="U48" s="129"/>
-      <c r="V48" s="130"/>
-    </row>
-    <row r="49" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+      <c r="R48" s="110"/>
+      <c r="S48" s="108"/>
+      <c r="T48" s="108"/>
+      <c r="U48" s="118"/>
+      <c r="V48" s="119"/>
+    </row>
+    <row r="49" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A49" s="17" t="s">
         <v>97</v>
       </c>
@@ -7101,20 +9666,20 @@
       <c r="N49" s="15"/>
       <c r="O49" s="15"/>
       <c r="P49" s="15"/>
-      <c r="R49" s="127" t="s">
+      <c r="R49" s="116" t="s">
         <v>222</v>
       </c>
-      <c r="S49" s="114"/>
-      <c r="T49" s="114"/>
-      <c r="U49" s="129">
+      <c r="S49" s="108"/>
+      <c r="T49" s="108"/>
+      <c r="U49" s="118">
         <v>51315</v>
       </c>
-      <c r="V49" s="130"/>
-      <c r="W49" s="113" t="s">
+      <c r="V49" s="119"/>
+      <c r="W49" s="109" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="50" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A50" s="17" t="s">
         <v>98</v>
       </c>
@@ -7135,17 +9700,17 @@
       <c r="N50" s="15"/>
       <c r="O50" s="15"/>
       <c r="P50" s="15"/>
-      <c r="R50" s="133" t="s">
+      <c r="R50" s="122" t="s">
         <v>103</v>
       </c>
-      <c r="S50" s="114"/>
-      <c r="T50" s="114"/>
-      <c r="U50" s="129"/>
-      <c r="V50" s="130">
+      <c r="S50" s="108"/>
+      <c r="T50" s="108"/>
+      <c r="U50" s="118"/>
+      <c r="V50" s="119">
         <v>51315</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A51" s="17" t="s">
         <v>135</v>
       </c>
@@ -7168,15 +9733,15 @@
       <c r="N51" s="15"/>
       <c r="O51" s="15"/>
       <c r="P51" s="15"/>
-      <c r="R51" s="117" t="s">
+      <c r="R51" s="112" t="s">
         <v>232</v>
       </c>
-      <c r="S51" s="114"/>
-      <c r="T51" s="114"/>
-      <c r="U51" s="129"/>
-      <c r="V51" s="130"/>
-    </row>
-    <row r="52" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+      <c r="S51" s="108"/>
+      <c r="T51" s="108"/>
+      <c r="U51" s="118"/>
+      <c r="V51" s="119"/>
+    </row>
+    <row r="52" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A52" s="17" t="s">
         <v>80</v>
       </c>
@@ -7197,13 +9762,13 @@
       <c r="N52" s="15"/>
       <c r="O52" s="15"/>
       <c r="P52" s="15"/>
-      <c r="R52" s="115"/>
-      <c r="S52" s="114"/>
-      <c r="T52" s="114"/>
-      <c r="U52" s="129"/>
-      <c r="V52" s="130"/>
-    </row>
-    <row r="53" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+      <c r="R52" s="110"/>
+      <c r="S52" s="108"/>
+      <c r="T52" s="108"/>
+      <c r="U52" s="118"/>
+      <c r="V52" s="119"/>
+    </row>
+    <row r="53" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A53" s="17" t="s">
         <v>136</v>
       </c>
@@ -7226,17 +9791,17 @@
       <c r="N53" s="15"/>
       <c r="O53" s="15"/>
       <c r="P53" s="15"/>
-      <c r="R53" s="135" t="s">
+      <c r="R53" s="124" t="s">
         <v>103</v>
       </c>
-      <c r="S53" s="114"/>
-      <c r="T53" s="114"/>
-      <c r="U53" s="136" t="s">
+      <c r="S53" s="108"/>
+      <c r="T53" s="108"/>
+      <c r="U53" s="125" t="s">
         <v>233</v>
       </c>
-      <c r="V53" s="130"/>
-    </row>
-    <row r="54" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+      <c r="V53" s="119"/>
+    </row>
+    <row r="54" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A54" s="17" t="s">
         <v>99</v>
       </c>
@@ -7257,17 +9822,17 @@
       <c r="N54" s="15"/>
       <c r="O54" s="15"/>
       <c r="P54" s="15"/>
-      <c r="R54" s="133" t="s">
+      <c r="R54" s="122" t="s">
         <v>104</v>
       </c>
-      <c r="S54" s="114"/>
-      <c r="T54" s="114"/>
-      <c r="U54" s="129"/>
-      <c r="V54" s="130">
+      <c r="S54" s="108"/>
+      <c r="T54" s="108"/>
+      <c r="U54" s="118"/>
+      <c r="V54" s="119">
         <v>52780</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="20" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:23" ht="20.25" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A55" s="17" t="s">
         <v>100</v>
       </c>
@@ -7292,15 +9857,15 @@
       <c r="N55" s="15"/>
       <c r="O55" s="15"/>
       <c r="P55" s="15"/>
-      <c r="R55" s="118" t="s">
+      <c r="R55" s="113" t="s">
         <v>234</v>
       </c>
-      <c r="S55" s="116"/>
-      <c r="T55" s="116"/>
-      <c r="U55" s="131"/>
-      <c r="V55" s="132"/>
-    </row>
-    <row r="56" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+      <c r="S55" s="111"/>
+      <c r="T55" s="111"/>
+      <c r="U55" s="120"/>
+      <c r="V55" s="121"/>
+    </row>
+    <row r="56" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A56" s="17" t="s">
         <v>101</v>
       </c>
@@ -7322,7 +9887,7 @@
       <c r="O56" s="15"/>
       <c r="P56" s="15"/>
     </row>
-    <row r="57" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A57" s="17" t="s">
         <v>102</v>
       </c>
@@ -7347,7 +9912,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A58" s="17" t="s">
         <v>103</v>
       </c>
@@ -7368,11 +9933,11 @@
       <c r="N58" s="15"/>
       <c r="O58" s="15"/>
       <c r="P58" s="15"/>
-      <c r="R58" s="112" t="s">
+      <c r="R58" s="108" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A59" s="17" t="s">
         <v>104</v>
       </c>
@@ -7393,11 +9958,11 @@
       <c r="N59" s="15"/>
       <c r="O59" s="15"/>
       <c r="P59" s="15"/>
-      <c r="R59" s="112" t="s">
+      <c r="R59" s="108" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A60" s="17" t="s">
         <v>105</v>
       </c>
@@ -7422,11 +9987,11 @@
       <c r="N60" s="15"/>
       <c r="O60" s="15"/>
       <c r="P60" s="15"/>
-      <c r="R60" s="112" t="s">
+      <c r="R60" s="108" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="61" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A61" s="17" t="s">
         <v>70</v>
       </c>
@@ -7449,11 +10014,11 @@
       <c r="N61" s="15"/>
       <c r="O61" s="15"/>
       <c r="P61" s="15"/>
-      <c r="R61" s="112" t="s">
+      <c r="R61" s="108" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="62" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A62" s="17" t="s">
         <v>84</v>
       </c>
@@ -7477,7 +10042,7 @@
       <c r="O62" s="15"/>
       <c r="P62" s="15"/>
     </row>
-    <row r="63" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A63" s="17" t="s">
         <v>88</v>
       </c>
@@ -7499,7 +10064,7 @@
       <c r="O63" s="15"/>
       <c r="P63" s="15"/>
     </row>
-    <row r="64" spans="1:23" ht="19" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:23" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A64" s="17" t="s">
         <v>90</v>
       </c>
@@ -7523,7 +10088,7 @@
       <c r="O64" s="15"/>
       <c r="P64" s="15"/>
     </row>
-    <row r="65" spans="1:16" ht="19" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A65" s="17" t="s">
         <v>106</v>
       </c>
@@ -7549,7 +10114,7 @@
       <c r="O65" s="15"/>
       <c r="P65" s="15"/>
     </row>
-    <row r="66" spans="1:16" ht="20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A66" s="18" t="s">
         <v>108</v>
       </c>
@@ -7573,7 +10138,7 @@
       <c r="O66" s="15"/>
       <c r="P66" s="15"/>
     </row>
-    <row r="67" spans="1:16" ht="20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A67" s="18" t="s">
         <v>109</v>
       </c>
@@ -7595,7 +10160,7 @@
       <c r="O67" s="15"/>
       <c r="P67" s="15"/>
     </row>
-    <row r="68" spans="1:16" ht="20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A68" s="18" t="s">
         <v>110</v>
       </c>
@@ -7617,7 +10182,7 @@
       <c r="O68" s="15"/>
       <c r="P68" s="15"/>
     </row>
-    <row r="69" spans="1:16" ht="20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A69" s="18" t="s">
         <v>79</v>
       </c>
@@ -7639,7 +10204,7 @@
       <c r="O69" s="15"/>
       <c r="P69" s="15"/>
     </row>
-    <row r="70" spans="1:16" ht="20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A70" s="18" t="s">
         <v>75</v>
       </c>
@@ -7661,7 +10226,7 @@
       <c r="O70" s="15"/>
       <c r="P70" s="15"/>
     </row>
-    <row r="71" spans="1:16" ht="20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" ht="39" x14ac:dyDescent="0.4">
       <c r="A71" s="18" t="s">
         <v>111</v>
       </c>
@@ -7683,7 +10248,7 @@
       <c r="O71" s="15"/>
       <c r="P71" s="15"/>
     </row>
-    <row r="72" spans="1:16" ht="20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A72" s="18" t="s">
         <v>72</v>
       </c>
@@ -7705,7 +10270,7 @@
       <c r="O72" s="15"/>
       <c r="P72" s="15"/>
     </row>
-    <row r="73" spans="1:16" ht="19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A73" s="18"/>
       <c r="B73" s="16"/>
       <c r="C73" s="15"/>
@@ -7723,7 +10288,7 @@
       <c r="O73" s="15"/>
       <c r="P73" s="15"/>
     </row>
-    <row r="74" spans="1:16" ht="20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A74" s="18" t="s">
         <v>112</v>
       </c>
@@ -7743,7 +10308,7 @@
       <c r="O74" s="15"/>
       <c r="P74" s="15"/>
     </row>
-    <row r="75" spans="1:16" ht="19" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A75" s="17"/>
       <c r="B75" s="15"/>
       <c r="C75" s="15"/>
@@ -7761,7 +10326,7 @@
       <c r="O75" s="15"/>
       <c r="P75" s="15"/>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A76" s="15"/>
       <c r="B76" s="15"/>
       <c r="C76" s="15">
@@ -7800,7 +10365,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB70836-D79F-4864-89CC-B27D7E0A03DC}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7809,13 +10374,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA4CDB96-6C4C-4200-8B12-486AAEF84CD0}">
   <dimension ref="A1:M35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="18.1640625" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B1" s="3"/>
       <c r="C1" s="4" t="s">
         <v>15</v>
@@ -7826,7 +10391,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -7843,7 +10408,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7867,7 +10432,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="6"/>
       <c r="C4" t="s">
         <v>152</v>
@@ -7886,7 +10451,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11"/>
       <c r="C5" s="12" t="s">
         <v>154</v>
@@ -7903,11 +10468,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="6"/>
       <c r="E6" s="7"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
@@ -7931,7 +10496,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8" s="6"/>
       <c r="C8" t="s">
         <v>79</v>
@@ -7949,7 +10514,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="11"/>
       <c r="C9" s="12" t="s">
         <v>158</v>
@@ -7966,11 +10531,11 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="6"/>
       <c r="E10" s="7"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>3</v>
       </c>
@@ -7994,7 +10559,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="6"/>
       <c r="C12" t="s">
         <v>159</v>
@@ -8012,7 +10577,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="11"/>
       <c r="C13" s="12" t="s">
         <v>163</v>
@@ -8029,11 +10594,11 @@
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="6"/>
       <c r="E14" s="7"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>4</v>
       </c>
@@ -8057,7 +10622,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
       <c r="C16" t="s">
         <v>165</v>
@@ -8075,7 +10640,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="11"/>
       <c r="C17" s="12" t="s">
         <v>167</v>
@@ -8092,11 +10657,11 @@
         <v>161</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="6"/>
       <c r="E18" s="7"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>5</v>
       </c>
@@ -8120,7 +10685,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B20" s="6"/>
       <c r="C20" t="s">
         <v>171</v>
@@ -8138,7 +10703,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B21" s="6"/>
       <c r="C21" t="s">
         <v>172</v>
@@ -8154,14 +10719,14 @@
         <v>161</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="11"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
       <c r="E22" s="13"/>
     </row>
-    <row r="23" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>6</v>
       </c>
@@ -8185,7 +10750,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B25" s="6"/>
       <c r="C25" t="s">
         <v>174</v>
@@ -8203,7 +10768,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="11"/>
       <c r="C26" s="12" t="s">
         <v>175</v>
@@ -8220,8 +10785,8 @@
         <v>161</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>7</v>
       </c>
@@ -8245,7 +10810,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B29" s="6"/>
       <c r="C29" t="s">
         <v>177</v>
@@ -8263,7 +10828,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="11"/>
       <c r="C30" s="12" t="s">
         <v>175</v>
@@ -8280,8 +10845,8 @@
         <v>161</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G32">
         <v>1</v>
       </c>
@@ -8299,7 +10864,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="7:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="7:13" x14ac:dyDescent="0.25">
       <c r="G33">
         <v>2</v>
       </c>
@@ -8319,7 +10884,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="7:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G34">
         <v>3</v>
       </c>
@@ -8339,7 +10904,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="7:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="7:13" x14ac:dyDescent="0.25">
       <c r="G35">
         <v>4</v>
       </c>
@@ -8358,14 +10923,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14BBB4DE-EA90-4F91-8180-6C1E6B7C8861}">
   <dimension ref="A2:L32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="10" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>76</v>
       </c>
@@ -8393,7 +10958,7 @@
       </c>
       <c r="L2" s="14"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="14"/>
       <c r="B3" s="14" t="s">
         <v>63</v>
@@ -8410,7 +10975,7 @@
       <c r="K3" s="14"/>
       <c r="L3" s="14"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="14"/>
       <c r="B4" s="14" t="s">
         <v>45</v>
@@ -8444,7 +11009,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>77</v>
       </c>
@@ -8466,7 +11031,7 @@
       </c>
       <c r="L5" s="14"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>78</v>
       </c>
@@ -8492,7 +11057,7 @@
       </c>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>79</v>
       </c>
@@ -8518,7 +11083,7 @@
       </c>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>80</v>
       </c>
@@ -8540,7 +11105,7 @@
       </c>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>81</v>
       </c>
@@ -8566,7 +11131,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>82</v>
       </c>
@@ -8588,7 +11153,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>52</v>
       </c>
@@ -8610,7 +11175,7 @@
         <v>15540</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>53</v>
       </c>
@@ -8632,7 +11197,7 @@
       </c>
       <c r="L12" s="14"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>83</v>
       </c>
@@ -8654,7 +11219,7 @@
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>84</v>
       </c>
@@ -8680,7 +11245,7 @@
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>85</v>
       </c>
@@ -8702,7 +11267,7 @@
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>86</v>
       </c>
@@ -8724,7 +11289,7 @@
       <c r="K16" s="14"/>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>87</v>
       </c>
@@ -8746,7 +11311,7 @@
       <c r="K17" s="14"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>88</v>
       </c>
@@ -8772,7 +11337,7 @@
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>89</v>
       </c>
@@ -8798,7 +11363,7 @@
       <c r="K19" s="14"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>90</v>
       </c>
@@ -8824,7 +11389,7 @@
       <c r="K20" s="14"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="14"/>
       <c r="B21" s="14">
         <v>206640</v>
@@ -8842,7 +11407,7 @@
       <c r="K21" s="14"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>69</v>
       </c>
@@ -8866,7 +11431,7 @@
       <c r="K22" s="14"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>70</v>
       </c>
@@ -8890,7 +11455,7 @@
       <c r="K23" s="14"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>71</v>
       </c>
@@ -8914,7 +11479,7 @@
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>72</v>
       </c>
@@ -8938,7 +11503,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>73</v>
       </c>
@@ -8962,7 +11527,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>74</v>
       </c>
@@ -8986,7 +11551,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>75</v>
       </c>
@@ -9010,7 +11575,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>92</v>
       </c>
@@ -9034,7 +11599,7 @@
         <v>89305</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>91</v>
       </c>
@@ -9054,7 +11619,7 @@
         <v>29555</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="14"/>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -9068,7 +11633,7 @@
       <c r="K31" s="14"/>
       <c r="L31" s="14"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>68</v>
       </c>
@@ -9116,81 +11681,81 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F243036-475E-442E-9214-8F3E938FBBFF}">
   <dimension ref="A1:L45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.6640625" customWidth="1"/>
+    <col min="1" max="1" width="32.7109375" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="11.1640625" customWidth="1"/>
-    <col min="4" max="4" width="4.6640625" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="4.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="17.5" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="15.1640625" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" customWidth="1"/>
-    <col min="12" max="12" width="18.5" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
+    <col min="11" max="11" width="17.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="103"/>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="104"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="144"/>
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="146"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="145"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="B2" s="103" t="s">
+      <c r="B2" s="144" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="104"/>
+      <c r="C2" s="145"/>
       <c r="D2" s="14"/>
-      <c r="E2" s="103" t="s">
+      <c r="E2" s="144" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="104"/>
-      <c r="G2" s="103" t="s">
+      <c r="F2" s="145"/>
+      <c r="G2" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="104"/>
-      <c r="I2" s="103" t="s">
+      <c r="H2" s="145"/>
+      <c r="I2" s="144" t="s">
         <v>205</v>
       </c>
-      <c r="J2" s="104"/>
-      <c r="K2" s="103" t="s">
+      <c r="J2" s="145"/>
+      <c r="K2" s="144" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="104"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L2" s="145"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="14"/>
-      <c r="B3" s="103" t="s">
+      <c r="B3" s="144" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="104"/>
+      <c r="C3" s="145"/>
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="103" t="s">
+      <c r="G3" s="144" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="104"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="104"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="104"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H3" s="145"/>
+      <c r="I3" s="144"/>
+      <c r="J3" s="145"/>
+      <c r="K3" s="144"/>
+      <c r="L3" s="145"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="14"/>
       <c r="B4" s="14" t="s">
         <v>45</v>
@@ -9226,7 +11791,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>77</v>
       </c>
@@ -9248,7 +11813,7 @@
       </c>
       <c r="L5" s="14"/>
     </row>
-    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>95</v>
       </c>
@@ -9270,7 +11835,7 @@
       </c>
       <c r="L6" s="14"/>
     </row>
-    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>79</v>
       </c>
@@ -9296,7 +11861,7 @@
       </c>
       <c r="L7" s="14"/>
     </row>
-    <row r="8" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A8" s="14" t="s">
         <v>97</v>
       </c>
@@ -9318,7 +11883,7 @@
       </c>
       <c r="L8" s="14"/>
     </row>
-    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>98</v>
       </c>
@@ -9340,7 +11905,7 @@
       </c>
       <c r="L9" s="14"/>
     </row>
-    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>180</v>
       </c>
@@ -9366,7 +11931,7 @@
         <v>96500</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>181</v>
       </c>
@@ -9388,7 +11953,7 @@
       </c>
       <c r="L11" s="14"/>
     </row>
-    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>182</v>
       </c>
@@ -9414,7 +11979,7 @@
         <v>12480</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>99</v>
       </c>
@@ -9436,7 +12001,7 @@
         <v>16400</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>102</v>
       </c>
@@ -9458,7 +12023,7 @@
         <v>64000</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>183</v>
       </c>
@@ -9480,7 +12045,7 @@
         <v>236950</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>184</v>
       </c>
@@ -9502,7 +12067,7 @@
       </c>
       <c r="L16" s="14"/>
     </row>
-    <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>185</v>
       </c>
@@ -9528,7 +12093,7 @@
       <c r="K17" s="15"/>
       <c r="L17" s="14"/>
     </row>
-    <row r="18" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>186</v>
       </c>
@@ -9550,7 +12115,7 @@
       <c r="K18" s="15"/>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>84</v>
       </c>
@@ -9576,7 +12141,7 @@
       <c r="K19" s="15"/>
       <c r="L19" s="14"/>
     </row>
-    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>89</v>
       </c>
@@ -9598,7 +12163,7 @@
       <c r="K20" s="15"/>
       <c r="L20" s="14"/>
     </row>
-    <row r="21" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>90</v>
       </c>
@@ -9624,7 +12189,7 @@
       <c r="K21" s="15"/>
       <c r="L21" s="14"/>
     </row>
-    <row r="22" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>70</v>
       </c>
@@ -9650,7 +12215,7 @@
       <c r="K22" s="15"/>
       <c r="L22" s="14"/>
     </row>
-    <row r="23" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="15"/>
       <c r="B23" s="92">
         <f>SUM(B5:B22)</f>
@@ -9670,7 +12235,7 @@
       <c r="K23" s="15"/>
       <c r="L23" s="14"/>
     </row>
-    <row r="24" spans="1:12" ht="18" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>187</v>
       </c>
@@ -9694,7 +12259,7 @@
       <c r="K24" s="15"/>
       <c r="L24" s="14"/>
     </row>
-    <row r="25" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A25" s="14" t="s">
         <v>188</v>
       </c>
@@ -9718,7 +12283,7 @@
       <c r="K25" s="15"/>
       <c r="L25" s="14"/>
     </row>
-    <row r="26" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A26" s="14" t="s">
         <v>75</v>
       </c>
@@ -9742,7 +12307,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A27" s="14" t="s">
         <v>72</v>
       </c>
@@ -9766,7 +12331,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A28" s="14" t="s">
         <v>189</v>
       </c>
@@ -9790,7 +12355,7 @@
         <v>4820</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A29" s="14" t="s">
         <v>190</v>
       </c>
@@ -9814,7 +12379,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A30" s="14" t="s">
         <v>191</v>
       </c>
@@ -9838,7 +12403,7 @@
       <c r="K30" s="15"/>
       <c r="L30" s="14"/>
     </row>
-    <row r="31" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="15"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -9876,7 +12441,7 @@
         <v>434370</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="18" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A32" s="14" t="s">
         <v>112</v>
       </c>
@@ -9896,7 +12461,7 @@
         <v>85490</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="15"/>
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
@@ -9922,7 +12487,7 @@
         <v>519860</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="18" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A34" s="15"/>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -9936,7 +12501,7 @@
       <c r="K34" s="91"/>
       <c r="L34" s="101"/>
     </row>
-    <row r="35" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A35" s="15"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -9950,7 +12515,7 @@
       <c r="K35" s="15"/>
       <c r="L35" s="14"/>
     </row>
-    <row r="36" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A36" s="32"/>
       <c r="B36" s="32"/>
       <c r="C36" s="32"/>
@@ -9963,7 +12528,7 @@
       <c r="J36" s="32"/>
       <c r="K36" s="32"/>
     </row>
-    <row r="37" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A37" s="32"/>
       <c r="B37" s="32"/>
       <c r="C37" s="32"/>
@@ -9976,7 +12541,7 @@
       <c r="J37" s="32"/>
       <c r="K37" s="32"/>
     </row>
-    <row r="38" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A38" s="32"/>
       <c r="B38" s="32"/>
       <c r="C38" s="32"/>
@@ -9989,7 +12554,7 @@
       <c r="J38" s="32"/>
       <c r="K38" s="32"/>
     </row>
-    <row r="39" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A39" s="32"/>
       <c r="B39" s="32"/>
       <c r="C39" s="32"/>
@@ -10002,32 +12567,32 @@
       <c r="J39" s="32"/>
       <c r="K39" s="32"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H40" s="85" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H41" s="85" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H42" s="85" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H43" s="85" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H44" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H45" t="s">
         <v>203</v>
       </c>
